--- a/test-data/sscData.xlsx
+++ b/test-data/sscData.xlsx
@@ -1,27 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Chorus Portal Automation_Work\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1534CEFD-2D7A-407F-AD29-5B7D703258C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39ACA5F5-BC86-4EAB-9977-239209F584BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="QA" sheetId="1" r:id="rId1"/>
     <sheet name="Names_Email" sheetId="2" r:id="rId2"/>
     <sheet name="API" sheetId="4" r:id="rId3"/>
-    <sheet name="API_new" sheetId="5" r:id="rId4"/>
+    <sheet name="API_Chorus" sheetId="5" r:id="rId4"/>
+    <sheet name="API_Fielo" sheetId="6" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="7" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">API_Fielo!$A$1:$S$72</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -65,8 +81,27 @@
 </comments>
 </file>
 
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={A467031E-3011-4E4C-8096-3DD99C049EBE}</author>
+  </authors>
+  <commentList>
+    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{A467031E-3011-4E4C-8096-3DD99C049EBE}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Only for "GET", "POST", "PUT"
+</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1547" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1780" uniqueCount="429">
   <si>
     <t>username</t>
   </si>
@@ -1075,6 +1110,484 @@
   </si>
   <si>
     <t>TestCase89</t>
+  </si>
+  <si>
+    <t>Ai4P@ssword4</t>
+  </si>
+  <si>
+    <t>AI4HR</t>
+  </si>
+  <si>
+    <t>TestCase8</t>
+  </si>
+  <si>
+    <t>TestCase9</t>
+  </si>
+  <si>
+    <t>TestCase10</t>
+  </si>
+  <si>
+    <t>fielo</t>
+  </si>
+  <si>
+    <t>https://loyalty-qa.app.fielo.com/dx/api/application/v2/objects?object=Store</t>
+  </si>
+  <si>
+    <t>https://loyalty-qa.app.fielo.com/dx/api/application/v2/data_views/GetStoreByBusinessKeys</t>
+  </si>
+  <si>
+    <t>PATCH</t>
+  </si>
+  <si>
+    <t>{
+    "pageInstructions": []
+}</t>
+  </si>
+  <si>
+    <t>https://loyalty-qa.app.fielo.com/dx/api/application/v2/objects?object=Product</t>
+  </si>
+  <si>
+    <t>https://loyalty-qa.app.fielo.com/dx/api/application/v2/data_views/GetProductByBusinessKeys</t>
+  </si>
+  <si>
+    <t>heading</t>
+  </si>
+  <si>
+    <t>Create Store</t>
+  </si>
+  <si>
+    <t>Get Store by Store Code</t>
+  </si>
+  <si>
+    <t>Update Store</t>
+  </si>
+  <si>
+    <t>Delete Store</t>
+  </si>
+  <si>
+    <t>Create Product</t>
+  </si>
+  <si>
+    <t>Get Product by Product Code</t>
+  </si>
+  <si>
+    <t>Update Product</t>
+  </si>
+  <si>
+    <t>https://loyalty-qa.app.fielo.com/dx/api/application/v2/objects/STE6TG95YWx0eV9fUHJvZHVjdF82ODlkZTM4MWY2ODE0ZjAwYTY4OTIyMmY/actions/Edit</t>
+  </si>
+  <si>
+    <t>Delete Product</t>
+  </si>
+  <si>
+    <t>https://loyalty-qa.app.fielo.com/dx/api/application/v2/objects/STE6TG95YWx0eV9fUHJvZHVjdF82ODlkZTM4MWY2ODE0ZjAwYTY4OTIyMmY/actions/DeleteObject</t>
+  </si>
+  <si>
+    <t>Create Reward</t>
+  </si>
+  <si>
+    <t>https://loyalty-qa.app.fielo.com/dx/api/application/v2/objects?Object=Reward</t>
+  </si>
+  <si>
+    <t>Get Reward By ExternalID</t>
+  </si>
+  <si>
+    <t>https://loyalty-qa.app.fielo.com/dx/api/application/v2/data_views/GetRewardByBusinessKeys</t>
+  </si>
+  <si>
+    <t>Add Reward Stock</t>
+  </si>
+  <si>
+    <t>https://loyalty-qa.app.fielo.com/dx/api/application/v2/objects/STE6TG95YWx0eV9fUmV3YXJkXzY4OWRmMWM0ZjY4MTRmMDBhNjg5MjI1Ng/actions/AddRewardStock</t>
+  </si>
+  <si>
+    <t>{
+  "content": {
+    "RewardQuantity": 100
+}
+}</t>
+  </si>
+  <si>
+    <t>Delete Reward</t>
+  </si>
+  <si>
+    <t>https://loyalty-qa.app.fielo.com/dx/api/application/v2/objects/STE6TG95YWx0eV9fU3RvcmVfNjg2N2UyNDFjOGJmZDE3ZGQ3ZDQ2NDBj/actions/DeleteObject</t>
+  </si>
+  <si>
+    <t>Get Program List</t>
+  </si>
+  <si>
+    <t>https://loyalty-qa.app.fielo.com/dx/api/application/v2/data_views/ProgramList</t>
+  </si>
+  <si>
+    <t>Create Member</t>
+  </si>
+  <si>
+    <t>https://loyalty-qa.app.fielo.com/dx/api/application/v2/objects?object=Member</t>
+  </si>
+  <si>
+    <t>Get Member By ExternalID</t>
+  </si>
+  <si>
+    <t>https://loyalty-qa.app.fielo.com/dx/api/application/v2/data_views/MemberByExternalID</t>
+  </si>
+  <si>
+    <t>Add Balance To Member</t>
+  </si>
+  <si>
+    <t>https://loyalty-qa.app.fielo.com/dx/api/application/v2/objects/STE6TG95YWx0eV9fTWVtYmVyXzY4OWUxMTk1ZjY4MTRmMDBhNjg5MjJlZA/actions/AddBalance</t>
+  </si>
+  <si>
+    <t>{
+  "content": {
+    "AdjustBalances":[
+    {
+        "Amount":20,
+        "Name":"Points"
+    }
+    ]
+  }
+}
+// Use the ID that is obtained in the Response of Get member By ExternalID in the URL
+// use the @Version that is obtained in the Get Member By ExternalID request: Set that in the Header of this request in if-match</t>
+  </si>
+  <si>
+    <t>Create Sale</t>
+  </si>
+  <si>
+    <t>https://loyalty-qa.app.fielo.com/dx/api/application/v2/objects?object=Sale</t>
+  </si>
+  <si>
+    <t>{
+  "objectTypeID": "SaleCase",
+  "content": {
+    "Origin": "API",
+    "ExternalID": "3aassdsadsad55aa921945595279542051",
+    "SaleChannelCode": "TT01",
+    "PointOfSaleID": "10",
+    "SaleItems": [
+      {
+        "ProductCode": "19529",
+        "Quantity": 1,
+        "TotalAmount":10
+      },
+      {
+        "ProductCode": "19527",
+        "Quantity": 1,
+        "TotalAmount":10
+      },
+      {
+        "ProductCode": "19856",
+        "Quantity": 1,
+        "TotalAmount":10
+      }
+    ],
+    "SaleDateTime": "2025-07-01T10:56:27.066Z",
+    "MemberExternalID": "99691eb263-3573-4be4-90b5-abe027d7b4ec",
+    "StoreCode": "NW-RJ567"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Create Segment</t>
+  </si>
+  <si>
+    <t>https://loyalty-qa.app.fielo.com/dx/api/application/v2/objects?object=Segment</t>
+  </si>
+  <si>
+    <t>{
+  "objectTypeID": "SegmentCase",
+  "content": {
+    "Name": "Test segment",
+    "Description": "Test segment"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Mark Segment Active</t>
+  </si>
+  <si>
+    <t>https://loyalty-qa.app.fielo.com/dx/api/application/v2/objects/STE6TG95YWx0eV9fU2VnbWVudENhc2VfNjg5ZTExZTkxZGQzOTQyZjgxMTYzNjY3/actions/MarkAsActive</t>
+  </si>
+  <si>
+    <t>Mark Segment Inactive</t>
+  </si>
+  <si>
+    <t>https://loyalty-qa.app.fielo.com/dx/api/application/v2/objects/STE6TG95YWx0eV9fU2VnbWVudENhc2VfNjg5ZTExZTkxZGQzOTQyZjgxMTYzNjY3/actions/MarkAsInactive</t>
+  </si>
+  <si>
+    <t>Get Ledger Entries Between Dates</t>
+  </si>
+  <si>
+    <t>https://loyalty-qa.app.fielo.com/dx/api/application/v2/data_views/LedgerEntriesBetweenDates</t>
+  </si>
+  <si>
+    <t>Create Redemption</t>
+  </si>
+  <si>
+    <t>https://loyalty-qa.app.fielo.com/dx/api/application/v2/cases?object=Redemption</t>
+  </si>
+  <si>
+    <t>Get RedemptionItem by Voucher Code</t>
+  </si>
+  <si>
+    <t>https://loyalty-qa.app.fielo.com/dx/api/application/v2/data_views/RedemptionItemsByVoucherCode</t>
+  </si>
+  <si>
+    <t>Lock Voucher Code</t>
+  </si>
+  <si>
+    <t>https://loyalty-qa.app.fielo.com/dx/api/application/v2/objects/STE6TG95YWx0eV9fUmVkZW1wdGlvbkl0ZW1DYXNlXzY4OWUxNzMwZjY4MTRmMDBhNjg5MjM1MA/actions/Lock</t>
+  </si>
+  <si>
+    <t>{
+  "content": {
+  }
+}
+// Use the ID that is obtained in the Response of Get RedemptionItem By Voucher Code in the Patch URL of this request.
+// use the @Version that is obtained in the Get RedemptionItem By Voucher Code: Set that in the Header of this request in if-match
+// 1. Lock the Redemption using Lock Action. 2. Use Redemption using Use Action in the URL</t>
+  </si>
+  <si>
+    <t>Use Voucher Code</t>
+  </si>
+  <si>
+    <t>https://loyalty-qa.app.fielo.com/dx/api/application/v2/objects/STE6TG95YWx0eV9fUmVkZW1wdGlvbkl0ZW1DYXNlXzY4OWUxNzMwZjY4MTRmMDBhNjg5MjM1MA/actions/Use</t>
+  </si>
+  <si>
+    <t>{
+  "content": {
+  }
+}
+// Use the ID that is obtained in the Response of Get RedemptionItem By Voucher Code in the Patch URL of this request.
+// use the @Version that is obtained in the Get RedemptionItem By Voucher Code: Set that in the Header of this request in if-match
+// 1. Lock the Redemption using Lock Action. 
+// 2. Use Redemption with Use Action</t>
+  </si>
+  <si>
+    <t>token</t>
+  </si>
+  <si>
+    <t>createdBy</t>
+  </si>
+  <si>
+    <t>"This stage is ready to transition."</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>https://loyalty-qa.app.fielo.com/dx/api/application/v2/cases/STE6TG95YWx0eV9fU3RvcmVfNjkzODQ0ZGZlNjQzMjgzMTcwNjhjNGI0/actions/Edit?viewType=form</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+https://loyalty-qa.app.fielo.com/dx/api/application/v2/cases/STE6TG95YWx0eV9fU3RvcmVfNjkzODQ0ZGZlNjQzMjgzMTcwNjhjNGI0/actions/DeleteObject?viewType=form</t>
+  </si>
+  <si>
+    <t>{"content":{"ReasonForStatusUpdate":"test"},"pageInstructions":[]}</t>
+  </si>
+  <si>
+    <t>{
+  "dataViewParameters": {
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "dataViewParameters": {
+    "Voucher Code": "2312312a"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Nuggets</t>
+  </si>
+  <si>
+    <t>ACTIVE</t>
+  </si>
+  <si>
+    <t>BK Apparel</t>
+  </si>
+  <si>
+    <t>Loyalty</t>
+  </si>
+  <si>
+    <t>ExternalID</t>
+  </si>
+  <si>
+    <t>Program</t>
+  </si>
+  <si>
+    <t>BusinessID</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "Name": "Store NW-RJ463",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "ProductCode": "19523",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "ExternalID": "45671",</t>
+  </si>
+  <si>
+    <t>{
+  "dataViewParameters": {
+    "ExternalID": "34567892"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "dataViewParameters": {
+    "MemberExternalID": "34567892",
+    "FromDateTime": "2025-08-01T21:50:42.060Z",
+    "ToDateTime": "2025-08-15T21:50:42.060Z"
+  },
+  "query":{
+    "select":[
+      {
+        "field":"CurrencyAvailable"
+      },
+      {
+        "field":"CurrencyAwarded"
+      },
+      {
+        "field":"Type"
+      },
+      {
+         "field":"Member"
+      },
+      {"field":"MemberBalance"}
+    ]
+}
+}</t>
+  </si>
+  <si>
+    <t>{
+  "caseTypeID": "RedemptionCase",
+  "content": {
+    "Origin": "API",
+    "MemberExternalID" : "34567892",
+    "RedemptionItems": [
+      {
+        "Quantity":"1",
+        "RewardExternalID":"34567",
+        "VoucherCode":"4532412a"
+      },
+      {
+        "Quantity":"1",
+        "RewardExternalID":"45678",
+        "VoucherCode":"2312312a"
+      }
+    ]
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "objectTypeID": "Member",
+  "content": {
+    "Origin": "API",
+    "ExternalID": "34567892",
+    "DateOfBirth": "2010-07-05",
+    "EmailAddress": "Sample@email.com",
+    "FullName":"Sample Member",
+    "MobileNumber":"9876543210",
+    "JoinDateTime":"2023-05-06T16:56:27.066Z",
+    "ProgramBusinessID":"P-337UUY"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "objectTypeID": "Store",
+  "content": {
+    "Origin": "API",
+    "StoreCode": "NW-RJ465",
+    "Name": "Store NW-RJ465",
+    "Description": "Store6 Description",
+    "Address": 
+      {
+        "Street":"Street1",
+        "City":"City1",
+        "StateProvince": "State1",
+        "Country": "BRAZIL",
+        "PostalCode": "12345"
+      },
+    "IsParticipating": true
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "dataViewParameters": {
+    "StoreCode": "NW-RJ465"
+  }
+}</t>
+  </si>
+  <si>
+    <t>"Store NW-RJ465"</t>
+  </si>
+  <si>
+    <t>{"content":{"Description":"Store4 Description","Name":"Store NW-RJ465","StoreCode":"NW-RJ465","Address":{"Street":"Street1","City":"City1","StateProvince":"State1","PostalCode":"12345","Country":"BRAZIL"},"IsParticipating":true},"pageInstructions":[]}</t>
+  </si>
+  <si>
+    <t>{
+  "objectTypeID": "Product",
+  "content": {
+    "Origin": "API",
+    "Name":"Nuggets",
+    "Description":"Nuggets",
+    "ProductCode": "19525",
+    "Brand": "Burger King",
+    "Category": "Snack",
+    "Incentivizable":true
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "dataViewParameters": {
+    "ProductCode": "19525"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+    "content": {
+        "Name": "Product",
+        "Description": "UpdatedDescription",
+        "ProductCode": "19525",
+        "Brand": "Brand",
+        "Category": "Category",
+        "Incentivizable": true
+    },
+    "pageInstructions": []
+}</t>
+  </si>
+  <si>
+    <t>{
+  "objectTypeID": "Reward",
+  "content": {
+    "Origin": "API",
+    "Name": "BK Apparel",
+    "ExternalID": "45673",
+    "RewardType": "stock_control",
+    "RewardExpiration": "2025-09-06T04:00:00.000Z",
+    "RewardCost": "",
+    "DaysAvailable": ""
+    }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "dataViewParameters": {
+    "ExternalID": "45673"
+  }
+}</t>
   </si>
 </sst>
 </file>
@@ -1170,7 +1683,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
@@ -1222,6 +1735,15 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1526,6 +2048,15 @@
 </ThreadedComments>
 </file>
 
+<file path=xl/threadedComments/threadedComment3.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="L1" dT="2025-10-27T16:27:55.40" personId="{2DC18BBD-7BBA-4FE2-8DD8-CEB2486A022C}" id="{A467031E-3011-4E4C-8096-3DD99C049EBE}">
+    <text xml:space="preserve">Only for "GET", "POST", "PUT"
+</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S9"/>
@@ -1534,7 +2065,7 @@
     <col min="1" max="1" width="11.109375" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="4.109375" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.109375" style="6" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="14.109375" style="6" customWidth="1"/>
     <col min="5" max="5" width="12.5546875" style="6" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" style="6" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.21875" style="6" bestFit="1" customWidth="1"/>
@@ -1558,7 +2089,7 @@
     <col min="25" max="16384" width="8.88671875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>11</v>
       </c>
@@ -1628,7 +2159,7 @@
         <v>34</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>186</v>
+        <v>333</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>5</v>
@@ -1654,7 +2185,7 @@
         <v>34</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>186</v>
+        <v>333</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>5</v>
@@ -1680,7 +2211,7 @@
         <v>34</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>186</v>
+        <v>333</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>5</v>
@@ -1704,7 +2235,7 @@
         <v>34</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>186</v>
+        <v>333</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>5</v>
@@ -1752,7 +2283,7 @@
         <v>34</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>186</v>
+        <v>333</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>5</v>
@@ -1775,7 +2306,7 @@
         <v>34</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>186</v>
+        <v>333</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>5</v>
@@ -1804,7 +2335,7 @@
         <v>34</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>186</v>
+        <v>333</v>
       </c>
       <c r="S8" s="6" t="s">
         <v>187</v>
@@ -1821,17 +2352,18 @@
         <v>34</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>186</v>
+        <v>333</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1" xr:uid="{C7A33EB6-8367-4005-A814-B19729D1B87B}"/>
     <hyperlink ref="H3" r:id="rId2" xr:uid="{6B0F5573-1B6D-40BD-A1CD-4FF2D6A12B60}"/>
-    <hyperlink ref="D2" r:id="rId3" xr:uid="{BFC9E07A-6B6B-4917-9373-71F733F22D5F}"/>
+    <hyperlink ref="D2" r:id="rId3" display="Ai4P@ssword3" xr:uid="{BFC9E07A-6B6B-4917-9373-71F733F22D5F}"/>
+    <hyperlink ref="D9" r:id="rId4" display="Ai4P@ssword3" xr:uid="{C693285A-AACF-4030-BAA6-4C6360692518}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>
 </worksheet>
 </file>
 
@@ -4427,15 +4959,15 @@
   <cols>
     <col min="1" max="1" width="10.5546875" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.77734375" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.21875" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.21875" style="6" customWidth="1"/>
     <col min="4" max="4" width="102.44140625" style="20" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.5546875" style="6" customWidth="1"/>
     <col min="6" max="6" width="13.88671875" style="6" customWidth="1"/>
-    <col min="7" max="7" width="35.6640625" style="20" customWidth="1"/>
-    <col min="8" max="8" width="21.21875" style="6" customWidth="1"/>
-    <col min="9" max="9" width="11.5546875" style="6" customWidth="1"/>
-    <col min="10" max="10" width="12.33203125" style="6" customWidth="1"/>
-    <col min="11" max="11" width="11.77734375" style="6" customWidth="1"/>
+    <col min="7" max="7" width="14.109375" style="20" customWidth="1"/>
+    <col min="8" max="8" width="21.21875" style="6" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="11.5546875" style="6" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" style="6" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="11.77734375" style="23" customWidth="1"/>
     <col min="12" max="12" width="25.5546875" style="6" customWidth="1"/>
     <col min="13" max="13" width="25.109375" style="6" customWidth="1"/>
     <col min="14" max="14" width="28.109375" style="6" bestFit="1" customWidth="1"/>
@@ -4476,7 +5008,7 @@
       <c r="J1" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="22" t="s">
         <v>61</v>
       </c>
       <c r="L1" s="4" t="s">
@@ -4514,8 +5046,8 @@
       <c r="E2" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F2" s="8" t="s">
-        <v>186</v>
+      <c r="F2" s="13" t="s">
+        <v>333</v>
       </c>
       <c r="G2" s="8"/>
       <c r="H2" s="10" t="s">
@@ -4527,11 +5059,11 @@
       <c r="J2" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="K2" s="6">
+      <c r="K2" s="23">
         <v>1</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>64</v>
+        <v>334</v>
       </c>
       <c r="M2" s="6" t="s">
         <v>5</v>
@@ -4553,8 +5085,8 @@
       <c r="E3" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="8" t="s">
-        <v>186</v>
+      <c r="F3" s="13" t="s">
+        <v>333</v>
       </c>
       <c r="G3" s="8"/>
       <c r="H3" s="6" t="s">
@@ -4566,7 +5098,7 @@
       <c r="J3" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="K3" s="6">
+      <c r="K3" s="23">
         <v>1</v>
       </c>
       <c r="L3" s="6" t="s">
@@ -4593,7 +5125,7 @@
         <v>34</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>186</v>
+        <v>333</v>
       </c>
       <c r="G4" s="8"/>
       <c r="H4" s="10" t="s">
@@ -4605,7 +5137,7 @@
       <c r="J4" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="23">
         <v>1</v>
       </c>
       <c r="L4" s="6" t="s">
@@ -4632,7 +5164,7 @@
         <v>34</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>186</v>
+        <v>333</v>
       </c>
       <c r="G5" s="8"/>
       <c r="H5" s="10" t="s">
@@ -4644,7 +5176,7 @@
       <c r="J5" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K5" s="23">
         <v>1</v>
       </c>
       <c r="L5" s="10" t="s">
@@ -4671,7 +5203,7 @@
         <v>34</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>186</v>
+        <v>333</v>
       </c>
       <c r="G6" s="8"/>
       <c r="H6" s="10" t="s">
@@ -4683,7 +5215,7 @@
       <c r="J6" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="23">
         <v>1</v>
       </c>
       <c r="L6" s="10" t="s">
@@ -4710,7 +5242,7 @@
         <v>34</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>186</v>
+        <v>333</v>
       </c>
       <c r="G7" s="8"/>
       <c r="H7" s="10" t="s">
@@ -4722,7 +5254,7 @@
       <c r="J7" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="K7" s="6">
+      <c r="K7" s="23">
         <v>1</v>
       </c>
       <c r="L7" s="10" t="s">
@@ -4749,7 +5281,7 @@
         <v>34</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>186</v>
+        <v>333</v>
       </c>
       <c r="G8" s="8"/>
       <c r="H8" s="10" t="s">
@@ -4761,7 +5293,7 @@
       <c r="J8" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="K8" s="6">
+      <c r="K8" s="23">
         <v>1</v>
       </c>
       <c r="L8" s="10" t="s">
@@ -4788,7 +5320,7 @@
         <v>34</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>186</v>
+        <v>333</v>
       </c>
       <c r="G9" s="8"/>
       <c r="H9" s="10" t="s">
@@ -4800,7 +5332,7 @@
       <c r="J9" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="K9" s="6">
+      <c r="K9" s="23">
         <v>1</v>
       </c>
       <c r="L9" s="10" t="s">
@@ -4827,7 +5359,7 @@
         <v>34</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>186</v>
+        <v>333</v>
       </c>
       <c r="G10" s="8"/>
       <c r="H10" s="10" t="s">
@@ -4839,7 +5371,7 @@
       <c r="J10" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="K10" s="6">
+      <c r="K10" s="23">
         <v>1</v>
       </c>
       <c r="L10" s="10" t="s">
@@ -4866,7 +5398,7 @@
         <v>34</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>186</v>
+        <v>333</v>
       </c>
       <c r="G11" s="8"/>
       <c r="H11" s="10" t="s">
@@ -4878,7 +5410,7 @@
       <c r="J11" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="K11" s="6">
+      <c r="K11" s="23">
         <v>1</v>
       </c>
       <c r="L11" s="10" t="s">
@@ -4905,7 +5437,7 @@
         <v>34</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>186</v>
+        <v>333</v>
       </c>
       <c r="G12" s="8"/>
       <c r="H12" s="10" t="s">
@@ -4917,7 +5449,7 @@
       <c r="J12" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="K12" s="6">
+      <c r="K12" s="23">
         <v>1</v>
       </c>
       <c r="L12" s="10" t="s">
@@ -4944,7 +5476,7 @@
         <v>34</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>186</v>
+        <v>333</v>
       </c>
       <c r="G13" s="8"/>
       <c r="H13" s="10" t="s">
@@ -4956,7 +5488,7 @@
       <c r="J13" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="K13" s="6">
+      <c r="K13" s="23">
         <v>1</v>
       </c>
       <c r="L13" s="10" t="s">
@@ -4983,7 +5515,7 @@
         <v>34</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>186</v>
+        <v>333</v>
       </c>
       <c r="G14" s="8"/>
       <c r="H14" s="10" t="s">
@@ -4995,7 +5527,7 @@
       <c r="J14" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="K14" s="6">
+      <c r="K14" s="23">
         <v>1</v>
       </c>
       <c r="L14" s="10" t="s">
@@ -5022,7 +5554,7 @@
         <v>34</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>186</v>
+        <v>333</v>
       </c>
       <c r="G15" s="8"/>
       <c r="H15" s="10" t="s">
@@ -5034,7 +5566,7 @@
       <c r="J15" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="K15" s="6">
+      <c r="K15" s="23">
         <v>1</v>
       </c>
       <c r="L15" s="10" t="s">
@@ -5061,7 +5593,7 @@
         <v>34</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>186</v>
+        <v>333</v>
       </c>
       <c r="G16" s="8"/>
       <c r="H16" s="10" t="s">
@@ -5073,7 +5605,7 @@
       <c r="J16" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="K16" s="6">
+      <c r="K16" s="23">
         <v>1</v>
       </c>
       <c r="L16" s="10" t="s">
@@ -5100,7 +5632,7 @@
         <v>34</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>186</v>
+        <v>333</v>
       </c>
       <c r="G17" s="8"/>
       <c r="H17" s="10" t="s">
@@ -5112,7 +5644,7 @@
       <c r="J17" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="K17" s="6">
+      <c r="K17" s="23">
         <v>1</v>
       </c>
       <c r="L17" s="10" t="s">
@@ -5139,7 +5671,7 @@
         <v>34</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>186</v>
+        <v>333</v>
       </c>
       <c r="G18" s="8"/>
       <c r="H18" s="10" t="s">
@@ -5151,7 +5683,7 @@
       <c r="J18" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="K18" s="6">
+      <c r="K18" s="23">
         <v>1</v>
       </c>
       <c r="L18" s="10" t="s">
@@ -5178,7 +5710,7 @@
         <v>34</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>186</v>
+        <v>333</v>
       </c>
       <c r="G19" s="8"/>
       <c r="H19" s="10" t="s">
@@ -5190,7 +5722,7 @@
       <c r="J19" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="K19" s="6">
+      <c r="K19" s="23">
         <v>1</v>
       </c>
       <c r="L19" s="10" t="s">
@@ -5217,7 +5749,7 @@
         <v>34</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>186</v>
+        <v>333</v>
       </c>
       <c r="G20" s="8"/>
       <c r="H20" s="10" t="s">
@@ -5229,7 +5761,7 @@
       <c r="J20" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="K20" s="6">
+      <c r="K20" s="23">
         <v>1</v>
       </c>
       <c r="L20" s="10" t="s">
@@ -5256,7 +5788,7 @@
         <v>34</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>186</v>
+        <v>333</v>
       </c>
       <c r="G21" s="8"/>
       <c r="H21" s="10" t="s">
@@ -5268,7 +5800,7 @@
       <c r="J21" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="K21" s="6">
+      <c r="K21" s="23">
         <v>1</v>
       </c>
       <c r="L21" s="10" t="s">
@@ -5295,7 +5827,7 @@
         <v>34</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>186</v>
+        <v>333</v>
       </c>
       <c r="G22" s="8"/>
       <c r="H22" s="10" t="s">
@@ -5307,7 +5839,7 @@
       <c r="J22" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="K22" s="6">
+      <c r="K22" s="23">
         <v>1</v>
       </c>
       <c r="L22" s="10" t="s">
@@ -5334,7 +5866,7 @@
         <v>34</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>186</v>
+        <v>333</v>
       </c>
       <c r="G23" s="8"/>
       <c r="H23" s="10" t="s">
@@ -5346,7 +5878,7 @@
       <c r="J23" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="K23" s="6">
+      <c r="K23" s="23">
         <v>1</v>
       </c>
       <c r="L23" s="10" t="s">
@@ -5373,7 +5905,7 @@
         <v>34</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>186</v>
+        <v>333</v>
       </c>
       <c r="G24" s="8"/>
       <c r="H24" s="6" t="s">
@@ -5385,7 +5917,7 @@
       <c r="J24" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="K24" s="6">
+      <c r="K24" s="23">
         <v>1</v>
       </c>
       <c r="L24" s="10" t="s">
@@ -5412,7 +5944,7 @@
         <v>34</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>186</v>
+        <v>333</v>
       </c>
       <c r="G25" s="8"/>
       <c r="H25" s="10" t="s">
@@ -5424,7 +5956,7 @@
       <c r="J25" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="K25" s="6">
+      <c r="K25" s="23">
         <v>1</v>
       </c>
       <c r="L25" s="10" t="s">
@@ -5451,7 +5983,7 @@
         <v>34</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>186</v>
+        <v>333</v>
       </c>
       <c r="G26" s="8"/>
       <c r="H26" s="6" t="s">
@@ -5463,7 +5995,7 @@
       <c r="J26" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="K26" s="6">
+      <c r="K26" s="23">
         <v>1</v>
       </c>
       <c r="L26" s="6" t="s">
@@ -5490,7 +6022,7 @@
         <v>34</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>186</v>
+        <v>333</v>
       </c>
       <c r="G27" s="8"/>
       <c r="H27" s="10" t="s">
@@ -5502,7 +6034,7 @@
       <c r="J27" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="K27" s="6">
+      <c r="K27" s="23">
         <v>1</v>
       </c>
       <c r="L27" s="6" t="s">
@@ -5529,7 +6061,7 @@
         <v>34</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>186</v>
+        <v>333</v>
       </c>
       <c r="G28" s="8"/>
       <c r="H28" s="6" t="s">
@@ -5541,7 +6073,7 @@
       <c r="J28" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="K28" s="6">
+      <c r="K28" s="23">
         <v>1</v>
       </c>
       <c r="L28" s="10" t="s">
@@ -5568,7 +6100,7 @@
         <v>34</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>186</v>
+        <v>333</v>
       </c>
       <c r="G29" s="8"/>
       <c r="H29" s="6" t="s">
@@ -5580,7 +6112,7 @@
       <c r="J29" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="K29" s="6">
+      <c r="K29" s="23">
         <v>1</v>
       </c>
       <c r="L29" s="10" t="s">
@@ -5607,7 +6139,7 @@
         <v>34</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>186</v>
+        <v>333</v>
       </c>
       <c r="G30" s="8"/>
       <c r="H30" s="6" t="s">
@@ -5619,7 +6151,7 @@
       <c r="J30" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="K30" s="6">
+      <c r="K30" s="23">
         <v>1</v>
       </c>
       <c r="L30" s="10" t="s">
@@ -5646,7 +6178,7 @@
         <v>34</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>186</v>
+        <v>333</v>
       </c>
       <c r="G31" s="8"/>
       <c r="H31" s="6" t="s">
@@ -5658,7 +6190,7 @@
       <c r="J31" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="K31" s="6">
+      <c r="K31" s="23">
         <v>1</v>
       </c>
       <c r="L31" s="10" t="s">
@@ -5685,7 +6217,7 @@
         <v>34</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>186</v>
+        <v>333</v>
       </c>
       <c r="G32" s="8"/>
       <c r="H32" s="6" t="s">
@@ -5697,7 +6229,7 @@
       <c r="J32" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="K32" s="6">
+      <c r="K32" s="23">
         <v>1</v>
       </c>
       <c r="L32" s="10" t="s">
@@ -5724,7 +6256,7 @@
         <v>34</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>186</v>
+        <v>333</v>
       </c>
       <c r="G33" s="8"/>
       <c r="H33" s="6" t="s">
@@ -5736,7 +6268,7 @@
       <c r="J33" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="K33" s="6">
+      <c r="K33" s="23">
         <v>1</v>
       </c>
       <c r="L33" s="10" t="s">
@@ -5763,13 +6295,13 @@
         <v>34</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>186</v>
+        <v>333</v>
       </c>
       <c r="G34" s="8"/>
       <c r="H34" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="K34" s="6">
+      <c r="K34" s="23">
         <v>1</v>
       </c>
       <c r="L34" s="10" t="s">
@@ -5796,13 +6328,13 @@
         <v>34</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>186</v>
+        <v>333</v>
       </c>
       <c r="G35" s="8"/>
       <c r="H35" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="K35" s="6">
+      <c r="K35" s="23">
         <v>1</v>
       </c>
       <c r="L35" s="10" t="s">
@@ -5829,13 +6361,13 @@
         <v>34</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>186</v>
+        <v>333</v>
       </c>
       <c r="G36" s="8"/>
       <c r="H36" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="K36" s="6">
+      <c r="K36" s="23">
         <v>1</v>
       </c>
       <c r="L36" s="10" t="s">
@@ -5862,13 +6394,13 @@
         <v>34</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>186</v>
+        <v>333</v>
       </c>
       <c r="G37" s="8"/>
       <c r="H37" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="K37" s="6">
+      <c r="K37" s="23">
         <v>1</v>
       </c>
       <c r="L37" s="10" t="s">
@@ -5895,7 +6427,7 @@
         <v>34</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>186</v>
+        <v>333</v>
       </c>
       <c r="G38" s="8"/>
       <c r="H38" s="6" t="s">
@@ -5907,7 +6439,7 @@
       <c r="J38" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="K38" s="6">
+      <c r="K38" s="23">
         <v>1</v>
       </c>
       <c r="L38" s="10" t="s">
@@ -5937,7 +6469,7 @@
         <v>34</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>186</v>
+        <v>333</v>
       </c>
       <c r="G39" s="8"/>
       <c r="H39" s="6" t="s">
@@ -5949,7 +6481,7 @@
       <c r="J39" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="K39" s="6">
+      <c r="K39" s="23">
         <v>1</v>
       </c>
       <c r="L39" s="10" t="s">
@@ -5979,7 +6511,7 @@
         <v>34</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>186</v>
+        <v>333</v>
       </c>
       <c r="G40" s="8"/>
       <c r="H40" s="6" t="s">
@@ -5991,7 +6523,7 @@
       <c r="J40" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="K40" s="6">
+      <c r="K40" s="23">
         <v>1</v>
       </c>
       <c r="L40" s="10" t="s">
@@ -6021,7 +6553,7 @@
         <v>34</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>186</v>
+        <v>333</v>
       </c>
       <c r="G41" s="8"/>
       <c r="H41" s="6" t="s">
@@ -6033,7 +6565,7 @@
       <c r="J41" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="K41" s="6">
+      <c r="K41" s="23">
         <v>1</v>
       </c>
       <c r="L41" s="10" t="s">
@@ -6063,7 +6595,7 @@
         <v>34</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>186</v>
+        <v>333</v>
       </c>
       <c r="G42" s="8"/>
       <c r="H42" s="6" t="s">
@@ -6075,7 +6607,7 @@
       <c r="J42" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="K42" s="6">
+      <c r="K42" s="23">
         <v>1</v>
       </c>
       <c r="L42" s="10" t="s">
@@ -6105,7 +6637,7 @@
         <v>34</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>186</v>
+        <v>333</v>
       </c>
       <c r="G43" s="8"/>
       <c r="L43" s="10" t="s">
@@ -6135,7 +6667,7 @@
         <v>34</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>186</v>
+        <v>333</v>
       </c>
       <c r="G44" s="8"/>
       <c r="N44" s="6" t="s">
@@ -6150,35 +6682,20 @@
         <v>179</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="D45" s="21" t="s">
-        <v>197</v>
+        <v>192</v>
+      </c>
+      <c r="D45" s="19" t="s">
+        <v>286</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>198</v>
+        <v>34</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>194</v>
+        <v>333</v>
       </c>
       <c r="G45" s="8"/>
-      <c r="H45" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="I45" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="J45" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="K45" s="6">
-        <v>1</v>
-      </c>
-      <c r="L45" s="10" t="s">
-        <v>195</v>
-      </c>
-      <c r="M45" s="6" t="s">
-        <v>5</v>
+      <c r="N45" s="6" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
@@ -6189,35 +6706,20 @@
         <v>179</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="D46" s="21" t="s">
-        <v>215</v>
+        <v>192</v>
+      </c>
+      <c r="D46" s="19" t="s">
+        <v>287</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>198</v>
+        <v>34</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>194</v>
+        <v>333</v>
       </c>
       <c r="G46" s="8"/>
-      <c r="H46" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="I46" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="J46" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="K46" s="6">
-        <v>1</v>
-      </c>
-      <c r="L46" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="M46" s="6" t="s">
-        <v>217</v>
+      <c r="N46" s="6" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
@@ -6228,35 +6730,20 @@
         <v>179</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="D47" s="21" t="s">
-        <v>237</v>
+        <v>192</v>
+      </c>
+      <c r="D47" s="19" t="s">
+        <v>289</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>198</v>
+        <v>34</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>194</v>
+        <v>333</v>
       </c>
       <c r="G47" s="8"/>
-      <c r="H47" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="I47" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="J47" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="K47" s="6">
-        <v>1</v>
-      </c>
-      <c r="L47" s="10" t="s">
-        <v>258</v>
-      </c>
-      <c r="M47" s="6" t="s">
-        <v>259</v>
+      <c r="N47" s="6" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
@@ -6267,38 +6754,23 @@
         <v>179</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="D48" s="21" t="s">
-        <v>238</v>
+        <v>192</v>
+      </c>
+      <c r="D48" s="19" t="s">
+        <v>290</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>198</v>
+        <v>34</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>194</v>
+        <v>333</v>
       </c>
       <c r="G48" s="8"/>
-      <c r="H48" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="I48" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="J48" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="K48" s="6">
-        <v>1</v>
-      </c>
-      <c r="L48" s="10" t="s">
-        <v>260</v>
-      </c>
-      <c r="M48" s="6" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N48" s="6" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
         <v>201</v>
       </c>
@@ -6306,38 +6778,23 @@
         <v>179</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="D49" s="21" t="s">
-        <v>239</v>
+        <v>192</v>
+      </c>
+      <c r="D49" s="19" t="s">
+        <v>294</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>198</v>
+        <v>34</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>194</v>
+        <v>333</v>
       </c>
       <c r="G49" s="8"/>
-      <c r="H49" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="I49" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="J49" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="K49" s="6">
-        <v>1</v>
-      </c>
-      <c r="L49" s="10" t="s">
-        <v>262</v>
-      </c>
-      <c r="M49" s="6" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N49" s="6" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
         <v>202</v>
       </c>
@@ -6345,38 +6802,23 @@
         <v>179</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="D50" s="21" t="s">
-        <v>240</v>
+        <v>192</v>
+      </c>
+      <c r="D50" s="19" t="s">
+        <v>295</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>198</v>
+        <v>34</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>194</v>
+        <v>333</v>
       </c>
       <c r="G50" s="8"/>
-      <c r="H50" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="I50" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="J50" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="K50" s="6">
-        <v>1</v>
-      </c>
-      <c r="L50" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="M50" s="6" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N50" s="6" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" s="6" t="s">
         <v>203</v>
       </c>
@@ -6384,38 +6826,23 @@
         <v>179</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="D51" s="21" t="s">
-        <v>241</v>
+        <v>192</v>
+      </c>
+      <c r="D51" s="19" t="s">
+        <v>296</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>198</v>
+        <v>34</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>194</v>
+        <v>333</v>
       </c>
       <c r="G51" s="8"/>
-      <c r="H51" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="I51" s="6" t="s">
-        <v>279</v>
-      </c>
-      <c r="J51" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="K51" s="6">
-        <v>1</v>
-      </c>
-      <c r="L51" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="M51" s="6" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N51" s="6" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
         <v>204</v>
       </c>
@@ -6423,38 +6850,23 @@
         <v>179</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="D52" s="21" t="s">
-        <v>242</v>
+        <v>192</v>
+      </c>
+      <c r="D52" s="19" t="s">
+        <v>284</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>198</v>
+        <v>34</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>194</v>
+        <v>333</v>
       </c>
       <c r="G52" s="8"/>
-      <c r="H52" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="I52" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="J52" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="K52" s="6">
-        <v>1</v>
-      </c>
-      <c r="L52" s="10" t="s">
-        <v>264</v>
-      </c>
-      <c r="M52" s="6" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N52" s="6" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" s="6" t="s">
         <v>205</v>
       </c>
@@ -6462,38 +6874,23 @@
         <v>179</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="D53" s="21" t="s">
-        <v>243</v>
+        <v>192</v>
+      </c>
+      <c r="D53" s="19" t="s">
+        <v>287</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>198</v>
+        <v>34</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>194</v>
+        <v>333</v>
       </c>
       <c r="G53" s="8"/>
-      <c r="H53" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="I53" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="J53" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="K53" s="6">
-        <v>1</v>
-      </c>
-      <c r="L53" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="M53" s="6" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N53" s="6" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" s="6" t="s">
         <v>206</v>
       </c>
@@ -6501,38 +6898,23 @@
         <v>179</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="D54" s="21" t="s">
-        <v>244</v>
+        <v>192</v>
+      </c>
+      <c r="D54" s="19" t="s">
+        <v>299</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>198</v>
+        <v>34</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>194</v>
+        <v>333</v>
       </c>
       <c r="G54" s="8"/>
-      <c r="H54" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="I54" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="J54" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="K54" s="6">
-        <v>1</v>
-      </c>
-      <c r="L54" s="10" t="s">
-        <v>268</v>
-      </c>
-      <c r="M54" s="6" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N54" s="6" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
         <v>207</v>
       </c>
@@ -6540,38 +6922,23 @@
         <v>179</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="D55" s="21" t="s">
-        <v>245</v>
+        <v>192</v>
+      </c>
+      <c r="D55" s="19" t="s">
+        <v>300</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>198</v>
+        <v>34</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>194</v>
+        <v>333</v>
       </c>
       <c r="G55" s="8"/>
-      <c r="H55" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="I55" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="J55" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="K55" s="6">
-        <v>1</v>
-      </c>
-      <c r="L55" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="M55" s="6" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N55" s="6" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" s="6" t="s">
         <v>208</v>
       </c>
@@ -6579,38 +6946,23 @@
         <v>179</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="D56" s="21" t="s">
-        <v>246</v>
+        <v>192</v>
+      </c>
+      <c r="D56" s="19" t="s">
+        <v>301</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>198</v>
+        <v>34</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>194</v>
+        <v>333</v>
       </c>
       <c r="G56" s="8"/>
-      <c r="H56" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="I56" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="J56" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="K56" s="6">
-        <v>1</v>
-      </c>
-      <c r="L56" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="M56" s="6" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N56" s="6" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" s="6" t="s">
         <v>209</v>
       </c>
@@ -6618,38 +6970,23 @@
         <v>179</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="D57" s="21" t="s">
-        <v>247</v>
+        <v>192</v>
+      </c>
+      <c r="D57" s="19" t="s">
+        <v>302</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>198</v>
+        <v>34</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>194</v>
+        <v>333</v>
       </c>
       <c r="G57" s="8"/>
-      <c r="H57" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="I57" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="J57" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="K57" s="6">
-        <v>1</v>
-      </c>
-      <c r="L57" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="M57" s="6" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N57" s="6" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" s="6" t="s">
         <v>210</v>
       </c>
@@ -6657,32 +6994,23 @@
         <v>179</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="D58" s="21" t="s">
-        <v>248</v>
+        <v>192</v>
+      </c>
+      <c r="D58" s="19" t="s">
+        <v>303</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>198</v>
+        <v>34</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>194</v>
+        <v>333</v>
       </c>
       <c r="G58" s="8"/>
-      <c r="H58" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="K58" s="6">
-        <v>1</v>
-      </c>
-      <c r="L58" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="M58" s="6" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N58" s="6" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" s="6" t="s">
         <v>211</v>
       </c>
@@ -6690,27 +7018,26 @@
         <v>179</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="D59" s="21" t="s">
-        <v>249</v>
+        <v>192</v>
+      </c>
+      <c r="D59" s="19" t="s">
+        <v>297</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>198</v>
+        <v>34</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>194</v>
+        <v>333</v>
       </c>
       <c r="G59" s="8"/>
-      <c r="H59" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="K59" s="6">
-        <v>0</v>
-      </c>
-      <c r="L59" s="10"/>
-    </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O59" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="P59" s="6" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" s="6" t="s">
         <v>212</v>
       </c>
@@ -6718,32 +7045,23 @@
         <v>179</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="D60" s="21" t="s">
-        <v>250</v>
+        <v>192</v>
+      </c>
+      <c r="D60" s="19" t="s">
+        <v>298</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>198</v>
+        <v>34</v>
       </c>
       <c r="F60" s="8" t="s">
-        <v>194</v>
+        <v>333</v>
       </c>
       <c r="G60" s="8"/>
-      <c r="H60" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="K60" s="6">
-        <v>1</v>
-      </c>
-      <c r="L60" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="M60" s="6" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="Q60" s="6" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A61" s="6" t="s">
         <v>213</v>
       </c>
@@ -6751,27 +7069,19 @@
         <v>179</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="D61" s="21" t="s">
-        <v>251</v>
-      </c>
-      <c r="E61" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="F61" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="G61" s="8"/>
-      <c r="H61" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="K61" s="6">
-        <v>0</v>
-      </c>
-      <c r="L61" s="10"/>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+        <v>192</v>
+      </c>
+      <c r="D61" s="20" t="s">
+        <v>325</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F61" s="6" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A62" s="6" t="s">
         <v>214</v>
       </c>
@@ -6781,45 +7091,40 @@
       <c r="C62" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="D62" s="19" t="s">
-        <v>286</v>
-      </c>
-      <c r="E62" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F62" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="G62" s="8"/>
-      <c r="N62" s="6" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="D62" s="20" t="s">
+        <v>326</v>
+      </c>
+      <c r="E62" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A63" s="6" t="s">
         <v>277</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>179</v>
+        <v>327</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="D63" s="19" t="s">
-        <v>287</v>
-      </c>
-      <c r="E63" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F63" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="G63" s="8"/>
-      <c r="N63" s="6" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="D63" s="20" t="s">
+        <v>328</v>
+      </c>
+      <c r="E63" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F63" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="G63" s="20" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A64" s="6" t="s">
         <v>288</v>
       </c>
@@ -6829,21 +7134,17 @@
       <c r="C64" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="D64" s="19" t="s">
-        <v>289</v>
-      </c>
-      <c r="E64" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F64" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="G64" s="8"/>
-      <c r="N64" s="6" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="D64" s="20" t="s">
+        <v>330</v>
+      </c>
+      <c r="E64" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A65" s="6" t="s">
         <v>291</v>
       </c>
@@ -6851,23 +7152,38 @@
         <v>179</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="D65" s="19" t="s">
-        <v>290</v>
+        <v>193</v>
+      </c>
+      <c r="D65" s="21" t="s">
+        <v>197</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F65" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="F65" s="13" t="s">
         <v>186</v>
       </c>
       <c r="G65" s="8"/>
-      <c r="N65" s="6" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="H65" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="I65" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="J65" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="K65" s="23">
+        <v>1</v>
+      </c>
+      <c r="L65" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="M65" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A66" s="6" t="s">
         <v>292</v>
       </c>
@@ -6875,23 +7191,38 @@
         <v>179</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="D66" s="19" t="s">
-        <v>294</v>
+        <v>193</v>
+      </c>
+      <c r="D66" s="21" t="s">
+        <v>215</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>34</v>
+        <v>198</v>
       </c>
       <c r="F66" s="8" t="s">
         <v>186</v>
       </c>
       <c r="G66" s="8"/>
-      <c r="N66" s="6" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="H66" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="I66" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="J66" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="K66" s="23">
+        <v>1</v>
+      </c>
+      <c r="L66" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="M66" s="6" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A67" s="6" t="s">
         <v>293</v>
       </c>
@@ -6899,23 +7230,38 @@
         <v>179</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="D67" s="19" t="s">
-        <v>295</v>
+        <v>193</v>
+      </c>
+      <c r="D67" s="21" t="s">
+        <v>237</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>34</v>
+        <v>198</v>
       </c>
       <c r="F67" s="8" t="s">
         <v>186</v>
       </c>
       <c r="G67" s="8"/>
-      <c r="N67" s="6" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="H67" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="I67" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="J67" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="K67" s="23">
+        <v>1</v>
+      </c>
+      <c r="L67" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="M67" s="6" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A68" s="6" t="s">
         <v>304</v>
       </c>
@@ -6923,23 +7269,38 @@
         <v>179</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="D68" s="19" t="s">
-        <v>296</v>
+        <v>193</v>
+      </c>
+      <c r="D68" s="21" t="s">
+        <v>238</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>34</v>
+        <v>198</v>
       </c>
       <c r="F68" s="8" t="s">
         <v>186</v>
       </c>
       <c r="G68" s="8"/>
-      <c r="N68" s="6" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="H68" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="I68" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="J68" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="K68" s="23">
+        <v>1</v>
+      </c>
+      <c r="L68" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="M68" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A69" s="6" t="s">
         <v>305</v>
       </c>
@@ -6947,23 +7308,38 @@
         <v>179</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="D69" s="19" t="s">
-        <v>284</v>
+        <v>193</v>
+      </c>
+      <c r="D69" s="21" t="s">
+        <v>239</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>34</v>
+        <v>198</v>
       </c>
       <c r="F69" s="8" t="s">
         <v>186</v>
       </c>
       <c r="G69" s="8"/>
-      <c r="N69" s="6" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="H69" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="I69" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="J69" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="K69" s="23">
+        <v>1</v>
+      </c>
+      <c r="L69" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="M69" s="6" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A70" s="6" t="s">
         <v>306</v>
       </c>
@@ -6971,23 +7347,38 @@
         <v>179</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="D70" s="19" t="s">
-        <v>287</v>
+        <v>193</v>
+      </c>
+      <c r="D70" s="21" t="s">
+        <v>240</v>
       </c>
       <c r="E70" s="7" t="s">
-        <v>34</v>
+        <v>198</v>
       </c>
       <c r="F70" s="8" t="s">
         <v>186</v>
       </c>
       <c r="G70" s="8"/>
-      <c r="N70" s="6" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="H70" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="I70" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="J70" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="K70" s="23">
+        <v>1</v>
+      </c>
+      <c r="L70" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="M70" s="6" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A71" s="6" t="s">
         <v>307</v>
       </c>
@@ -6995,23 +7386,38 @@
         <v>179</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="D71" s="19" t="s">
-        <v>299</v>
+        <v>193</v>
+      </c>
+      <c r="D71" s="21" t="s">
+        <v>241</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>34</v>
+        <v>198</v>
       </c>
       <c r="F71" s="8" t="s">
         <v>186</v>
       </c>
       <c r="G71" s="8"/>
-      <c r="N71" s="6" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="H71" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="I71" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="J71" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="K71" s="23">
+        <v>1</v>
+      </c>
+      <c r="L71" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="M71" s="6" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A72" s="6" t="s">
         <v>308</v>
       </c>
@@ -7019,23 +7425,38 @@
         <v>179</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="D72" s="19" t="s">
-        <v>300</v>
+        <v>193</v>
+      </c>
+      <c r="D72" s="21" t="s">
+        <v>242</v>
       </c>
       <c r="E72" s="7" t="s">
-        <v>34</v>
+        <v>198</v>
       </c>
       <c r="F72" s="8" t="s">
         <v>186</v>
       </c>
       <c r="G72" s="8"/>
-      <c r="N72" s="6" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="H72" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="I72" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="J72" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="K72" s="23">
+        <v>1</v>
+      </c>
+      <c r="L72" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="M72" s="6" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A73" s="6" t="s">
         <v>309</v>
       </c>
@@ -7043,23 +7464,38 @@
         <v>179</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="D73" s="19" t="s">
-        <v>301</v>
+        <v>193</v>
+      </c>
+      <c r="D73" s="21" t="s">
+        <v>243</v>
       </c>
       <c r="E73" s="7" t="s">
-        <v>34</v>
+        <v>198</v>
       </c>
       <c r="F73" s="8" t="s">
         <v>186</v>
       </c>
       <c r="G73" s="8"/>
-      <c r="N73" s="6" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="H73" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I73" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J73" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="K73" s="23">
+        <v>1</v>
+      </c>
+      <c r="L73" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="M73" s="6" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A74" s="6" t="s">
         <v>310</v>
       </c>
@@ -7067,23 +7503,38 @@
         <v>179</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="D74" s="19" t="s">
-        <v>302</v>
+        <v>193</v>
+      </c>
+      <c r="D74" s="21" t="s">
+        <v>244</v>
       </c>
       <c r="E74" s="7" t="s">
-        <v>34</v>
+        <v>198</v>
       </c>
       <c r="F74" s="8" t="s">
         <v>186</v>
       </c>
       <c r="G74" s="8"/>
-      <c r="N74" s="6" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="H74" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="I74" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="J74" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="K74" s="23">
+        <v>1</v>
+      </c>
+      <c r="L74" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="M74" s="6" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A75" s="6" t="s">
         <v>311</v>
       </c>
@@ -7091,23 +7542,38 @@
         <v>179</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="D75" s="19" t="s">
-        <v>303</v>
+        <v>193</v>
+      </c>
+      <c r="D75" s="21" t="s">
+        <v>245</v>
       </c>
       <c r="E75" s="7" t="s">
-        <v>34</v>
+        <v>198</v>
       </c>
       <c r="F75" s="8" t="s">
         <v>186</v>
       </c>
       <c r="G75" s="8"/>
-      <c r="N75" s="6" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="H75" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="I75" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="J75" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="K75" s="23">
+        <v>1</v>
+      </c>
+      <c r="L75" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="M75" s="6" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A76" s="6" t="s">
         <v>312</v>
       </c>
@@ -7115,26 +7581,38 @@
         <v>179</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="D76" s="19" t="s">
-        <v>297</v>
+        <v>193</v>
+      </c>
+      <c r="D76" s="21" t="s">
+        <v>246</v>
       </c>
       <c r="E76" s="7" t="s">
-        <v>34</v>
+        <v>198</v>
       </c>
       <c r="F76" s="8" t="s">
         <v>186</v>
       </c>
       <c r="G76" s="8"/>
-      <c r="O76" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="P76" s="6" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="H76" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="I76" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="J76" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="K76" s="23">
+        <v>1</v>
+      </c>
+      <c r="L76" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="M76" s="6" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A77" s="6" t="s">
         <v>313</v>
       </c>
@@ -7142,23 +7620,38 @@
         <v>179</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="D77" s="19" t="s">
-        <v>298</v>
+        <v>193</v>
+      </c>
+      <c r="D77" s="21" t="s">
+        <v>247</v>
       </c>
       <c r="E77" s="7" t="s">
-        <v>34</v>
+        <v>198</v>
       </c>
       <c r="F77" s="8" t="s">
         <v>186</v>
       </c>
       <c r="G77" s="8"/>
-      <c r="Q77" s="6" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="78" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="H77" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I77" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J77" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="K77" s="23">
+        <v>1</v>
+      </c>
+      <c r="L77" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="M77" s="6" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A78" s="6" t="s">
         <v>314</v>
       </c>
@@ -7166,19 +7659,32 @@
         <v>179</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="D78" s="20" t="s">
-        <v>325</v>
-      </c>
-      <c r="E78" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F78" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="D78" s="21" t="s">
+        <v>248</v>
+      </c>
+      <c r="E78" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="F78" s="8" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="79" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G78" s="8"/>
+      <c r="H78" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="K78" s="23">
+        <v>1</v>
+      </c>
+      <c r="L78" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="M78" s="6" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A79" s="6" t="s">
         <v>331</v>
       </c>
@@ -7186,42 +7692,60 @@
         <v>179</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="D79" s="20" t="s">
-        <v>326</v>
-      </c>
-      <c r="E79" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F79" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="D79" s="21" t="s">
+        <v>249</v>
+      </c>
+      <c r="E79" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="F79" s="8" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="80" spans="1:17" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="G79" s="8"/>
+      <c r="H79" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="K79" s="23">
+        <v>0</v>
+      </c>
+      <c r="L79" s="10"/>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A80" s="6" t="s">
         <v>332</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>327</v>
+        <v>179</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="D80" s="20" t="s">
-        <v>328</v>
-      </c>
-      <c r="E80" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F80" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="D80" s="21" t="s">
+        <v>250</v>
+      </c>
+      <c r="E80" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="F80" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="G80" s="20" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G80" s="8"/>
+      <c r="H80" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="K80" s="23">
+        <v>1</v>
+      </c>
+      <c r="L80" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="M80" s="6" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" s="6" t="s">
         <v>324</v>
       </c>
@@ -7229,148 +7753,1433 @@
         <v>179</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="D81" s="20" t="s">
-        <v>330</v>
-      </c>
-      <c r="E81" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F81" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="D81" s="21" t="s">
+        <v>251</v>
+      </c>
+      <c r="E81" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="F81" s="8" t="s">
         <v>186</v>
       </c>
+      <c r="G81" s="8"/>
+      <c r="H81" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="K81" s="23">
+        <v>0</v>
+      </c>
+      <c r="L81" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" xr:uid="{9EC057FB-C5B5-44B3-99E2-1F07D282EEFA}"/>
-    <hyperlink ref="D2" r:id="rId2" xr:uid="{DF42C02A-824E-4E10-AA7B-0771CC4EE460}"/>
-    <hyperlink ref="D3" r:id="rId3" xr:uid="{2147172F-2E37-4463-BE0A-FE2081D5ED60}"/>
-    <hyperlink ref="D5" r:id="rId4" display="https://awddev.trialclient1.awdcloud.co.uk/awdServer/awd/services/v1/businessareas/CARRENTAL/types/ATCHMENT" xr:uid="{6A7C0DFB-326C-46B2-9C2F-EA8A24B9E8E1}"/>
-    <hyperlink ref="D6" r:id="rId5" display="https://awddev.trialclient1.awdcloud.co.uk/awdServer/awd/services/v1/businessareas/SAMPLEBA/types/AUTOTEST1" xr:uid="{18687945-0D4C-4B9A-A0C6-2AB5543920DD}"/>
-    <hyperlink ref="D16" r:id="rId6" display="https://awddev.trialclient1.awdcloud.co.uk/awdServer/awd/services/v1/businessareas/AI4HR/types/BGCHECK" xr:uid="{21C42D77-F702-463A-AF54-5C4CAEE1682A}"/>
-    <hyperlink ref="D17" r:id="rId7" display="https://awddev.trialclient1.awdcloud.co.uk/awdServer/awd/services/v1/businessareas/AI4HR/types/BNKSTMNT" xr:uid="{42606AB6-D4FF-4116-A465-4617B1BE2C14}"/>
-    <hyperlink ref="D18" r:id="rId8" display="https://awddev.trialclient1.awdcloud.co.uk/awdServer/awd/services/v1/businessareas/AI4HR/types/CAPHIRE" xr:uid="{3B4E8E9B-8EEA-45D9-8B71-3A2DF2170CBF}"/>
-    <hyperlink ref="D19" r:id="rId9" display="https://awddev.trialclient1.awdcloud.co.uk/awdServer/awd/services/v1/businessareas/CARRENTAL/types/CARBOOKING" xr:uid="{665F9F84-02D6-4A88-AD5E-0AC10487298C}"/>
-    <hyperlink ref="D20" r:id="rId10" display="https://awddev.trialclient1.awdcloud.co.uk/awdServer/awd/services/v1/businessareas/COLLECTION/types/CHEQUE" xr:uid="{A16D2730-A512-4296-8A66-A62CCBCD432D}"/>
-    <hyperlink ref="D21" r:id="rId11" display="https://awddev.trialclient1.awdcloud.co.uk/awdServer/awd/services/v1/businessareas/LIFEPEN/types/CLIENT" xr:uid="{758A978F-6D1F-4A6E-9F15-B3B7C3FEB74F}"/>
-    <hyperlink ref="D22" r:id="rId12" display="https://awddev.trialclient1.awdcloud.co.uk/awdServer/awd/services/v1/businessareas/COLLECTION/types/CMADDCHG" xr:uid="{8954C273-6DF1-4E1A-AEDB-1620DE146415}"/>
-    <hyperlink ref="D23" r:id="rId13" display="https://awddev.trialclient1.awdcloud.co.uk/awdServer/awd/services/v1/user/queues" xr:uid="{8A81631B-E69F-44E5-B42C-3947C99340FC}"/>
-    <hyperlink ref="D24" r:id="rId14" display="https://awddev.trialclient1.awdcloud.co.uk/awdServer/awd/services/v1/user/states" xr:uid="{FEA117A0-8EF1-48BA-BB51-8078B3B1A10D}"/>
-    <hyperlink ref="D25" r:id="rId15" display="https://awddev.trialclient1.awdcloud.co.uk/awdServer/awd/services/v1/user/types/categorycodes" xr:uid="{D263760F-4180-42B8-87B3-EFAC20CCC7A0}"/>
-    <hyperlink ref="D26" r:id="rId16" display="https://awddev.trialclient1.awdcloud.co.uk/awdServer/awd/services/v1/user/businessareas/clientcodes" xr:uid="{138EC656-A29D-40DE-8CAF-0C3CABAEEA72}"/>
-    <hyperlink ref="D27" r:id="rId17" display="https://awddev.trialclient1.awdcloud.co.uk/awdServer/awd/services/v1/users/workgroups" xr:uid="{815B0348-EB78-453A-9F97-131086DFBD1E}"/>
-    <hyperlink ref="D28" r:id="rId18" display="https://awddev.trialclient1.awdcloud.co.uk/awdServer/awd/services/v1/fields" xr:uid="{42CA46F5-C0C9-4178-AD2D-0D442FE32DC0}"/>
-    <hyperlink ref="D29" r:id="rId19" display="https://awddev.trialclient1.awdcloud.co.uk/awdServer/awd/services/v1/user/instances" xr:uid="{B0843220-CD18-4426-87FA-31420FF87D84}"/>
-    <hyperlink ref="D30" r:id="rId20" display="https://awddev.trialclient1.awdcloud.co.uk/awdServer/awd/services/v1/users" xr:uid="{E425B4B1-BA30-4FE2-B126-B52DF6488AD3}"/>
-    <hyperlink ref="D31" r:id="rId21" display="https://awddev.trialclient1.awdcloud.co.uk/awdServer/awd/services/v1/user/workspace" xr:uid="{77D117E2-521B-422E-B4C1-FA7D8E8A4CC9}"/>
-    <hyperlink ref="D32" r:id="rId22" display="https://awddev.trialclient1.awdcloud.co.uk/awdServer/awd/services/v1/user/workspaces" xr:uid="{8816B477-8B38-4F11-8FBC-39C2245CFBC7}"/>
-    <hyperlink ref="D33" r:id="rId23" display="https://awddev.trialclient1.awdcloud.co.uk/awdServer/awd/services/v1/user/instances/assigned" xr:uid="{F7662E8A-1516-4C66-A316-0B3AF5D6B37B}"/>
-    <hyperlink ref="D34" r:id="rId24" display="https://awddev.trialclient1.awdcloud.co.uk/awdServer/awd/services/v1/user/instances/workselected" xr:uid="{7ED01241-FB35-416C-B27E-FB8E66A5CFA7}"/>
-    <hyperlink ref="D35" r:id="rId25" display="https://awddev.trialclient1.awdcloud.co.uk/awdServer/awd/services/v1/cm/users" xr:uid="{4230F204-D9B9-48B9-A96C-745BB9EAA263}"/>
-    <hyperlink ref="D36" r:id="rId26" display="https://awddev.trialclient1.awdcloud.co.uk/awdServer/awd/services/v1/cm/tasks/forecast" xr:uid="{074D32E4-39A3-4B64-BA1B-3295977EB9C2}"/>
-    <hyperlink ref="D37" r:id="rId27" display="https://awddev.trialclient1.awdcloud.co.uk/awdServer/awd/services/v1/cm/teams" xr:uid="{C133A2D9-509B-41E5-AC67-1BC4CD890AAD}"/>
-    <hyperlink ref="D39" r:id="rId28" display="http://localhost/awdServer/awd/services/v1/instances/2025-09-02-10.55.47.298540T01/history" xr:uid="{0CF1AB16-15F6-4960-8720-CD948296B07D}"/>
-    <hyperlink ref="D40" r:id="rId29" display="http://localhost/awdServer/awd/services/v1/instances/2025-09-02-10.55.47.298540T01/actions" xr:uid="{A4F35F75-A9A7-4017-BC5D-AE35755F376B}"/>
-    <hyperlink ref="D41" r:id="rId30" display="http://localhost/awdServer/awd/services/v1/instances/2025-09-02-10.55.47.298540T01/actions/menus" xr:uid="{60E582BC-268A-4114-9E5B-BCF261996F1F}"/>
-    <hyperlink ref="D42" r:id="rId31" display="http://localhost/awdServer/awd/services/v1/instances/2025-09-02-10.55.47.298540T01/presentationflow/instance" xr:uid="{E09D17CE-6719-428A-AB19-854BB9CAF7A2}"/>
-    <hyperlink ref="D43" r:id="rId32" display="http://localhost/awdServer/awd/services/v1/user/instances/2025-09-11-10.29.46.491160T01/locked" xr:uid="{7230F8D9-A9BF-4DC4-876F-452FF95DA3AE}"/>
-    <hyperlink ref="D44" r:id="rId33" display="http://localhost/awdServer/awd/services/v1/user/instances/2025-09-11-10.29.46.491160T01/locked" xr:uid="{C15A1B25-D1F1-4FB9-A47B-E55A7562295D}"/>
-    <hyperlink ref="F3" r:id="rId34" xr:uid="{9683E518-651F-472E-8EFD-82A0EC251A82}"/>
-    <hyperlink ref="F4" r:id="rId35" xr:uid="{6952F459-A2C3-4B84-858F-4D9DFB89C993}"/>
-    <hyperlink ref="F5" r:id="rId36" xr:uid="{6B3FC817-1520-4E6D-AD5A-593011DA1FFF}"/>
-    <hyperlink ref="F6" r:id="rId37" xr:uid="{1CA96936-9E7A-4250-9162-A18347B862AC}"/>
-    <hyperlink ref="F7" r:id="rId38" xr:uid="{A302CBEA-B4C5-41D4-B764-A9160DC7D76B}"/>
-    <hyperlink ref="F8" r:id="rId39" xr:uid="{6705C2B8-4A82-40A9-8D45-41775E7EF419}"/>
-    <hyperlink ref="F9" r:id="rId40" xr:uid="{11A240C8-DC73-49FD-843C-2AAC372699C7}"/>
-    <hyperlink ref="F10" r:id="rId41" xr:uid="{B6C43CEB-E556-4E84-81A6-669E07A0F1BD}"/>
-    <hyperlink ref="F11" r:id="rId42" xr:uid="{92F0C668-F138-40CC-8968-D23ED80C3414}"/>
-    <hyperlink ref="F12" r:id="rId43" xr:uid="{7C80706E-9FCF-438B-A6B2-C8164871843A}"/>
-    <hyperlink ref="F13" r:id="rId44" xr:uid="{7906E3BB-CA98-49B8-9FEA-15AF1D75821A}"/>
-    <hyperlink ref="F14" r:id="rId45" xr:uid="{6A41207C-E3DE-494C-BA7B-98BF93E7B01A}"/>
-    <hyperlink ref="F15" r:id="rId46" xr:uid="{33873B4A-93E9-4E44-A98F-84885CBFAB74}"/>
-    <hyperlink ref="F16" r:id="rId47" xr:uid="{715479B6-0DB2-4334-8D80-AFAD9851B315}"/>
-    <hyperlink ref="F17" r:id="rId48" xr:uid="{A45D1273-4E72-4EB7-82BD-08B87EA2A67B}"/>
-    <hyperlink ref="F18" r:id="rId49" xr:uid="{B89E684C-33FC-4A9F-9411-C506619DB115}"/>
-    <hyperlink ref="F19" r:id="rId50" xr:uid="{FC96CEDB-A461-4426-B97A-FEDE2BA40F1D}"/>
-    <hyperlink ref="F20" r:id="rId51" xr:uid="{2CAEC558-9E09-47D7-8375-6F087FF189F2}"/>
-    <hyperlink ref="F21" r:id="rId52" xr:uid="{7D8716E5-E830-4FA0-A7E0-7F5A3D424D0B}"/>
-    <hyperlink ref="F22" r:id="rId53" xr:uid="{21E09B81-7243-419A-A2D4-1E1855280D2E}"/>
-    <hyperlink ref="F23" r:id="rId54" xr:uid="{0A76A49B-F7ED-4AF8-946E-A0E3F99E0E1E}"/>
-    <hyperlink ref="F24" r:id="rId55" xr:uid="{8E25C8E1-2122-480B-81D1-6782A34A28FD}"/>
-    <hyperlink ref="F25" r:id="rId56" xr:uid="{EE52A10D-6F05-4E54-AAA6-910348963FCF}"/>
-    <hyperlink ref="F26" r:id="rId57" xr:uid="{A590F463-7B01-4721-A07D-85B92E5D52DB}"/>
-    <hyperlink ref="F27" r:id="rId58" xr:uid="{8C30351D-C77A-4D15-9770-1B7455F50974}"/>
-    <hyperlink ref="F28" r:id="rId59" xr:uid="{82802EDB-D168-47B5-898D-494EFE55168F}"/>
-    <hyperlink ref="F29" r:id="rId60" xr:uid="{7748FCA0-4DC0-438B-A77C-E40942B0633B}"/>
-    <hyperlink ref="F30" r:id="rId61" xr:uid="{8AAAC512-8B1C-4F33-B2DF-4D3249E3D15C}"/>
-    <hyperlink ref="F31" r:id="rId62" xr:uid="{05480B5C-DC31-4E8A-A53B-51F17FF020BA}"/>
-    <hyperlink ref="F32" r:id="rId63" xr:uid="{103A691C-2C8B-427B-BC5E-E6925B9D8D86}"/>
-    <hyperlink ref="F33" r:id="rId64" xr:uid="{437F3B03-53EB-4D7D-81F8-9D3E416FC99C}"/>
-    <hyperlink ref="F34" r:id="rId65" xr:uid="{69E772EA-BE8E-431E-9F81-DDF21B8C6B70}"/>
-    <hyperlink ref="F35" r:id="rId66" xr:uid="{4BB88EE4-41D8-4598-8DE3-35DAD8B6B68C}"/>
-    <hyperlink ref="F36" r:id="rId67" xr:uid="{BEABBF4F-1B51-4879-BA90-D4397F496C41}"/>
-    <hyperlink ref="F37" r:id="rId68" xr:uid="{3046850A-9999-4574-8E76-9575A8FD9B61}"/>
-    <hyperlink ref="F38" r:id="rId69" xr:uid="{62D2280B-D5C5-433A-9AEA-C49D425CBA12}"/>
-    <hyperlink ref="F39" r:id="rId70" xr:uid="{D7664AD4-C959-4D5C-BF1F-1BDC3433F1A0}"/>
-    <hyperlink ref="F40" r:id="rId71" xr:uid="{8AFC3042-B79D-4570-A547-A03DAF8999AA}"/>
-    <hyperlink ref="F41" r:id="rId72" xr:uid="{2B14BF73-E995-4833-8FD6-79379768FA69}"/>
-    <hyperlink ref="F42" r:id="rId73" xr:uid="{8C0D4D4E-61D4-43F0-9A9D-96B5B531B4B2}"/>
-    <hyperlink ref="F43" r:id="rId74" xr:uid="{5CE7C8D2-AAF8-4E81-BFA8-AEB44448D35A}"/>
-    <hyperlink ref="F44" r:id="rId75" xr:uid="{F60BA2E1-DD5B-40C8-8728-236666E98373}"/>
-    <hyperlink ref="F45" r:id="rId76" xr:uid="{865FFE70-7B7A-4E59-9C85-74F4B748E47F}"/>
-    <hyperlink ref="D45" r:id="rId77" xr:uid="{E047679F-7320-44C9-AD70-9750DB88531B}"/>
-    <hyperlink ref="F46" r:id="rId78" xr:uid="{8E84351C-A5A0-4ED8-9A13-0C6CC8A73B13}"/>
-    <hyperlink ref="D46" r:id="rId79" xr:uid="{1D5A44DA-A292-4263-97F6-2462FF56EDE5}"/>
-    <hyperlink ref="D47" r:id="rId80" xr:uid="{B5ED2BFD-5B45-4D41-851D-AD0B6E9F074B}"/>
-    <hyperlink ref="D48" r:id="rId81" xr:uid="{87FD801E-1FC1-4D1B-91EF-1DC799CBB043}"/>
-    <hyperlink ref="D49" r:id="rId82" xr:uid="{B1D49CC6-1662-47F1-A33F-E8C43B17B572}"/>
-    <hyperlink ref="D50" r:id="rId83" xr:uid="{BB924419-B422-4845-A584-D271AB469397}"/>
-    <hyperlink ref="D51" r:id="rId84" display="https://awddev.trialclient1.awdcloud.co.uk/awdServer/awd/services/v1/users/workgroups" xr:uid="{79D00392-6B26-4D30-84A2-C5831D8E5A2F}"/>
-    <hyperlink ref="D52" r:id="rId85" xr:uid="{E6ABB07C-DDD9-4D26-8137-F45B3304F126}"/>
-    <hyperlink ref="D53" r:id="rId86" xr:uid="{C1FD76DD-75BE-4018-BEEA-3B53D933B101}"/>
-    <hyperlink ref="D54" r:id="rId87" xr:uid="{914F5D16-3B86-475C-85B5-A38C1E75F9E9}"/>
-    <hyperlink ref="D55" r:id="rId88" xr:uid="{3D002A29-26C2-46E2-BF9A-C505B5F4E805}"/>
-    <hyperlink ref="D56" r:id="rId89" display="https://awddev.trialclient1.awdcloud.co.uk/awdServer/awd/services/v1/user/workspaces" xr:uid="{52DC01A8-99BC-428E-ABD9-47246B0BE4AA}"/>
-    <hyperlink ref="D57" r:id="rId90" xr:uid="{26B68C88-DBF3-4AF7-8A48-54D1024B6765}"/>
-    <hyperlink ref="D58" r:id="rId91" xr:uid="{C39F9C32-4839-476A-BCEE-482C15C78774}"/>
-    <hyperlink ref="D59" r:id="rId92" xr:uid="{9E7CE5B2-F6F2-400B-9C07-FD1E791EBD77}"/>
-    <hyperlink ref="D60" r:id="rId93" xr:uid="{8036E621-2426-4D7A-A6AB-5AF9C1BE761B}"/>
-    <hyperlink ref="D61" r:id="rId94" xr:uid="{5DF38B53-0CA5-42DA-A575-7F4F6C3B9DF1}"/>
-    <hyperlink ref="F47" r:id="rId95" xr:uid="{5DB5AC0C-71D1-4C45-9562-443D15A4C45B}"/>
-    <hyperlink ref="F48" r:id="rId96" xr:uid="{6E7A917C-E45A-4305-8343-7E0BD492CF0B}"/>
-    <hyperlink ref="F49" r:id="rId97" xr:uid="{9563EB9F-115D-4F1B-9BE8-0C31C8A195B7}"/>
-    <hyperlink ref="F50" r:id="rId98" xr:uid="{D43673A4-CB74-496B-BE79-A275B653D1DE}"/>
-    <hyperlink ref="F51" r:id="rId99" xr:uid="{37AF8A9C-9B32-40FD-8EA3-2BEB8ED407AA}"/>
-    <hyperlink ref="F52" r:id="rId100" xr:uid="{3C2D6F45-4634-42D5-B8BE-C43A64817B26}"/>
-    <hyperlink ref="F53" r:id="rId101" xr:uid="{82CFA9DB-BEC4-4A2D-A69D-EE76258BF9F4}"/>
-    <hyperlink ref="F54" r:id="rId102" xr:uid="{314E59C9-A17B-43C5-8AF8-AF25839FF825}"/>
-    <hyperlink ref="F55" r:id="rId103" xr:uid="{05C0634E-5A19-4C79-AAB0-9086CA1B1086}"/>
-    <hyperlink ref="F56" r:id="rId104" xr:uid="{3821458C-C98D-40C5-A51F-209CB9B9C722}"/>
-    <hyperlink ref="F57" r:id="rId105" xr:uid="{39BFA95A-E7A5-433A-8B01-65B4A018563E}"/>
-    <hyperlink ref="F58" r:id="rId106" xr:uid="{0ACE6B04-F2F4-4D45-A4CE-9EE66530EBE2}"/>
-    <hyperlink ref="F59" r:id="rId107" xr:uid="{DE39C578-DAC3-4DDC-927F-6EC731500051}"/>
-    <hyperlink ref="F60" r:id="rId108" xr:uid="{2793E287-F126-4E4B-BDC9-9719C72246F9}"/>
-    <hyperlink ref="F61" r:id="rId109" xr:uid="{D77712B7-CF6E-435A-88B0-16D01E8BE58B}"/>
-    <hyperlink ref="D38" r:id="rId110" display="http://localhost/awdServer/awd/services/v1/instances/2025-09-02-10.55.47.298540T01/quality" xr:uid="{90498AF2-91FB-4EE4-A121-890C20F09735}"/>
-    <hyperlink ref="D62" r:id="rId111" xr:uid="{415E6C4F-6AFA-409A-A077-12D1AC7B8566}"/>
-    <hyperlink ref="F62" r:id="rId112" xr:uid="{DD02ADE6-CFF6-4B51-8E8F-7E4724B43A95}"/>
-    <hyperlink ref="F76" r:id="rId113" xr:uid="{80C552D8-F772-4147-AA3B-85BFE549DB0C}"/>
-    <hyperlink ref="D76" r:id="rId114" xr:uid="{270ADC3D-4ED5-45CD-ABBB-A57946D4FE6C}"/>
-    <hyperlink ref="D77" r:id="rId115" xr:uid="{957C581E-1CB4-4B83-9E1A-0B437CE62D6C}"/>
-    <hyperlink ref="F77" r:id="rId116" xr:uid="{88449496-BD05-4EEA-A541-47D6D193EBAD}"/>
-    <hyperlink ref="D72" r:id="rId117" xr:uid="{08DF8184-107D-48D7-AE2F-EB207468EEB8}"/>
-    <hyperlink ref="D73" r:id="rId118" xr:uid="{04D1A2E5-DE82-4A38-9790-FB9987A522FB}"/>
-    <hyperlink ref="D74" r:id="rId119" xr:uid="{FD272625-5E18-475A-A6F1-860B24570060}"/>
-    <hyperlink ref="D75" r:id="rId120" xr:uid="{369BCF9A-FEA0-47B2-B236-428EFAD0646E}"/>
-    <hyperlink ref="F72" r:id="rId121" xr:uid="{5AF08A32-5A08-4305-A59E-950D100B64A0}"/>
-    <hyperlink ref="F73" r:id="rId122" xr:uid="{71A4E974-AFEB-41B7-8662-9FCF3C37A6E9}"/>
-    <hyperlink ref="F74" r:id="rId123" xr:uid="{A2E209E2-0A14-437E-90BF-8A35B255954E}"/>
-    <hyperlink ref="F75" r:id="rId124" xr:uid="{280D1C2C-2C64-4631-94CB-4C9A63A22A3B}"/>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{DF42C02A-824E-4E10-AA7B-0771CC4EE460}"/>
+    <hyperlink ref="D3" r:id="rId2" xr:uid="{2147172F-2E37-4463-BE0A-FE2081D5ED60}"/>
+    <hyperlink ref="D5" r:id="rId3" display="https://awddev.trialclient1.awdcloud.co.uk/awdServer/awd/services/v1/businessareas/CARRENTAL/types/ATCHMENT" xr:uid="{6A7C0DFB-326C-46B2-9C2F-EA8A24B9E8E1}"/>
+    <hyperlink ref="D6" r:id="rId4" display="https://awddev.trialclient1.awdcloud.co.uk/awdServer/awd/services/v1/businessareas/SAMPLEBA/types/AUTOTEST1" xr:uid="{18687945-0D4C-4B9A-A0C6-2AB5543920DD}"/>
+    <hyperlink ref="D16" r:id="rId5" display="https://awddev.trialclient1.awdcloud.co.uk/awdServer/awd/services/v1/businessareas/AI4HR/types/BGCHECK" xr:uid="{21C42D77-F702-463A-AF54-5C4CAEE1682A}"/>
+    <hyperlink ref="D17" r:id="rId6" display="https://awddev.trialclient1.awdcloud.co.uk/awdServer/awd/services/v1/businessareas/AI4HR/types/BNKSTMNT" xr:uid="{42606AB6-D4FF-4116-A465-4617B1BE2C14}"/>
+    <hyperlink ref="D18" r:id="rId7" display="https://awddev.trialclient1.awdcloud.co.uk/awdServer/awd/services/v1/businessareas/AI4HR/types/CAPHIRE" xr:uid="{3B4E8E9B-8EEA-45D9-8B71-3A2DF2170CBF}"/>
+    <hyperlink ref="D19" r:id="rId8" display="https://awddev.trialclient1.awdcloud.co.uk/awdServer/awd/services/v1/businessareas/CARRENTAL/types/CARBOOKING" xr:uid="{665F9F84-02D6-4A88-AD5E-0AC10487298C}"/>
+    <hyperlink ref="D20" r:id="rId9" display="https://awddev.trialclient1.awdcloud.co.uk/awdServer/awd/services/v1/businessareas/COLLECTION/types/CHEQUE" xr:uid="{A16D2730-A512-4296-8A66-A62CCBCD432D}"/>
+    <hyperlink ref="D21" r:id="rId10" display="https://awddev.trialclient1.awdcloud.co.uk/awdServer/awd/services/v1/businessareas/LIFEPEN/types/CLIENT" xr:uid="{758A978F-6D1F-4A6E-9F15-B3B7C3FEB74F}"/>
+    <hyperlink ref="D22" r:id="rId11" display="https://awddev.trialclient1.awdcloud.co.uk/awdServer/awd/services/v1/businessareas/COLLECTION/types/CMADDCHG" xr:uid="{8954C273-6DF1-4E1A-AEDB-1620DE146415}"/>
+    <hyperlink ref="D23" r:id="rId12" display="https://awddev.trialclient1.awdcloud.co.uk/awdServer/awd/services/v1/user/queues" xr:uid="{8A81631B-E69F-44E5-B42C-3947C99340FC}"/>
+    <hyperlink ref="D24" r:id="rId13" display="https://awddev.trialclient1.awdcloud.co.uk/awdServer/awd/services/v1/user/states" xr:uid="{FEA117A0-8EF1-48BA-BB51-8078B3B1A10D}"/>
+    <hyperlink ref="D25" r:id="rId14" display="https://awddev.trialclient1.awdcloud.co.uk/awdServer/awd/services/v1/user/types/categorycodes" xr:uid="{D263760F-4180-42B8-87B3-EFAC20CCC7A0}"/>
+    <hyperlink ref="D26" r:id="rId15" display="https://awddev.trialclient1.awdcloud.co.uk/awdServer/awd/services/v1/user/businessareas/clientcodes" xr:uid="{138EC656-A29D-40DE-8CAF-0C3CABAEEA72}"/>
+    <hyperlink ref="D27" r:id="rId16" display="https://awddev.trialclient1.awdcloud.co.uk/awdServer/awd/services/v1/users/workgroups" xr:uid="{815B0348-EB78-453A-9F97-131086DFBD1E}"/>
+    <hyperlink ref="D28" r:id="rId17" display="https://awddev.trialclient1.awdcloud.co.uk/awdServer/awd/services/v1/fields" xr:uid="{42CA46F5-C0C9-4178-AD2D-0D442FE32DC0}"/>
+    <hyperlink ref="D29" r:id="rId18" display="https://awddev.trialclient1.awdcloud.co.uk/awdServer/awd/services/v1/user/instances" xr:uid="{B0843220-CD18-4426-87FA-31420FF87D84}"/>
+    <hyperlink ref="D30" r:id="rId19" display="https://awddev.trialclient1.awdcloud.co.uk/awdServer/awd/services/v1/users" xr:uid="{E425B4B1-BA30-4FE2-B126-B52DF6488AD3}"/>
+    <hyperlink ref="D31" r:id="rId20" display="https://awddev.trialclient1.awdcloud.co.uk/awdServer/awd/services/v1/user/workspace" xr:uid="{77D117E2-521B-422E-B4C1-FA7D8E8A4CC9}"/>
+    <hyperlink ref="D32" r:id="rId21" display="https://awddev.trialclient1.awdcloud.co.uk/awdServer/awd/services/v1/user/workspaces" xr:uid="{8816B477-8B38-4F11-8FBC-39C2245CFBC7}"/>
+    <hyperlink ref="D33" r:id="rId22" display="https://awddev.trialclient1.awdcloud.co.uk/awdServer/awd/services/v1/user/instances/assigned" xr:uid="{F7662E8A-1516-4C66-A316-0B3AF5D6B37B}"/>
+    <hyperlink ref="D34" r:id="rId23" display="https://awddev.trialclient1.awdcloud.co.uk/awdServer/awd/services/v1/user/instances/workselected" xr:uid="{7ED01241-FB35-416C-B27E-FB8E66A5CFA7}"/>
+    <hyperlink ref="D35" r:id="rId24" display="https://awddev.trialclient1.awdcloud.co.uk/awdServer/awd/services/v1/cm/users" xr:uid="{4230F204-D9B9-48B9-A96C-745BB9EAA263}"/>
+    <hyperlink ref="D36" r:id="rId25" display="https://awddev.trialclient1.awdcloud.co.uk/awdServer/awd/services/v1/cm/tasks/forecast" xr:uid="{074D32E4-39A3-4B64-BA1B-3295977EB9C2}"/>
+    <hyperlink ref="D37" r:id="rId26" display="https://awddev.trialclient1.awdcloud.co.uk/awdServer/awd/services/v1/cm/teams" xr:uid="{C133A2D9-509B-41E5-AC67-1BC4CD890AAD}"/>
+    <hyperlink ref="D39" r:id="rId27" display="http://localhost/awdServer/awd/services/v1/instances/2025-09-02-10.55.47.298540T01/history" xr:uid="{0CF1AB16-15F6-4960-8720-CD948296B07D}"/>
+    <hyperlink ref="D40" r:id="rId28" display="http://localhost/awdServer/awd/services/v1/instances/2025-09-02-10.55.47.298540T01/actions" xr:uid="{A4F35F75-A9A7-4017-BC5D-AE35755F376B}"/>
+    <hyperlink ref="D41" r:id="rId29" display="http://localhost/awdServer/awd/services/v1/instances/2025-09-02-10.55.47.298540T01/actions/menus" xr:uid="{60E582BC-268A-4114-9E5B-BCF261996F1F}"/>
+    <hyperlink ref="D42" r:id="rId30" display="http://localhost/awdServer/awd/services/v1/instances/2025-09-02-10.55.47.298540T01/presentationflow/instance" xr:uid="{E09D17CE-6719-428A-AB19-854BB9CAF7A2}"/>
+    <hyperlink ref="D43" r:id="rId31" display="http://localhost/awdServer/awd/services/v1/user/instances/2025-09-11-10.29.46.491160T01/locked" xr:uid="{7230F8D9-A9BF-4DC4-876F-452FF95DA3AE}"/>
+    <hyperlink ref="D44" r:id="rId32" display="http://localhost/awdServer/awd/services/v1/user/instances/2025-09-11-10.29.46.491160T01/locked" xr:uid="{C15A1B25-D1F1-4FB9-A47B-E55A7562295D}"/>
+    <hyperlink ref="F3" r:id="rId33" display="Ai4P@ssword3" xr:uid="{9683E518-651F-472E-8EFD-82A0EC251A82}"/>
+    <hyperlink ref="F4" r:id="rId34" display="Ai4P@ssword3" xr:uid="{6952F459-A2C3-4B84-858F-4D9DFB89C993}"/>
+    <hyperlink ref="F5" r:id="rId35" display="Ai4P@ssword3" xr:uid="{6B3FC817-1520-4E6D-AD5A-593011DA1FFF}"/>
+    <hyperlink ref="F6" r:id="rId36" display="Ai4P@ssword3" xr:uid="{1CA96936-9E7A-4250-9162-A18347B862AC}"/>
+    <hyperlink ref="F7" r:id="rId37" display="Ai4P@ssword3" xr:uid="{A302CBEA-B4C5-41D4-B764-A9160DC7D76B}"/>
+    <hyperlink ref="F8" r:id="rId38" display="Ai4P@ssword3" xr:uid="{6705C2B8-4A82-40A9-8D45-41775E7EF419}"/>
+    <hyperlink ref="F9" r:id="rId39" display="Ai4P@ssword3" xr:uid="{11A240C8-DC73-49FD-843C-2AAC372699C7}"/>
+    <hyperlink ref="F10" r:id="rId40" display="Ai4P@ssword3" xr:uid="{B6C43CEB-E556-4E84-81A6-669E07A0F1BD}"/>
+    <hyperlink ref="F11" r:id="rId41" display="Ai4P@ssword3" xr:uid="{92F0C668-F138-40CC-8968-D23ED80C3414}"/>
+    <hyperlink ref="F12" r:id="rId42" display="Ai4P@ssword3" xr:uid="{7C80706E-9FCF-438B-A6B2-C8164871843A}"/>
+    <hyperlink ref="F13" r:id="rId43" display="Ai4P@ssword3" xr:uid="{7906E3BB-CA98-49B8-9FEA-15AF1D75821A}"/>
+    <hyperlink ref="F14" r:id="rId44" display="Ai4P@ssword3" xr:uid="{6A41207C-E3DE-494C-BA7B-98BF93E7B01A}"/>
+    <hyperlink ref="F15" r:id="rId45" display="Ai4P@ssword3" xr:uid="{33873B4A-93E9-4E44-A98F-84885CBFAB74}"/>
+    <hyperlink ref="F16" r:id="rId46" display="Ai4P@ssword3" xr:uid="{715479B6-0DB2-4334-8D80-AFAD9851B315}"/>
+    <hyperlink ref="F17" r:id="rId47" display="Ai4P@ssword3" xr:uid="{A45D1273-4E72-4EB7-82BD-08B87EA2A67B}"/>
+    <hyperlink ref="F18" r:id="rId48" display="Ai4P@ssword3" xr:uid="{B89E684C-33FC-4A9F-9411-C506619DB115}"/>
+    <hyperlink ref="F19" r:id="rId49" display="Ai4P@ssword3" xr:uid="{FC96CEDB-A461-4426-B97A-FEDE2BA40F1D}"/>
+    <hyperlink ref="F20" r:id="rId50" display="Ai4P@ssword3" xr:uid="{2CAEC558-9E09-47D7-8375-6F087FF189F2}"/>
+    <hyperlink ref="F21" r:id="rId51" display="Ai4P@ssword3" xr:uid="{7D8716E5-E830-4FA0-A7E0-7F5A3D424D0B}"/>
+    <hyperlink ref="F22" r:id="rId52" display="Ai4P@ssword3" xr:uid="{21E09B81-7243-419A-A2D4-1E1855280D2E}"/>
+    <hyperlink ref="F23" r:id="rId53" display="Ai4P@ssword3" xr:uid="{0A76A49B-F7ED-4AF8-946E-A0E3F99E0E1E}"/>
+    <hyperlink ref="F24" r:id="rId54" display="Ai4P@ssword3" xr:uid="{8E25C8E1-2122-480B-81D1-6782A34A28FD}"/>
+    <hyperlink ref="F25" r:id="rId55" display="Ai4P@ssword3" xr:uid="{EE52A10D-6F05-4E54-AAA6-910348963FCF}"/>
+    <hyperlink ref="F26" r:id="rId56" display="Ai4P@ssword3" xr:uid="{A590F463-7B01-4721-A07D-85B92E5D52DB}"/>
+    <hyperlink ref="F27" r:id="rId57" display="Ai4P@ssword3" xr:uid="{8C30351D-C77A-4D15-9770-1B7455F50974}"/>
+    <hyperlink ref="F28" r:id="rId58" display="Ai4P@ssword3" xr:uid="{82802EDB-D168-47B5-898D-494EFE55168F}"/>
+    <hyperlink ref="F29" r:id="rId59" display="Ai4P@ssword3" xr:uid="{7748FCA0-4DC0-438B-A77C-E40942B0633B}"/>
+    <hyperlink ref="F30" r:id="rId60" display="Ai4P@ssword3" xr:uid="{8AAAC512-8B1C-4F33-B2DF-4D3249E3D15C}"/>
+    <hyperlink ref="F31" r:id="rId61" display="Ai4P@ssword3" xr:uid="{05480B5C-DC31-4E8A-A53B-51F17FF020BA}"/>
+    <hyperlink ref="F32" r:id="rId62" display="Ai4P@ssword3" xr:uid="{103A691C-2C8B-427B-BC5E-E6925B9D8D86}"/>
+    <hyperlink ref="F33" r:id="rId63" display="Ai4P@ssword3" xr:uid="{437F3B03-53EB-4D7D-81F8-9D3E416FC99C}"/>
+    <hyperlink ref="F34" r:id="rId64" display="Ai4P@ssword3" xr:uid="{69E772EA-BE8E-431E-9F81-DDF21B8C6B70}"/>
+    <hyperlink ref="F35" r:id="rId65" display="Ai4P@ssword3" xr:uid="{4BB88EE4-41D8-4598-8DE3-35DAD8B6B68C}"/>
+    <hyperlink ref="F36" r:id="rId66" display="Ai4P@ssword3" xr:uid="{BEABBF4F-1B51-4879-BA90-D4397F496C41}"/>
+    <hyperlink ref="F37" r:id="rId67" display="Ai4P@ssword3" xr:uid="{3046850A-9999-4574-8E76-9575A8FD9B61}"/>
+    <hyperlink ref="F38" r:id="rId68" display="Ai4P@ssword3" xr:uid="{62D2280B-D5C5-433A-9AEA-C49D425CBA12}"/>
+    <hyperlink ref="F39" r:id="rId69" display="Ai4P@ssword3" xr:uid="{D7664AD4-C959-4D5C-BF1F-1BDC3433F1A0}"/>
+    <hyperlink ref="F40" r:id="rId70" display="Ai4P@ssword3" xr:uid="{8AFC3042-B79D-4570-A547-A03DAF8999AA}"/>
+    <hyperlink ref="F41" r:id="rId71" display="Ai4P@ssword3" xr:uid="{2B14BF73-E995-4833-8FD6-79379768FA69}"/>
+    <hyperlink ref="F42" r:id="rId72" display="Ai4P@ssword3" xr:uid="{8C0D4D4E-61D4-43F0-9A9D-96B5B531B4B2}"/>
+    <hyperlink ref="F43" r:id="rId73" display="Ai4P@ssword3" xr:uid="{5CE7C8D2-AAF8-4E81-BFA8-AEB44448D35A}"/>
+    <hyperlink ref="F44" r:id="rId74" display="Ai4P@ssword3" xr:uid="{F60BA2E1-DD5B-40C8-8728-236666E98373}"/>
+    <hyperlink ref="F65" r:id="rId75" display="Ai4P@ssword2" xr:uid="{865FFE70-7B7A-4E59-9C85-74F4B748E47F}"/>
+    <hyperlink ref="D65" r:id="rId76" xr:uid="{E047679F-7320-44C9-AD70-9750DB88531B}"/>
+    <hyperlink ref="F66" r:id="rId77" display="Ai4P@ssword2" xr:uid="{8E84351C-A5A0-4ED8-9A13-0C6CC8A73B13}"/>
+    <hyperlink ref="D66" r:id="rId78" xr:uid="{1D5A44DA-A292-4263-97F6-2462FF56EDE5}"/>
+    <hyperlink ref="D67" r:id="rId79" xr:uid="{B5ED2BFD-5B45-4D41-851D-AD0B6E9F074B}"/>
+    <hyperlink ref="D68" r:id="rId80" xr:uid="{87FD801E-1FC1-4D1B-91EF-1DC799CBB043}"/>
+    <hyperlink ref="D69" r:id="rId81" xr:uid="{B1D49CC6-1662-47F1-A33F-E8C43B17B572}"/>
+    <hyperlink ref="D70" r:id="rId82" xr:uid="{BB924419-B422-4845-A584-D271AB469397}"/>
+    <hyperlink ref="D71" r:id="rId83" display="https://awddev.trialclient1.awdcloud.co.uk/awdServer/awd/services/v1/users/workgroups" xr:uid="{79D00392-6B26-4D30-84A2-C5831D8E5A2F}"/>
+    <hyperlink ref="D72" r:id="rId84" xr:uid="{E6ABB07C-DDD9-4D26-8137-F45B3304F126}"/>
+    <hyperlink ref="D73" r:id="rId85" xr:uid="{C1FD76DD-75BE-4018-BEEA-3B53D933B101}"/>
+    <hyperlink ref="D74" r:id="rId86" xr:uid="{914F5D16-3B86-475C-85B5-A38C1E75F9E9}"/>
+    <hyperlink ref="D75" r:id="rId87" xr:uid="{3D002A29-26C2-46E2-BF9A-C505B5F4E805}"/>
+    <hyperlink ref="D76" r:id="rId88" display="https://awddev.trialclient1.awdcloud.co.uk/awdServer/awd/services/v1/user/workspaces" xr:uid="{52DC01A8-99BC-428E-ABD9-47246B0BE4AA}"/>
+    <hyperlink ref="D77" r:id="rId89" xr:uid="{26B68C88-DBF3-4AF7-8A48-54D1024B6765}"/>
+    <hyperlink ref="D78" r:id="rId90" xr:uid="{C39F9C32-4839-476A-BCEE-482C15C78774}"/>
+    <hyperlink ref="D79" r:id="rId91" xr:uid="{9E7CE5B2-F6F2-400B-9C07-FD1E791EBD77}"/>
+    <hyperlink ref="D80" r:id="rId92" xr:uid="{8036E621-2426-4D7A-A6AB-5AF9C1BE761B}"/>
+    <hyperlink ref="D81" r:id="rId93" xr:uid="{5DF38B53-0CA5-42DA-A575-7F4F6C3B9DF1}"/>
+    <hyperlink ref="F67" r:id="rId94" display="Ai4P@ssword2" xr:uid="{5DB5AC0C-71D1-4C45-9562-443D15A4C45B}"/>
+    <hyperlink ref="F68" r:id="rId95" display="Ai4P@ssword2" xr:uid="{6E7A917C-E45A-4305-8343-7E0BD492CF0B}"/>
+    <hyperlink ref="F69" r:id="rId96" display="Ai4P@ssword2" xr:uid="{9563EB9F-115D-4F1B-9BE8-0C31C8A195B7}"/>
+    <hyperlink ref="F70" r:id="rId97" display="Ai4P@ssword2" xr:uid="{D43673A4-CB74-496B-BE79-A275B653D1DE}"/>
+    <hyperlink ref="F71" r:id="rId98" display="Ai4P@ssword2" xr:uid="{37AF8A9C-9B32-40FD-8EA3-2BEB8ED407AA}"/>
+    <hyperlink ref="F72" r:id="rId99" display="Ai4P@ssword2" xr:uid="{3C2D6F45-4634-42D5-B8BE-C43A64817B26}"/>
+    <hyperlink ref="F73" r:id="rId100" display="Ai4P@ssword2" xr:uid="{82CFA9DB-BEC4-4A2D-A69D-EE76258BF9F4}"/>
+    <hyperlink ref="F74" r:id="rId101" display="Ai4P@ssword2" xr:uid="{314E59C9-A17B-43C5-8AF8-AF25839FF825}"/>
+    <hyperlink ref="F75" r:id="rId102" display="Ai4P@ssword2" xr:uid="{05C0634E-5A19-4C79-AAB0-9086CA1B1086}"/>
+    <hyperlink ref="F76" r:id="rId103" display="Ai4P@ssword2" xr:uid="{3821458C-C98D-40C5-A51F-209CB9B9C722}"/>
+    <hyperlink ref="F77" r:id="rId104" display="Ai4P@ssword2" xr:uid="{39BFA95A-E7A5-433A-8B01-65B4A018563E}"/>
+    <hyperlink ref="F78" r:id="rId105" display="Ai4P@ssword2" xr:uid="{0ACE6B04-F2F4-4D45-A4CE-9EE66530EBE2}"/>
+    <hyperlink ref="F79" r:id="rId106" display="Ai4P@ssword2" xr:uid="{DE39C578-DAC3-4DDC-927F-6EC731500051}"/>
+    <hyperlink ref="F80" r:id="rId107" display="Ai4P@ssword2" xr:uid="{2793E287-F126-4E4B-BDC9-9719C72246F9}"/>
+    <hyperlink ref="F81" r:id="rId108" display="Ai4P@ssword2" xr:uid="{D77712B7-CF6E-435A-88B0-16D01E8BE58B}"/>
+    <hyperlink ref="D38" r:id="rId109" display="http://localhost/awdServer/awd/services/v1/instances/2025-09-02-10.55.47.298540T01/quality" xr:uid="{90498AF2-91FB-4EE4-A121-890C20F09735}"/>
+    <hyperlink ref="D45" r:id="rId110" xr:uid="{415E6C4F-6AFA-409A-A077-12D1AC7B8566}"/>
+    <hyperlink ref="F45" r:id="rId111" display="Ai4P@ssword3" xr:uid="{DD02ADE6-CFF6-4B51-8E8F-7E4724B43A95}"/>
+    <hyperlink ref="F59" r:id="rId112" display="Ai4P@ssword3" xr:uid="{80C552D8-F772-4147-AA3B-85BFE549DB0C}"/>
+    <hyperlink ref="D59" r:id="rId113" xr:uid="{270ADC3D-4ED5-45CD-ABBB-A57946D4FE6C}"/>
+    <hyperlink ref="D60" r:id="rId114" xr:uid="{957C581E-1CB4-4B83-9E1A-0B437CE62D6C}"/>
+    <hyperlink ref="F60" r:id="rId115" display="Ai4P@ssword3" xr:uid="{88449496-BD05-4EEA-A541-47D6D193EBAD}"/>
+    <hyperlink ref="D55" r:id="rId116" xr:uid="{08DF8184-107D-48D7-AE2F-EB207468EEB8}"/>
+    <hyperlink ref="D56" r:id="rId117" xr:uid="{04D1A2E5-DE82-4A38-9790-FB9987A522FB}"/>
+    <hyperlink ref="D57" r:id="rId118" xr:uid="{FD272625-5E18-475A-A6F1-860B24570060}"/>
+    <hyperlink ref="D58" r:id="rId119" xr:uid="{369BCF9A-FEA0-47B2-B236-428EFAD0646E}"/>
+    <hyperlink ref="F55" r:id="rId120" display="Ai4P@ssword3" xr:uid="{5AF08A32-5A08-4305-A59E-950D100B64A0}"/>
+    <hyperlink ref="F56" r:id="rId121" display="Ai4P@ssword3" xr:uid="{71A4E974-AFEB-41B7-8662-9FCF3C37A6E9}"/>
+    <hyperlink ref="F57" r:id="rId122" display="Ai4P@ssword3" xr:uid="{A2E209E2-0A14-437E-90BF-8A35B255954E}"/>
+    <hyperlink ref="F58" r:id="rId123" display="Ai4P@ssword3" xr:uid="{280D1C2C-2C64-4631-94CB-4C9A63A22A3B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId125"/>
-  <legacyDrawing r:id="rId126"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId124"/>
+  <legacyDrawing r:id="rId125"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6EB2110-1CA2-484F-8F7E-8283FD1B5DEB}">
+  <dimension ref="A1:S72"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.77734375" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.21875" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="102.44140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.5546875" style="6" customWidth="1"/>
+    <col min="7" max="8" width="13.88671875" style="6" customWidth="1"/>
+    <col min="9" max="9" width="34.44140625" style="20" customWidth="1"/>
+    <col min="10" max="10" width="21.21875" style="6" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="11.5546875" style="6" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="12.33203125" style="6" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="11.77734375" style="23" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="25.5546875" style="6" customWidth="1"/>
+    <col min="15" max="15" width="30.5546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="28.109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.77734375" style="6" customWidth="1"/>
+    <col min="18" max="18" width="11.21875" style="6" customWidth="1"/>
+    <col min="19" max="19" width="10.109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="8.88671875" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>345</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="F1" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="17" t="s">
+        <v>396</v>
+      </c>
+      <c r="I1" s="17" t="s">
+        <v>178</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="M1" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="S1" s="4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" ht="259.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>346</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>339</v>
+      </c>
+      <c r="F2" s="7"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="24" t="s">
+        <v>420</v>
+      </c>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="N2" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="72" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>340</v>
+      </c>
+      <c r="F3" s="7"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="24" t="s">
+        <v>421</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>422</v>
+      </c>
+      <c r="O3" s="6" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>343</v>
+      </c>
+      <c r="F4" s="7"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="24" t="s">
+        <v>424</v>
+      </c>
+      <c r="J4" s="10"/>
+      <c r="N4" s="10" t="s">
+        <v>412</v>
+      </c>
+      <c r="O4" s="6" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="72" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>344</v>
+      </c>
+      <c r="F5" s="7"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="24" t="s">
+        <v>425</v>
+      </c>
+      <c r="J5" s="10"/>
+      <c r="N5" t="s">
+        <v>405</v>
+      </c>
+      <c r="O5" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>357</v>
+      </c>
+      <c r="F6" s="7"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="24" t="s">
+        <v>427</v>
+      </c>
+      <c r="J6" s="10"/>
+      <c r="N6" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="O6" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="72" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>359</v>
+      </c>
+      <c r="F7" s="7"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="24" t="s">
+        <v>428</v>
+      </c>
+      <c r="J7" s="10"/>
+      <c r="N7" t="s">
+        <v>407</v>
+      </c>
+      <c r="O7" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>366</v>
+      </c>
+      <c r="F8" s="7"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="24" t="s">
+        <v>403</v>
+      </c>
+      <c r="J8" s="10"/>
+      <c r="N8" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="O8" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="216" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>368</v>
+      </c>
+      <c r="F9" s="7"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="24" t="s">
+        <v>419</v>
+      </c>
+      <c r="J9" s="10"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="10"/>
+    </row>
+    <row r="10" spans="1:19" ht="72" x14ac:dyDescent="0.3">
+      <c r="A10" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>370</v>
+      </c>
+      <c r="F10" s="7"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="24" t="s">
+        <v>416</v>
+      </c>
+      <c r="J10" s="10"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="10"/>
+    </row>
+    <row r="11" spans="1:19" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="F11" s="7"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="24" t="s">
+        <v>376</v>
+      </c>
+      <c r="J11" s="10"/>
+      <c r="N11" s="10"/>
+      <c r="O11" s="10"/>
+    </row>
+    <row r="12" spans="1:19" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>378</v>
+      </c>
+      <c r="F12" s="7"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="24" t="s">
+        <v>379</v>
+      </c>
+      <c r="J12" s="10"/>
+      <c r="N12" s="10"/>
+      <c r="O12" s="10"/>
+    </row>
+    <row r="13" spans="1:19" ht="374.4" x14ac:dyDescent="0.3">
+      <c r="A13" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>385</v>
+      </c>
+      <c r="F13" s="7"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="24" t="s">
+        <v>417</v>
+      </c>
+      <c r="J13" s="10"/>
+      <c r="N13" s="10"/>
+      <c r="O13" s="10"/>
+    </row>
+    <row r="14" spans="1:19" ht="273.60000000000002" x14ac:dyDescent="0.3">
+      <c r="A14" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>387</v>
+      </c>
+      <c r="F14" s="7"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="24" t="s">
+        <v>418</v>
+      </c>
+      <c r="J14" s="10"/>
+      <c r="N14" s="10"/>
+      <c r="O14" s="10"/>
+    </row>
+    <row r="15" spans="1:19" ht="72" x14ac:dyDescent="0.3">
+      <c r="A15" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>389</v>
+      </c>
+      <c r="F15" s="7"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="24" t="s">
+        <v>404</v>
+      </c>
+      <c r="N15" s="10"/>
+      <c r="O15" s="10"/>
+    </row>
+    <row r="16" spans="1:19" ht="216" x14ac:dyDescent="0.3">
+      <c r="A16" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="E16" s="19" t="s">
+        <v>391</v>
+      </c>
+      <c r="F16" s="7"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="24" t="s">
+        <v>392</v>
+      </c>
+      <c r="J16" s="10"/>
+      <c r="N16" s="10"/>
+      <c r="O16" s="10"/>
+    </row>
+    <row r="17" spans="1:14" ht="216" x14ac:dyDescent="0.3">
+      <c r="A17" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>394</v>
+      </c>
+      <c r="F17" s="7"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="24" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A18" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>400</v>
+      </c>
+      <c r="F18" s="7"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="24" t="s">
+        <v>423</v>
+      </c>
+      <c r="J18" s="10"/>
+    </row>
+    <row r="19" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>401</v>
+      </c>
+      <c r="F19" s="7"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="24" t="s">
+        <v>402</v>
+      </c>
+      <c r="N19" s="10"/>
+    </row>
+    <row r="20" spans="1:14" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>353</v>
+      </c>
+      <c r="F20" s="7"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="24" t="s">
+        <v>426</v>
+      </c>
+      <c r="N20" s="10"/>
+    </row>
+    <row r="21" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A21" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="E21" s="19" t="s">
+        <v>355</v>
+      </c>
+      <c r="F21" s="7"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="24" t="s">
+        <v>342</v>
+      </c>
+      <c r="N21" s="10"/>
+    </row>
+    <row r="22" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+      <c r="A22" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="E22" s="19" t="s">
+        <v>361</v>
+      </c>
+      <c r="F22" s="7"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="24" t="s">
+        <v>362</v>
+      </c>
+      <c r="N22" s="10"/>
+    </row>
+    <row r="23" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A23" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="E23" s="19" t="s">
+        <v>364</v>
+      </c>
+      <c r="F23" s="7"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="24" t="s">
+        <v>342</v>
+      </c>
+      <c r="N23" s="10"/>
+    </row>
+    <row r="24" spans="1:14" ht="244.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="E24" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="F24" s="7"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="24" t="s">
+        <v>373</v>
+      </c>
+      <c r="N24" s="10"/>
+    </row>
+    <row r="25" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A25" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="E25" s="19" t="s">
+        <v>381</v>
+      </c>
+      <c r="F25" s="7"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="24" t="s">
+        <v>342</v>
+      </c>
+      <c r="N25" s="10"/>
+    </row>
+    <row r="26" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A26" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="E26" s="19" t="s">
+        <v>383</v>
+      </c>
+      <c r="F26" s="7"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="24" t="s">
+        <v>342</v>
+      </c>
+      <c r="N26" s="10"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A27" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E27" s="21"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="24"/>
+      <c r="N27" s="10"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A28" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E28" s="21"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="24"/>
+      <c r="N28" s="10"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A29" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E29" s="19"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="24"/>
+      <c r="N29" s="10"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A30" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="E30" s="19"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="24"/>
+      <c r="N30" s="10"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A31" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="E31" s="19"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="8"/>
+      <c r="I31" s="24"/>
+      <c r="N31" s="10"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A32" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="E32" s="19"/>
+      <c r="F32" s="7"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="8"/>
+      <c r="I32" s="24"/>
+      <c r="N32" s="10"/>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A33" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E33" s="19"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8"/>
+      <c r="I33" s="24"/>
+      <c r="N33" s="10"/>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A34" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E34" s="19"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="24"/>
+      <c r="N34" s="10"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A35" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="E35" s="19"/>
+      <c r="F35" s="7"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="8"/>
+      <c r="I35" s="24"/>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A36" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="E36" s="21"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="13"/>
+      <c r="H36" s="13"/>
+      <c r="I36" s="24"/>
+      <c r="J36" s="10"/>
+      <c r="K36" s="10"/>
+      <c r="N36" s="10"/>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A37" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="E37" s="21"/>
+      <c r="F37" s="7"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="8"/>
+      <c r="I37" s="24"/>
+      <c r="J37" s="10"/>
+      <c r="K37" s="10"/>
+      <c r="N37" s="10"/>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A38" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="E38" s="21"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="8"/>
+      <c r="H38" s="8"/>
+      <c r="I38" s="24"/>
+      <c r="J38" s="10"/>
+      <c r="N38" s="10"/>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A39" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="E39" s="21"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="8"/>
+      <c r="H39" s="8"/>
+      <c r="I39" s="24"/>
+      <c r="N39" s="10"/>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A40" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="E40" s="21"/>
+      <c r="F40" s="7"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="8"/>
+      <c r="I40" s="24"/>
+      <c r="J40" s="10"/>
+      <c r="N40" s="10"/>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A41" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="E41" s="21"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="8"/>
+      <c r="H41" s="8"/>
+      <c r="I41" s="24"/>
+      <c r="N41" s="10"/>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A42" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="E42" s="21"/>
+      <c r="F42" s="7"/>
+      <c r="G42" s="8"/>
+      <c r="H42" s="8"/>
+      <c r="I42" s="24"/>
+      <c r="J42" s="10"/>
+      <c r="N42" s="10"/>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A43" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="E43" s="21"/>
+      <c r="F43" s="7"/>
+      <c r="G43" s="8"/>
+      <c r="H43" s="8"/>
+      <c r="I43" s="24"/>
+      <c r="N43" s="10"/>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A44" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="E44" s="21"/>
+      <c r="F44" s="7"/>
+      <c r="G44" s="8"/>
+      <c r="H44" s="8"/>
+      <c r="I44" s="24"/>
+      <c r="N44" s="10"/>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A45" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="E45" s="21"/>
+      <c r="F45" s="7"/>
+      <c r="G45" s="8"/>
+      <c r="H45" s="8"/>
+      <c r="I45" s="24"/>
+      <c r="N45" s="10"/>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A46" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="E46" s="21"/>
+      <c r="F46" s="7"/>
+      <c r="G46" s="8"/>
+      <c r="H46" s="8"/>
+      <c r="I46" s="24"/>
+      <c r="N46" s="10"/>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A47" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="E47" s="21"/>
+      <c r="F47" s="7"/>
+      <c r="G47" s="8"/>
+      <c r="H47" s="8"/>
+      <c r="I47" s="24"/>
+      <c r="N47" s="10"/>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A48" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="E48" s="21"/>
+      <c r="F48" s="7"/>
+      <c r="G48" s="8"/>
+      <c r="H48" s="8"/>
+      <c r="I48" s="24"/>
+      <c r="N48" s="10"/>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A49" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="E49" s="21"/>
+      <c r="F49" s="7"/>
+      <c r="G49" s="8"/>
+      <c r="H49" s="8"/>
+      <c r="I49" s="24"/>
+      <c r="N49" s="10"/>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A50" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="E50" s="21"/>
+      <c r="F50" s="7"/>
+      <c r="G50" s="8"/>
+      <c r="H50" s="8"/>
+      <c r="I50" s="24"/>
+      <c r="N50" s="10"/>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A51" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="E51" s="21"/>
+      <c r="F51" s="7"/>
+      <c r="G51" s="8"/>
+      <c r="H51" s="8"/>
+      <c r="I51" s="24"/>
+      <c r="N51" s="10"/>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A52" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="E52" s="21"/>
+      <c r="F52" s="7"/>
+      <c r="G52" s="8"/>
+      <c r="H52" s="8"/>
+      <c r="I52" s="24"/>
+      <c r="N52" s="10"/>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A53" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="E53" s="19"/>
+      <c r="F53" s="7"/>
+      <c r="G53" s="8"/>
+      <c r="H53" s="8"/>
+      <c r="I53" s="24"/>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A54" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="E54" s="19"/>
+      <c r="F54" s="7"/>
+      <c r="G54" s="8"/>
+      <c r="H54" s="8"/>
+      <c r="I54" s="24"/>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A55" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="E55" s="19"/>
+      <c r="F55" s="7"/>
+      <c r="G55" s="8"/>
+      <c r="H55" s="8"/>
+      <c r="I55" s="24"/>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A56" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="E56" s="19"/>
+      <c r="F56" s="7"/>
+      <c r="G56" s="8"/>
+      <c r="H56" s="8"/>
+      <c r="I56" s="24"/>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A57" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="E57" s="19"/>
+      <c r="F57" s="7"/>
+      <c r="G57" s="8"/>
+      <c r="H57" s="8"/>
+      <c r="I57" s="24"/>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A58" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="E58" s="19"/>
+      <c r="F58" s="7"/>
+      <c r="G58" s="8"/>
+      <c r="H58" s="8"/>
+      <c r="I58" s="24"/>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A59" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="E59" s="19"/>
+      <c r="F59" s="7"/>
+      <c r="G59" s="8"/>
+      <c r="H59" s="8"/>
+      <c r="I59" s="24"/>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A60" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="E60" s="19"/>
+      <c r="F60" s="7"/>
+      <c r="G60" s="8"/>
+      <c r="H60" s="8"/>
+      <c r="I60" s="24"/>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A61" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="E61" s="19"/>
+      <c r="F61" s="7"/>
+      <c r="G61" s="8"/>
+      <c r="H61" s="8"/>
+      <c r="I61" s="24"/>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A62" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="E62" s="19"/>
+      <c r="F62" s="7"/>
+      <c r="G62" s="8"/>
+      <c r="H62" s="8"/>
+      <c r="I62" s="24"/>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A63" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="E63" s="19"/>
+      <c r="F63" s="7"/>
+      <c r="G63" s="8"/>
+      <c r="H63" s="8"/>
+      <c r="I63" s="24"/>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A64" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="E64" s="19"/>
+      <c r="F64" s="7"/>
+      <c r="G64" s="8"/>
+      <c r="H64" s="8"/>
+      <c r="I64" s="24"/>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A65" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="E65" s="19"/>
+      <c r="F65" s="7"/>
+      <c r="G65" s="8"/>
+      <c r="H65" s="8"/>
+      <c r="I65" s="24"/>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A66" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="E66" s="19"/>
+      <c r="F66" s="7"/>
+      <c r="G66" s="8"/>
+      <c r="H66" s="8"/>
+      <c r="I66" s="24"/>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A67" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="E67" s="19"/>
+      <c r="F67" s="7"/>
+      <c r="G67" s="8"/>
+      <c r="H67" s="8"/>
+      <c r="I67" s="24"/>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A68" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="E68" s="19"/>
+      <c r="F68" s="7"/>
+      <c r="G68" s="8"/>
+      <c r="H68" s="8"/>
+      <c r="I68" s="24"/>
+      <c r="S68" s="6" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A69" s="6" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A70" s="6" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A71" s="6" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A72" s="6" t="s">
+        <v>307</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:S72" xr:uid="{E6EB2110-1CA2-484F-8F7E-8283FD1B5DEB}"/>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" xr:uid="{5ECDF837-1EDA-467A-A547-373FC5F2475D}"/>
+    <hyperlink ref="E18" r:id="rId2" xr:uid="{FD58767E-31F1-464D-A872-ADC83F505F1B}"/>
+    <hyperlink ref="E19" r:id="rId3" display="https://loyalty-qa.app.fielo.com/dx/api/application/v2/objects/STE6TG95YWx0eV9fU3RvcmVfNjg5ZGUzMTdmNjgxNGYwMGE2ODkyMjFj/actions/DeleteObject" xr:uid="{1E0ECA56-7548-4CEF-AF39-1BF0E4859675}"/>
+    <hyperlink ref="E4" r:id="rId4" xr:uid="{38D8AF0D-9175-4DC5-837E-89E11A211D9F}"/>
+    <hyperlink ref="E20" r:id="rId5" xr:uid="{900DBFDA-8F0B-431F-9C71-9087D6317F39}"/>
+    <hyperlink ref="E21" r:id="rId6" xr:uid="{00CF059F-AFEA-48D9-BDFE-3A422119000B}"/>
+    <hyperlink ref="E6" r:id="rId7" xr:uid="{AEE19489-A0EB-4220-98D7-24F8ED48D31F}"/>
+    <hyperlink ref="E7" r:id="rId8" xr:uid="{C343DB94-06D0-4C84-8C05-FBB0524AE8A5}"/>
+    <hyperlink ref="E22" r:id="rId9" xr:uid="{37A3F89A-96B3-402E-ABC7-67D6E7E4010B}"/>
+    <hyperlink ref="E23" r:id="rId10" xr:uid="{4FE53B88-9CED-4601-B570-DEC4C53C523B}"/>
+    <hyperlink ref="E8" r:id="rId11" xr:uid="{2D1AA7C3-7BF9-4351-AF90-8EF27FCF742A}"/>
+    <hyperlink ref="E9" r:id="rId12" xr:uid="{0B698410-EB1B-4575-AD2F-E8C91ABFA35F}"/>
+    <hyperlink ref="E10" r:id="rId13" xr:uid="{CD3E0902-8EC2-4FF0-B69E-BC5FEEB0D05C}"/>
+    <hyperlink ref="E24" r:id="rId14" xr:uid="{FEA314B7-E508-48E0-88C6-B366BC9A3864}"/>
+    <hyperlink ref="E11" r:id="rId15" xr:uid="{29914A7A-FC14-4925-9B0E-28AD9863F13D}"/>
+    <hyperlink ref="E12" r:id="rId16" xr:uid="{BC295E0D-DF39-4C33-93DC-61D8E59AB476}"/>
+    <hyperlink ref="E25" r:id="rId17" xr:uid="{70F6F2EF-D75D-4436-A765-FD0E1976C8EA}"/>
+    <hyperlink ref="E26" r:id="rId18" xr:uid="{19A6AD31-17CC-486A-81F6-AA23A74CEC82}"/>
+    <hyperlink ref="E13" r:id="rId19" xr:uid="{A7735A53-5C05-4FDA-8AB6-BDAAF80C61D3}"/>
+    <hyperlink ref="E14" r:id="rId20" xr:uid="{516FC244-F94D-47C3-A179-2EC1A1A53E16}"/>
+    <hyperlink ref="E15" r:id="rId21" xr:uid="{172DDC1F-7CAA-4A1A-B6C7-D770F5C31918}"/>
+    <hyperlink ref="E16" r:id="rId22" xr:uid="{9F2FE0CA-36E4-40C6-BA98-1E41C69AE037}"/>
+    <hyperlink ref="E17" r:id="rId23" xr:uid="{135C3925-D504-4FEA-82C6-426A153FDE16}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId24"/>
+  <legacyDrawing r:id="rId25"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B77525C4-6DDF-4233-9B32-99C21BD925A4}">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="32.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>415</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/test-data/sscData.xlsx
+++ b/test-data/sscData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Chorus Portal Automation_Work\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39ACA5F5-BC86-4EAB-9977-239209F584BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA93298E-F759-47D9-8A19-10C629AA0856}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1506,8 +1506,8 @@
   "objectTypeID": "Store",
   "content": {
     "Origin": "API",
-    "StoreCode": "NW-RJ465",
-    "Name": "Store NW-RJ465",
+    "StoreCode": "NW-RJ466",
+    "Name": "Store NW-RJ466",
     "Description": "Store6 Description",
     "Address": 
       {
@@ -1524,15 +1524,15 @@
   <si>
     <t>{
   "dataViewParameters": {
-    "StoreCode": "NW-RJ465"
+    "StoreCode": "NW-RJ466"
   }
 }</t>
   </si>
   <si>
-    <t>"Store NW-RJ465"</t>
-  </si>
-  <si>
-    <t>{"content":{"Description":"Store4 Description","Name":"Store NW-RJ465","StoreCode":"NW-RJ465","Address":{"Street":"Street1","City":"City1","StateProvince":"State1","PostalCode":"12345","Country":"BRAZIL"},"IsParticipating":true},"pageInstructions":[]}</t>
+    <t>"Store NW-RJ466"</t>
+  </si>
+  <si>
+    <t>{"content":{"Description":"Store4 Description","Name":"Store NW-RJ466","StoreCode":"NW-RJ466","Address":{"Street":"Street1","City":"City1","StateProvince":"State1","PostalCode":"12345","Country":"BRAZIL"},"IsParticipating":true},"pageInstructions":[]}</t>
   </si>
   <si>
     <t>{
@@ -1541,7 +1541,7 @@
     "Origin": "API",
     "Name":"Nuggets",
     "Description":"Nuggets",
-    "ProductCode": "19525",
+    "ProductCode": "19526",
     "Brand": "Burger King",
     "Category": "Snack",
     "Incentivizable":true
@@ -1551,7 +1551,7 @@
   <si>
     <t>{
   "dataViewParameters": {
-    "ProductCode": "19525"
+    "ProductCode": "19526"
   }
 }</t>
   </si>
@@ -1560,7 +1560,7 @@
     "content": {
         "Name": "Product",
         "Description": "UpdatedDescription",
-        "ProductCode": "19525",
+        "ProductCode": "19526",
         "Brand": "Brand",
         "Category": "Category",
         "Incentivizable": true
@@ -1574,7 +1574,7 @@
   "content": {
     "Origin": "API",
     "Name": "BK Apparel",
-    "ExternalID": "45673",
+    "ExternalID": "45674",
     "RewardType": "stock_control",
     "RewardExpiration": "2025-09-06T04:00:00.000Z",
     "RewardCost": "",
@@ -1585,7 +1585,7 @@
   <si>
     <t>{
   "dataViewParameters": {
-    "ExternalID": "45673"
+    "ExternalID": "45674"
   }
 }</t>
   </si>

--- a/test-data/sscData.xlsx
+++ b/test-data/sscData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Chorus Portal Automation_Work\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA93298E-F759-47D9-8A19-10C629AA0856}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D284E30-093A-47F3-A1FB-9D59885BFA60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/test-data/sscData.xlsx
+++ b/test-data/sscData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Chorus Portal Automation_Work\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D284E30-093A-47F3-A1FB-9D59885BFA60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7A527EE-113D-4795-9965-F3D99353F338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="QA" sheetId="1" r:id="rId1"/>
@@ -1112,9 +1112,6 @@
     <t>TestCase89</t>
   </si>
   <si>
-    <t>Ai4P@ssword4</t>
-  </si>
-  <si>
     <t>AI4HR</t>
   </si>
   <si>
@@ -1256,37 +1253,6 @@
   </si>
   <si>
     <t>https://loyalty-qa.app.fielo.com/dx/api/application/v2/objects?object=Sale</t>
-  </si>
-  <si>
-    <t>{
-  "objectTypeID": "SaleCase",
-  "content": {
-    "Origin": "API",
-    "ExternalID": "3aassdsadsad55aa921945595279542051",
-    "SaleChannelCode": "TT01",
-    "PointOfSaleID": "10",
-    "SaleItems": [
-      {
-        "ProductCode": "19529",
-        "Quantity": 1,
-        "TotalAmount":10
-      },
-      {
-        "ProductCode": "19527",
-        "Quantity": 1,
-        "TotalAmount":10
-      },
-      {
-        "ProductCode": "19856",
-        "Quantity": 1,
-        "TotalAmount":10
-      }
-    ],
-    "SaleDateTime": "2025-07-01T10:56:27.066Z",
-    "MemberExternalID": "99691eb263-3573-4be4-90b5-abe027d7b4ec",
-    "StoreCode": "NW-RJ567"
-  }
-}</t>
   </si>
   <si>
     <t>Create Segment</t>
@@ -1506,8 +1472,8 @@
   "objectTypeID": "Store",
   "content": {
     "Origin": "API",
-    "StoreCode": "NW-RJ466",
-    "Name": "Store NW-RJ466",
+    "StoreCode": "NW-RJ470",
+    "Name": "Store NW-RJ470",
     "Description": "Store6 Description",
     "Address": 
       {
@@ -1524,15 +1490,15 @@
   <si>
     <t>{
   "dataViewParameters": {
-    "StoreCode": "NW-RJ466"
+    "StoreCode": "NW-RJ470"
   }
 }</t>
   </si>
   <si>
-    <t>"Store NW-RJ466"</t>
-  </si>
-  <si>
-    <t>{"content":{"Description":"Store4 Description","Name":"Store NW-RJ466","StoreCode":"NW-RJ466","Address":{"Street":"Street1","City":"City1","StateProvince":"State1","PostalCode":"12345","Country":"BRAZIL"},"IsParticipating":true},"pageInstructions":[]}</t>
+    <t>"Store NW-RJ470"</t>
+  </si>
+  <si>
+    <t>{"content":{"Description":"Store4 Description","Name":"Store NW-RJ470","StoreCode":"NW-RJ470","Address":{"Street":"Street1","City":"City1","StateProvince":"State1","PostalCode":"12345","Country":"BRAZIL"},"IsParticipating":true},"pageInstructions":[]}</t>
   </si>
   <si>
     <t>{
@@ -1541,7 +1507,7 @@
     "Origin": "API",
     "Name":"Nuggets",
     "Description":"Nuggets",
-    "ProductCode": "19526",
+    "ProductCode": "19530",
     "Brand": "Burger King",
     "Category": "Snack",
     "Incentivizable":true
@@ -1551,7 +1517,38 @@
   <si>
     <t>{
   "dataViewParameters": {
-    "ProductCode": "19526"
+    "ProductCode": "19530"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "objectTypeID": "SaleCase",
+  "content": {
+    "Origin": "API",
+    "ExternalID": "3aassdsadsad55aa921945595279542051",
+    "SaleChannelCode": "TT01",
+    "PointOfSaleID": "10",
+    "SaleItems": [
+      {
+        "ProductCode": "19530",
+        "Quantity": 1,
+        "TotalAmount":10
+      },
+      {
+        "ProductCode": "19530",
+        "Quantity": 1,
+        "TotalAmount":10
+      },
+      {
+        "ProductCode": "19856",
+        "Quantity": 1,
+        "TotalAmount":10
+      }
+    ],
+    "SaleDateTime": "2025-07-01T10:56:27.066Z",
+    "MemberExternalID": "99691eb263-3573-4be4-90b5-abe027d7b4ec",
+    "StoreCode": "NW-RJ567"
   }
 }</t>
   </si>
@@ -1560,7 +1557,7 @@
     "content": {
         "Name": "Product",
         "Description": "UpdatedDescription",
-        "ProductCode": "19526",
+        "ProductCode": "19530",
         "Brand": "Brand",
         "Category": "Category",
         "Incentivizable": true
@@ -1574,7 +1571,7 @@
   "content": {
     "Origin": "API",
     "Name": "BK Apparel",
-    "ExternalID": "45674",
+    "ExternalID": "45678",
     "RewardType": "stock_control",
     "RewardExpiration": "2025-09-06T04:00:00.000Z",
     "RewardCost": "",
@@ -1585,9 +1582,12 @@
   <si>
     <t>{
   "dataViewParameters": {
-    "ExternalID": "45674"
+    "ExternalID": "45678"
   }
 }</t>
+  </si>
+  <si>
+    <t>Ai4P@ssword5</t>
   </si>
 </sst>
 </file>
@@ -2159,7 +2159,7 @@
         <v>34</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>5</v>
@@ -2185,7 +2185,7 @@
         <v>34</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>5</v>
@@ -2211,7 +2211,7 @@
         <v>34</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>5</v>
@@ -2235,7 +2235,7 @@
         <v>34</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>5</v>
@@ -2283,7 +2283,7 @@
         <v>34</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>5</v>
@@ -2306,7 +2306,7 @@
         <v>34</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>5</v>
@@ -2335,7 +2335,7 @@
         <v>34</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="S8" s="6" t="s">
         <v>187</v>
@@ -2352,7 +2352,7 @@
         <v>34</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
     </row>
   </sheetData>
@@ -2360,7 +2360,7 @@
     <hyperlink ref="H2" r:id="rId1" xr:uid="{C7A33EB6-8367-4005-A814-B19729D1B87B}"/>
     <hyperlink ref="H3" r:id="rId2" xr:uid="{6B0F5573-1B6D-40BD-A1CD-4FF2D6A12B60}"/>
     <hyperlink ref="D2" r:id="rId3" display="Ai4P@ssword3" xr:uid="{BFC9E07A-6B6B-4917-9373-71F733F22D5F}"/>
-    <hyperlink ref="D9" r:id="rId4" display="Ai4P@ssword3" xr:uid="{C693285A-AACF-4030-BAA6-4C6360692518}"/>
+    <hyperlink ref="D9" r:id="rId4" display="Ai4P@ssword4" xr:uid="{C693285A-AACF-4030-BAA6-4C6360692518}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>
@@ -5047,7 +5047,7 @@
         <v>34</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G2" s="8"/>
       <c r="H2" s="10" t="s">
@@ -5063,7 +5063,7 @@
         <v>1</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="M2" s="6" t="s">
         <v>5</v>
@@ -5086,7 +5086,7 @@
         <v>34</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G3" s="8"/>
       <c r="H3" s="6" t="s">
@@ -5125,7 +5125,7 @@
         <v>34</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G4" s="8"/>
       <c r="H4" s="10" t="s">
@@ -5164,7 +5164,7 @@
         <v>34</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G5" s="8"/>
       <c r="H5" s="10" t="s">
@@ -5203,7 +5203,7 @@
         <v>34</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G6" s="8"/>
       <c r="H6" s="10" t="s">
@@ -5242,7 +5242,7 @@
         <v>34</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G7" s="8"/>
       <c r="H7" s="10" t="s">
@@ -5281,7 +5281,7 @@
         <v>34</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G8" s="8"/>
       <c r="H8" s="10" t="s">
@@ -5320,7 +5320,7 @@
         <v>34</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G9" s="8"/>
       <c r="H9" s="10" t="s">
@@ -5359,7 +5359,7 @@
         <v>34</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G10" s="8"/>
       <c r="H10" s="10" t="s">
@@ -5398,7 +5398,7 @@
         <v>34</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G11" s="8"/>
       <c r="H11" s="10" t="s">
@@ -5437,7 +5437,7 @@
         <v>34</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G12" s="8"/>
       <c r="H12" s="10" t="s">
@@ -5476,7 +5476,7 @@
         <v>34</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G13" s="8"/>
       <c r="H13" s="10" t="s">
@@ -5515,7 +5515,7 @@
         <v>34</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G14" s="8"/>
       <c r="H14" s="10" t="s">
@@ -5554,7 +5554,7 @@
         <v>34</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G15" s="8"/>
       <c r="H15" s="10" t="s">
@@ -5593,7 +5593,7 @@
         <v>34</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G16" s="8"/>
       <c r="H16" s="10" t="s">
@@ -5632,7 +5632,7 @@
         <v>34</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G17" s="8"/>
       <c r="H17" s="10" t="s">
@@ -5671,7 +5671,7 @@
         <v>34</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G18" s="8"/>
       <c r="H18" s="10" t="s">
@@ -5710,7 +5710,7 @@
         <v>34</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G19" s="8"/>
       <c r="H19" s="10" t="s">
@@ -5749,7 +5749,7 @@
         <v>34</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G20" s="8"/>
       <c r="H20" s="10" t="s">
@@ -5788,7 +5788,7 @@
         <v>34</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G21" s="8"/>
       <c r="H21" s="10" t="s">
@@ -5827,7 +5827,7 @@
         <v>34</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G22" s="8"/>
       <c r="H22" s="10" t="s">
@@ -5866,7 +5866,7 @@
         <v>34</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G23" s="8"/>
       <c r="H23" s="10" t="s">
@@ -5905,7 +5905,7 @@
         <v>34</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G24" s="8"/>
       <c r="H24" s="6" t="s">
@@ -5944,7 +5944,7 @@
         <v>34</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G25" s="8"/>
       <c r="H25" s="10" t="s">
@@ -5983,7 +5983,7 @@
         <v>34</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G26" s="8"/>
       <c r="H26" s="6" t="s">
@@ -6022,7 +6022,7 @@
         <v>34</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G27" s="8"/>
       <c r="H27" s="10" t="s">
@@ -6061,7 +6061,7 @@
         <v>34</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G28" s="8"/>
       <c r="H28" s="6" t="s">
@@ -6100,7 +6100,7 @@
         <v>34</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G29" s="8"/>
       <c r="H29" s="6" t="s">
@@ -6139,7 +6139,7 @@
         <v>34</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G30" s="8"/>
       <c r="H30" s="6" t="s">
@@ -6178,7 +6178,7 @@
         <v>34</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G31" s="8"/>
       <c r="H31" s="6" t="s">
@@ -6217,7 +6217,7 @@
         <v>34</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G32" s="8"/>
       <c r="H32" s="6" t="s">
@@ -6256,7 +6256,7 @@
         <v>34</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G33" s="8"/>
       <c r="H33" s="6" t="s">
@@ -6295,7 +6295,7 @@
         <v>34</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G34" s="8"/>
       <c r="H34" s="6" t="s">
@@ -6328,7 +6328,7 @@
         <v>34</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G35" s="8"/>
       <c r="H35" s="6" t="s">
@@ -6361,7 +6361,7 @@
         <v>34</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G36" s="8"/>
       <c r="H36" s="6" t="s">
@@ -6394,7 +6394,7 @@
         <v>34</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G37" s="8"/>
       <c r="H37" s="6" t="s">
@@ -6427,7 +6427,7 @@
         <v>34</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G38" s="8"/>
       <c r="H38" s="6" t="s">
@@ -6469,7 +6469,7 @@
         <v>34</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G39" s="8"/>
       <c r="H39" s="6" t="s">
@@ -6511,7 +6511,7 @@
         <v>34</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G40" s="8"/>
       <c r="H40" s="6" t="s">
@@ -6553,7 +6553,7 @@
         <v>34</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G41" s="8"/>
       <c r="H41" s="6" t="s">
@@ -6595,7 +6595,7 @@
         <v>34</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G42" s="8"/>
       <c r="H42" s="6" t="s">
@@ -6637,7 +6637,7 @@
         <v>34</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G43" s="8"/>
       <c r="L43" s="10" t="s">
@@ -6667,7 +6667,7 @@
         <v>34</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G44" s="8"/>
       <c r="N44" s="6" t="s">
@@ -6691,7 +6691,7 @@
         <v>34</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G45" s="8"/>
       <c r="N45" s="6" t="s">
@@ -6715,7 +6715,7 @@
         <v>34</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G46" s="8"/>
       <c r="N46" s="6" t="s">
@@ -6739,7 +6739,7 @@
         <v>34</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G47" s="8"/>
       <c r="N47" s="6" t="s">
@@ -6763,7 +6763,7 @@
         <v>34</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G48" s="8"/>
       <c r="N48" s="6" t="s">
@@ -6787,7 +6787,7 @@
         <v>34</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G49" s="8"/>
       <c r="N49" s="6" t="s">
@@ -6811,7 +6811,7 @@
         <v>34</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G50" s="8"/>
       <c r="N50" s="6" t="s">
@@ -6835,7 +6835,7 @@
         <v>34</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G51" s="8"/>
       <c r="N51" s="6" t="s">
@@ -6859,7 +6859,7 @@
         <v>34</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G52" s="8"/>
       <c r="N52" s="6" t="s">
@@ -6883,7 +6883,7 @@
         <v>34</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G53" s="8"/>
       <c r="N53" s="6" t="s">
@@ -6907,7 +6907,7 @@
         <v>34</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G54" s="8"/>
       <c r="N54" s="6" t="s">
@@ -6931,7 +6931,7 @@
         <v>34</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G55" s="8"/>
       <c r="N55" s="6" t="s">
@@ -6955,7 +6955,7 @@
         <v>34</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G56" s="8"/>
       <c r="N56" s="6" t="s">
@@ -6979,7 +6979,7 @@
         <v>34</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G57" s="8"/>
       <c r="N57" s="6" t="s">
@@ -7003,7 +7003,7 @@
         <v>34</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G58" s="8"/>
       <c r="N58" s="6" t="s">
@@ -7027,7 +7027,7 @@
         <v>34</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G59" s="8"/>
       <c r="O59" s="6" t="s">
@@ -7054,7 +7054,7 @@
         <v>34</v>
       </c>
       <c r="F60" s="8" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G60" s="8"/>
       <c r="Q60" s="6" t="s">
@@ -7078,7 +7078,7 @@
         <v>34</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
     </row>
     <row r="62" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
@@ -7098,7 +7098,7 @@
         <v>34</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
     </row>
     <row r="63" spans="1:17" ht="230.4" x14ac:dyDescent="0.3">
@@ -7118,7 +7118,7 @@
         <v>34</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="G63" s="20" t="s">
         <v>329</v>
@@ -7141,7 +7141,7 @@
         <v>34</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.3">
@@ -7899,10 +7899,11 @@
     <hyperlink ref="F56" r:id="rId121" display="Ai4P@ssword3" xr:uid="{71A4E974-AFEB-41B7-8662-9FCF3C37A6E9}"/>
     <hyperlink ref="F57" r:id="rId122" display="Ai4P@ssword3" xr:uid="{A2E209E2-0A14-437E-90BF-8A35B255954E}"/>
     <hyperlink ref="F58" r:id="rId123" display="Ai4P@ssword3" xr:uid="{280D1C2C-2C64-4631-94CB-4C9A63A22A3B}"/>
+    <hyperlink ref="F2" r:id="rId124" display="Ai4P@ssword4" xr:uid="{B5F9DBAD-A1A7-454B-96C6-8035CCE043EB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId124"/>
-  <legacyDrawing r:id="rId125"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId125"/>
+  <legacyDrawing r:id="rId126"/>
 </worksheet>
 </file>
 
@@ -7911,13 +7912,13 @@
   <dimension ref="A1:S72"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.77734375" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.21875" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.21875" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5546875" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="33.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="102.44140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.5546875" style="6" customWidth="1"/>
-    <col min="7" max="8" width="13.88671875" style="6" customWidth="1"/>
+    <col min="6" max="6" width="9.5546875" style="6" hidden="1" customWidth="1"/>
+    <col min="7" max="8" width="13.88671875" style="6" hidden="1" customWidth="1"/>
     <col min="9" max="9" width="34.44140625" style="20" customWidth="1"/>
     <col min="10" max="10" width="21.21875" style="6" hidden="1" customWidth="1"/>
     <col min="11" max="11" width="11.5546875" style="6" hidden="1" customWidth="1"/>
@@ -7925,10 +7926,10 @@
     <col min="13" max="13" width="11.77734375" style="23" hidden="1" customWidth="1"/>
     <col min="14" max="14" width="25.5546875" style="6" customWidth="1"/>
     <col min="15" max="15" width="30.5546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="28.109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17.77734375" style="6" customWidth="1"/>
-    <col min="18" max="18" width="11.21875" style="6" customWidth="1"/>
-    <col min="19" max="19" width="10.109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="28.109375" style="6" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="17.77734375" style="6" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="11.21875" style="6" hidden="1" customWidth="1"/>
+    <col min="19" max="19" width="10.109375" style="6" hidden="1" customWidth="1"/>
     <col min="20" max="16384" width="8.88671875" style="6"/>
   </cols>
   <sheetData>
@@ -7943,7 +7944,7 @@
         <v>191</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E1" s="18" t="s">
         <v>50</v>
@@ -7955,7 +7956,7 @@
         <v>1</v>
       </c>
       <c r="H1" s="17" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="I1" s="17" t="s">
         <v>178</v>
@@ -7999,27 +8000,27 @@
         <v>327</v>
       </c>
       <c r="C2" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>345</v>
+      </c>
+      <c r="E2" s="19" t="s">
         <v>338</v>
-      </c>
-      <c r="D2" s="21" t="s">
-        <v>346</v>
-      </c>
-      <c r="E2" s="19" t="s">
-        <v>339</v>
       </c>
       <c r="F2" s="7"/>
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
       <c r="I2" s="24" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="J2" s="10"/>
       <c r="K2" s="10"/>
       <c r="N2" s="6" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="72" x14ac:dyDescent="0.3">
@@ -8030,25 +8031,25 @@
         <v>327</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E3" s="19" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F3" s="7"/>
       <c r="G3" s="13"/>
       <c r="H3" s="13"/>
       <c r="I3" s="24" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="172.8" x14ac:dyDescent="0.3">
@@ -8059,26 +8060,26 @@
         <v>327</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E4" s="19" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F4" s="7"/>
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
       <c r="I4" s="24" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="J4" s="10"/>
       <c r="N4" s="10" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="O4" s="6" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="72" x14ac:dyDescent="0.3">
@@ -8089,26 +8090,26 @@
         <v>327</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F5" s="7"/>
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
       <c r="I5" s="24" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="J5" s="10"/>
       <c r="N5" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="O5" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="187.2" x14ac:dyDescent="0.3">
@@ -8119,26 +8120,26 @@
         <v>327</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D6" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="E6" s="19" t="s">
         <v>356</v>
-      </c>
-      <c r="E6" s="19" t="s">
-        <v>357</v>
       </c>
       <c r="F6" s="7"/>
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
       <c r="I6" s="24" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="J6" s="10"/>
       <c r="N6" s="10" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="O6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="72" x14ac:dyDescent="0.3">
@@ -8149,26 +8150,26 @@
         <v>327</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D7" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="E7" s="19" t="s">
         <v>358</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>359</v>
       </c>
       <c r="F7" s="7"/>
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
       <c r="I7" s="24" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="J7" s="10"/>
       <c r="N7" t="s">
+        <v>405</v>
+      </c>
+      <c r="O7" t="s">
         <v>407</v>
-      </c>
-      <c r="O7" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="57.6" x14ac:dyDescent="0.3">
@@ -8179,49 +8180,49 @@
         <v>327</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D8" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="E8" s="19" t="s">
         <v>365</v>
-      </c>
-      <c r="E8" s="19" t="s">
-        <v>366</v>
       </c>
       <c r="F8" s="7"/>
       <c r="G8" s="8"/>
       <c r="H8" s="8"/>
       <c r="I8" s="24" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="J8" s="10"/>
       <c r="N8" s="10" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="O8" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="9" spans="1:19" ht="216" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>327</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D9" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="E9" s="19" t="s">
         <v>367</v>
-      </c>
-      <c r="E9" s="19" t="s">
-        <v>368</v>
       </c>
       <c r="F9" s="7"/>
       <c r="G9" s="8"/>
       <c r="H9" s="8"/>
       <c r="I9" s="24" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="J9" s="10"/>
       <c r="N9" s="10"/>
@@ -8229,25 +8230,25 @@
     </row>
     <row r="10" spans="1:19" ht="72" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>327</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D10" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="E10" s="19" t="s">
         <v>369</v>
-      </c>
-      <c r="E10" s="19" t="s">
-        <v>370</v>
       </c>
       <c r="F10" s="7"/>
       <c r="G10" s="8"/>
       <c r="H10" s="8"/>
       <c r="I10" s="24" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="J10" s="10"/>
       <c r="N10" s="10"/>
@@ -8255,25 +8256,25 @@
     </row>
     <row r="11" spans="1:19" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>327</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D11" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="E11" s="19" t="s">
         <v>374</v>
-      </c>
-      <c r="E11" s="19" t="s">
-        <v>375</v>
       </c>
       <c r="F11" s="7"/>
       <c r="G11" s="8"/>
       <c r="H11" s="8"/>
       <c r="I11" s="24" t="s">
-        <v>376</v>
+        <v>424</v>
       </c>
       <c r="J11" s="10"/>
       <c r="N11" s="10"/>
@@ -8287,19 +8288,19 @@
         <v>327</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="F12" s="7"/>
       <c r="G12" s="8"/>
       <c r="H12" s="8"/>
       <c r="I12" s="24" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="J12" s="10"/>
       <c r="N12" s="10"/>
@@ -8313,19 +8314,19 @@
         <v>327</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="F13" s="7"/>
       <c r="G13" s="8"/>
       <c r="H13" s="8"/>
       <c r="I13" s="24" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="J13" s="10"/>
       <c r="N13" s="10"/>
@@ -8339,19 +8340,19 @@
         <v>327</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E14" s="19" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="F14" s="7"/>
       <c r="G14" s="8"/>
       <c r="H14" s="8"/>
       <c r="I14" s="24" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="J14" s="10"/>
       <c r="N14" s="10"/>
@@ -8365,19 +8366,19 @@
         <v>327</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E15" s="19" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F15" s="7"/>
       <c r="G15" s="8"/>
       <c r="H15" s="8"/>
       <c r="I15" s="24" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="N15" s="10"/>
       <c r="O15" s="10"/>
@@ -8387,22 +8388,22 @@
         <v>69</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="E16" s="19" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="8"/>
       <c r="H16" s="8"/>
       <c r="I16" s="24" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="J16" s="10"/>
       <c r="N16" s="10"/>
@@ -8413,22 +8414,22 @@
         <v>70</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F17" s="7"/>
       <c r="G17" s="8"/>
       <c r="H17" s="8"/>
       <c r="I17" s="24" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="115.2" x14ac:dyDescent="0.3">
@@ -8436,22 +8437,22 @@
         <v>71</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E18" s="19" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="F18" s="7"/>
       <c r="G18" s="8"/>
       <c r="H18" s="8"/>
       <c r="I18" s="24" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="J18" s="10"/>
     </row>
@@ -8460,22 +8461,22 @@
         <v>72</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E19" s="19" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F19" s="7"/>
       <c r="G19" s="8"/>
       <c r="H19" s="8"/>
       <c r="I19" s="24" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="N19" s="10"/>
     </row>
@@ -8484,22 +8485,22 @@
         <v>73</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D20" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="E20" s="19" t="s">
         <v>352</v>
-      </c>
-      <c r="E20" s="19" t="s">
-        <v>353</v>
       </c>
       <c r="F20" s="7"/>
       <c r="G20" s="8"/>
       <c r="H20" s="8"/>
       <c r="I20" s="24" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="N20" s="10"/>
     </row>
@@ -8508,22 +8509,22 @@
         <v>74</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D21" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="E21" s="19" t="s">
         <v>354</v>
-      </c>
-      <c r="E21" s="19" t="s">
-        <v>355</v>
       </c>
       <c r="F21" s="7"/>
       <c r="G21" s="8"/>
       <c r="H21" s="8"/>
       <c r="I21" s="24" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="N21" s="10"/>
     </row>
@@ -8532,22 +8533,22 @@
         <v>75</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D22" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="E22" s="19" t="s">
         <v>360</v>
-      </c>
-      <c r="E22" s="19" t="s">
-        <v>361</v>
       </c>
       <c r="F22" s="7"/>
       <c r="G22" s="8"/>
       <c r="H22" s="8"/>
       <c r="I22" s="24" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="N22" s="10"/>
     </row>
@@ -8556,22 +8557,22 @@
         <v>76</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D23" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="E23" s="19" t="s">
         <v>363</v>
-      </c>
-      <c r="E23" s="19" t="s">
-        <v>364</v>
       </c>
       <c r="F23" s="7"/>
       <c r="G23" s="8"/>
       <c r="H23" s="8"/>
       <c r="I23" s="24" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="N23" s="10"/>
     </row>
@@ -8580,22 +8581,22 @@
         <v>77</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D24" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="E24" s="19" t="s">
         <v>371</v>
-      </c>
-      <c r="E24" s="19" t="s">
-        <v>372</v>
       </c>
       <c r="F24" s="7"/>
       <c r="G24" s="8"/>
       <c r="H24" s="8"/>
       <c r="I24" s="24" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="N24" s="10"/>
     </row>
@@ -8604,22 +8605,22 @@
         <v>78</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E25" s="19" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="F25" s="7"/>
       <c r="G25" s="8"/>
       <c r="H25" s="8"/>
       <c r="I25" s="24" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="N25" s="10"/>
     </row>
@@ -8628,22 +8629,22 @@
         <v>79</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E26" s="19" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="F26" s="7"/>
       <c r="G26" s="8"/>
       <c r="H26" s="8"/>
       <c r="I26" s="24" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="N26" s="10"/>
     </row>
@@ -9166,17 +9167,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
   </sheetData>

--- a/test-data/sscData.xlsx
+++ b/test-data/sscData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Chorus Portal Automation_Work\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7A527EE-113D-4795-9965-F3D99353F338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2D5A1E3-37AC-46AA-B51B-1846DEFE939E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="QA" sheetId="1" r:id="rId1"/>
@@ -1112,9 +1112,6 @@
     <t>TestCase89</t>
   </si>
   <si>
-    <t>AI4HR</t>
-  </si>
-  <si>
     <t>TestCase8</t>
   </si>
   <si>
@@ -1589,12 +1586,15 @@
   <si>
     <t>Ai4P@ssword5</t>
   </si>
+  <si>
+    <t>Insurance</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1655,6 +1655,13 @@
       <name val="Courier New"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1683,7 +1690,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
@@ -1745,6 +1752,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2065,7 +2073,7 @@
     <col min="1" max="1" width="11.109375" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="4.109375" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.109375" style="6" customWidth="1"/>
+    <col min="4" max="4" width="14.109375" style="6" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="12.5546875" style="6" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" style="6" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.21875" style="6" bestFit="1" customWidth="1"/>
@@ -2159,7 +2167,7 @@
         <v>34</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>5</v>
@@ -2185,7 +2193,7 @@
         <v>34</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>5</v>
@@ -2211,7 +2219,7 @@
         <v>34</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>5</v>
@@ -2235,7 +2243,7 @@
         <v>34</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>5</v>
@@ -2283,7 +2291,7 @@
         <v>34</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>5</v>
@@ -2306,7 +2314,7 @@
         <v>34</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>5</v>
@@ -2335,7 +2343,7 @@
         <v>34</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="S8" s="6" t="s">
         <v>187</v>
@@ -2352,7 +2360,7 @@
         <v>34</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
   </sheetData>
@@ -4962,7 +4970,7 @@
     <col min="3" max="3" width="7.21875" style="6" customWidth="1"/>
     <col min="4" max="4" width="102.44140625" style="20" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.5546875" style="6" customWidth="1"/>
-    <col min="6" max="6" width="13.88671875" style="6" customWidth="1"/>
+    <col min="6" max="6" width="13.88671875" style="6" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="14.109375" style="20" customWidth="1"/>
     <col min="8" max="8" width="21.21875" style="6" hidden="1" customWidth="1"/>
     <col min="9" max="9" width="11.5546875" style="6" hidden="1" customWidth="1"/>
@@ -5047,7 +5055,7 @@
         <v>34</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G2" s="8"/>
       <c r="H2" s="10" t="s">
@@ -5062,8 +5070,8 @@
       <c r="K2" s="23">
         <v>1</v>
       </c>
-      <c r="L2" s="6" t="s">
-        <v>333</v>
+      <c r="L2" s="25" t="s">
+        <v>428</v>
       </c>
       <c r="M2" s="6" t="s">
         <v>5</v>
@@ -5086,7 +5094,7 @@
         <v>34</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G3" s="8"/>
       <c r="H3" s="6" t="s">
@@ -5125,7 +5133,7 @@
         <v>34</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G4" s="8"/>
       <c r="H4" s="10" t="s">
@@ -5164,7 +5172,7 @@
         <v>34</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G5" s="8"/>
       <c r="H5" s="10" t="s">
@@ -5203,7 +5211,7 @@
         <v>34</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G6" s="8"/>
       <c r="H6" s="10" t="s">
@@ -5242,7 +5250,7 @@
         <v>34</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G7" s="8"/>
       <c r="H7" s="10" t="s">
@@ -5281,7 +5289,7 @@
         <v>34</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G8" s="8"/>
       <c r="H8" s="10" t="s">
@@ -5320,7 +5328,7 @@
         <v>34</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G9" s="8"/>
       <c r="H9" s="10" t="s">
@@ -5359,7 +5367,7 @@
         <v>34</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G10" s="8"/>
       <c r="H10" s="10" t="s">
@@ -5398,7 +5406,7 @@
         <v>34</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G11" s="8"/>
       <c r="H11" s="10" t="s">
@@ -5437,7 +5445,7 @@
         <v>34</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G12" s="8"/>
       <c r="H12" s="10" t="s">
@@ -5476,7 +5484,7 @@
         <v>34</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G13" s="8"/>
       <c r="H13" s="10" t="s">
@@ -5515,7 +5523,7 @@
         <v>34</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G14" s="8"/>
       <c r="H14" s="10" t="s">
@@ -5554,7 +5562,7 @@
         <v>34</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G15" s="8"/>
       <c r="H15" s="10" t="s">
@@ -5593,7 +5601,7 @@
         <v>34</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G16" s="8"/>
       <c r="H16" s="10" t="s">
@@ -5632,7 +5640,7 @@
         <v>34</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G17" s="8"/>
       <c r="H17" s="10" t="s">
@@ -5671,7 +5679,7 @@
         <v>34</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G18" s="8"/>
       <c r="H18" s="10" t="s">
@@ -5710,7 +5718,7 @@
         <v>34</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G19" s="8"/>
       <c r="H19" s="10" t="s">
@@ -5749,7 +5757,7 @@
         <v>34</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G20" s="8"/>
       <c r="H20" s="10" t="s">
@@ -5788,7 +5796,7 @@
         <v>34</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G21" s="8"/>
       <c r="H21" s="10" t="s">
@@ -5827,7 +5835,7 @@
         <v>34</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G22" s="8"/>
       <c r="H22" s="10" t="s">
@@ -5866,7 +5874,7 @@
         <v>34</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G23" s="8"/>
       <c r="H23" s="10" t="s">
@@ -5905,7 +5913,7 @@
         <v>34</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G24" s="8"/>
       <c r="H24" s="6" t="s">
@@ -5944,7 +5952,7 @@
         <v>34</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G25" s="8"/>
       <c r="H25" s="10" t="s">
@@ -5983,7 +5991,7 @@
         <v>34</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G26" s="8"/>
       <c r="H26" s="6" t="s">
@@ -6022,7 +6030,7 @@
         <v>34</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G27" s="8"/>
       <c r="H27" s="10" t="s">
@@ -6061,7 +6069,7 @@
         <v>34</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G28" s="8"/>
       <c r="H28" s="6" t="s">
@@ -6100,7 +6108,7 @@
         <v>34</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G29" s="8"/>
       <c r="H29" s="6" t="s">
@@ -6139,7 +6147,7 @@
         <v>34</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G30" s="8"/>
       <c r="H30" s="6" t="s">
@@ -6178,7 +6186,7 @@
         <v>34</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G31" s="8"/>
       <c r="H31" s="6" t="s">
@@ -6217,7 +6225,7 @@
         <v>34</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G32" s="8"/>
       <c r="H32" s="6" t="s">
@@ -6256,7 +6264,7 @@
         <v>34</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G33" s="8"/>
       <c r="H33" s="6" t="s">
@@ -6295,7 +6303,7 @@
         <v>34</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G34" s="8"/>
       <c r="H34" s="6" t="s">
@@ -6328,7 +6336,7 @@
         <v>34</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G35" s="8"/>
       <c r="H35" s="6" t="s">
@@ -6361,7 +6369,7 @@
         <v>34</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G36" s="8"/>
       <c r="H36" s="6" t="s">
@@ -6394,7 +6402,7 @@
         <v>34</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G37" s="8"/>
       <c r="H37" s="6" t="s">
@@ -6427,7 +6435,7 @@
         <v>34</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G38" s="8"/>
       <c r="H38" s="6" t="s">
@@ -6469,7 +6477,7 @@
         <v>34</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G39" s="8"/>
       <c r="H39" s="6" t="s">
@@ -6511,7 +6519,7 @@
         <v>34</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G40" s="8"/>
       <c r="H40" s="6" t="s">
@@ -6553,7 +6561,7 @@
         <v>34</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G41" s="8"/>
       <c r="H41" s="6" t="s">
@@ -6595,7 +6603,7 @@
         <v>34</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G42" s="8"/>
       <c r="H42" s="6" t="s">
@@ -6637,7 +6645,7 @@
         <v>34</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G43" s="8"/>
       <c r="L43" s="10" t="s">
@@ -6667,7 +6675,7 @@
         <v>34</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G44" s="8"/>
       <c r="N44" s="6" t="s">
@@ -6691,7 +6699,7 @@
         <v>34</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G45" s="8"/>
       <c r="N45" s="6" t="s">
@@ -6715,7 +6723,7 @@
         <v>34</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G46" s="8"/>
       <c r="N46" s="6" t="s">
@@ -6739,7 +6747,7 @@
         <v>34</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G47" s="8"/>
       <c r="N47" s="6" t="s">
@@ -6763,7 +6771,7 @@
         <v>34</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G48" s="8"/>
       <c r="N48" s="6" t="s">
@@ -6787,7 +6795,7 @@
         <v>34</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G49" s="8"/>
       <c r="N49" s="6" t="s">
@@ -6811,7 +6819,7 @@
         <v>34</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G50" s="8"/>
       <c r="N50" s="6" t="s">
@@ -6835,7 +6843,7 @@
         <v>34</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G51" s="8"/>
       <c r="N51" s="6" t="s">
@@ -6859,7 +6867,7 @@
         <v>34</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G52" s="8"/>
       <c r="N52" s="6" t="s">
@@ -6883,7 +6891,7 @@
         <v>34</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G53" s="8"/>
       <c r="N53" s="6" t="s">
@@ -6907,7 +6915,7 @@
         <v>34</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G54" s="8"/>
       <c r="N54" s="6" t="s">
@@ -6931,7 +6939,7 @@
         <v>34</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G55" s="8"/>
       <c r="N55" s="6" t="s">
@@ -6955,7 +6963,7 @@
         <v>34</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G56" s="8"/>
       <c r="N56" s="6" t="s">
@@ -6979,7 +6987,7 @@
         <v>34</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G57" s="8"/>
       <c r="N57" s="6" t="s">
@@ -7003,7 +7011,7 @@
         <v>34</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G58" s="8"/>
       <c r="N58" s="6" t="s">
@@ -7027,7 +7035,7 @@
         <v>34</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G59" s="8"/>
       <c r="O59" s="6" t="s">
@@ -7054,7 +7062,7 @@
         <v>34</v>
       </c>
       <c r="F60" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G60" s="8"/>
       <c r="Q60" s="6" t="s">
@@ -7078,7 +7086,7 @@
         <v>34</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="62" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
@@ -7098,7 +7106,7 @@
         <v>34</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="63" spans="1:17" ht="230.4" x14ac:dyDescent="0.3">
@@ -7118,7 +7126,7 @@
         <v>34</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G63" s="20" t="s">
         <v>329</v>
@@ -7141,7 +7149,7 @@
         <v>34</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.3">
@@ -7944,7 +7952,7 @@
         <v>191</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E1" s="18" t="s">
         <v>50</v>
@@ -7956,7 +7964,7 @@
         <v>1</v>
       </c>
       <c r="H1" s="17" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I1" s="17" t="s">
         <v>178</v>
@@ -8000,27 +8008,27 @@
         <v>327</v>
       </c>
       <c r="C2" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>344</v>
+      </c>
+      <c r="E2" s="19" t="s">
         <v>337</v>
-      </c>
-      <c r="D2" s="21" t="s">
-        <v>345</v>
-      </c>
-      <c r="E2" s="19" t="s">
-        <v>338</v>
       </c>
       <c r="F2" s="7"/>
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
       <c r="I2" s="24" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="J2" s="10"/>
       <c r="K2" s="10"/>
       <c r="N2" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="O2" s="6" t="s">
         <v>395</v>
-      </c>
-      <c r="O2" s="6" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="72" x14ac:dyDescent="0.3">
@@ -8031,25 +8039,25 @@
         <v>327</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E3" s="19" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F3" s="7"/>
       <c r="G3" s="13"/>
       <c r="H3" s="13"/>
       <c r="I3" s="24" t="s">
+        <v>418</v>
+      </c>
+      <c r="N3" s="6" t="s">
         <v>419</v>
       </c>
-      <c r="N3" s="6" t="s">
-        <v>420</v>
-      </c>
       <c r="O3" s="6" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="172.8" x14ac:dyDescent="0.3">
@@ -8060,26 +8068,26 @@
         <v>327</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E4" s="19" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F4" s="7"/>
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
       <c r="I4" s="24" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="J4" s="10"/>
       <c r="N4" s="10" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="O4" s="6" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="72" x14ac:dyDescent="0.3">
@@ -8090,26 +8098,26 @@
         <v>327</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F5" s="7"/>
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
       <c r="I5" s="24" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="J5" s="10"/>
       <c r="N5" t="s">
+        <v>402</v>
+      </c>
+      <c r="O5" t="s">
         <v>403</v>
-      </c>
-      <c r="O5" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="187.2" x14ac:dyDescent="0.3">
@@ -8120,26 +8128,26 @@
         <v>327</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D6" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="E6" s="19" t="s">
         <v>355</v>
-      </c>
-      <c r="E6" s="19" t="s">
-        <v>356</v>
       </c>
       <c r="F6" s="7"/>
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
       <c r="I6" s="24" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="J6" s="10"/>
       <c r="N6" s="10" t="s">
+        <v>404</v>
+      </c>
+      <c r="O6" t="s">
         <v>405</v>
-      </c>
-      <c r="O6" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="72" x14ac:dyDescent="0.3">
@@ -8150,26 +8158,26 @@
         <v>327</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D7" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="E7" s="19" t="s">
         <v>357</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>358</v>
       </c>
       <c r="F7" s="7"/>
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
       <c r="I7" s="24" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="J7" s="10"/>
       <c r="N7" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="O7" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="57.6" x14ac:dyDescent="0.3">
@@ -8180,49 +8188,49 @@
         <v>327</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D8" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="E8" s="19" t="s">
         <v>364</v>
-      </c>
-      <c r="E8" s="19" t="s">
-        <v>365</v>
       </c>
       <c r="F8" s="7"/>
       <c r="G8" s="8"/>
       <c r="H8" s="8"/>
       <c r="I8" s="24" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="J8" s="10"/>
       <c r="N8" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="O8" t="s">
         <v>408</v>
-      </c>
-      <c r="O8" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="9" spans="1:19" ht="216" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>327</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D9" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="E9" s="19" t="s">
         <v>366</v>
-      </c>
-      <c r="E9" s="19" t="s">
-        <v>367</v>
       </c>
       <c r="F9" s="7"/>
       <c r="G9" s="8"/>
       <c r="H9" s="8"/>
       <c r="I9" s="24" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="J9" s="10"/>
       <c r="N9" s="10"/>
@@ -8230,25 +8238,25 @@
     </row>
     <row r="10" spans="1:19" ht="72" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>327</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D10" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="E10" s="19" t="s">
         <v>368</v>
-      </c>
-      <c r="E10" s="19" t="s">
-        <v>369</v>
       </c>
       <c r="F10" s="7"/>
       <c r="G10" s="8"/>
       <c r="H10" s="8"/>
       <c r="I10" s="24" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="J10" s="10"/>
       <c r="N10" s="10"/>
@@ -8256,25 +8264,25 @@
     </row>
     <row r="11" spans="1:19" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>327</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D11" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="E11" s="19" t="s">
         <v>373</v>
-      </c>
-      <c r="E11" s="19" t="s">
-        <v>374</v>
       </c>
       <c r="F11" s="7"/>
       <c r="G11" s="8"/>
       <c r="H11" s="8"/>
       <c r="I11" s="24" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="J11" s="10"/>
       <c r="N11" s="10"/>
@@ -8288,19 +8296,19 @@
         <v>327</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D12" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="E12" s="19" t="s">
         <v>375</v>
-      </c>
-      <c r="E12" s="19" t="s">
-        <v>376</v>
       </c>
       <c r="F12" s="7"/>
       <c r="G12" s="8"/>
       <c r="H12" s="8"/>
       <c r="I12" s="24" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J12" s="10"/>
       <c r="N12" s="10"/>
@@ -8314,19 +8322,19 @@
         <v>327</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D13" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="E13" s="19" t="s">
         <v>382</v>
-      </c>
-      <c r="E13" s="19" t="s">
-        <v>383</v>
       </c>
       <c r="F13" s="7"/>
       <c r="G13" s="8"/>
       <c r="H13" s="8"/>
       <c r="I13" s="24" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="J13" s="10"/>
       <c r="N13" s="10"/>
@@ -8340,19 +8348,19 @@
         <v>327</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D14" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="E14" s="19" t="s">
         <v>384</v>
-      </c>
-      <c r="E14" s="19" t="s">
-        <v>385</v>
       </c>
       <c r="F14" s="7"/>
       <c r="G14" s="8"/>
       <c r="H14" s="8"/>
       <c r="I14" s="24" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="J14" s="10"/>
       <c r="N14" s="10"/>
@@ -8366,19 +8374,19 @@
         <v>327</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D15" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="E15" s="19" t="s">
         <v>386</v>
-      </c>
-      <c r="E15" s="19" t="s">
-        <v>387</v>
       </c>
       <c r="F15" s="7"/>
       <c r="G15" s="8"/>
       <c r="H15" s="8"/>
       <c r="I15" s="24" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="N15" s="10"/>
       <c r="O15" s="10"/>
@@ -8388,22 +8396,22 @@
         <v>69</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D16" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="E16" s="19" t="s">
         <v>388</v>
-      </c>
-      <c r="E16" s="19" t="s">
-        <v>389</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="8"/>
       <c r="H16" s="8"/>
       <c r="I16" s="24" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="J16" s="10"/>
       <c r="N16" s="10"/>
@@ -8414,22 +8422,22 @@
         <v>70</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D17" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="E17" s="19" t="s">
         <v>391</v>
-      </c>
-      <c r="E17" s="19" t="s">
-        <v>392</v>
       </c>
       <c r="F17" s="7"/>
       <c r="G17" s="8"/>
       <c r="H17" s="8"/>
       <c r="I17" s="24" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="115.2" x14ac:dyDescent="0.3">
@@ -8437,22 +8445,22 @@
         <v>71</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E18" s="19" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="F18" s="7"/>
       <c r="G18" s="8"/>
       <c r="H18" s="8"/>
       <c r="I18" s="24" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="J18" s="10"/>
     </row>
@@ -8461,22 +8469,22 @@
         <v>72</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E19" s="19" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F19" s="7"/>
       <c r="G19" s="8"/>
       <c r="H19" s="8"/>
       <c r="I19" s="24" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="N19" s="10"/>
     </row>
@@ -8485,22 +8493,22 @@
         <v>73</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D20" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="E20" s="19" t="s">
         <v>351</v>
-      </c>
-      <c r="E20" s="19" t="s">
-        <v>352</v>
       </c>
       <c r="F20" s="7"/>
       <c r="G20" s="8"/>
       <c r="H20" s="8"/>
       <c r="I20" s="24" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="N20" s="10"/>
     </row>
@@ -8509,22 +8517,22 @@
         <v>74</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D21" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="E21" s="19" t="s">
         <v>353</v>
-      </c>
-      <c r="E21" s="19" t="s">
-        <v>354</v>
       </c>
       <c r="F21" s="7"/>
       <c r="G21" s="8"/>
       <c r="H21" s="8"/>
       <c r="I21" s="24" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="N21" s="10"/>
     </row>
@@ -8533,22 +8541,22 @@
         <v>75</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D22" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="E22" s="19" t="s">
         <v>359</v>
-      </c>
-      <c r="E22" s="19" t="s">
-        <v>360</v>
       </c>
       <c r="F22" s="7"/>
       <c r="G22" s="8"/>
       <c r="H22" s="8"/>
       <c r="I22" s="24" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="N22" s="10"/>
     </row>
@@ -8557,22 +8565,22 @@
         <v>76</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D23" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="E23" s="19" t="s">
         <v>362</v>
-      </c>
-      <c r="E23" s="19" t="s">
-        <v>363</v>
       </c>
       <c r="F23" s="7"/>
       <c r="G23" s="8"/>
       <c r="H23" s="8"/>
       <c r="I23" s="24" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="N23" s="10"/>
     </row>
@@ -8581,22 +8589,22 @@
         <v>77</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D24" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="E24" s="19" t="s">
         <v>370</v>
-      </c>
-      <c r="E24" s="19" t="s">
-        <v>371</v>
       </c>
       <c r="F24" s="7"/>
       <c r="G24" s="8"/>
       <c r="H24" s="8"/>
       <c r="I24" s="24" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="N24" s="10"/>
     </row>
@@ -8605,22 +8613,22 @@
         <v>78</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D25" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="E25" s="19" t="s">
         <v>378</v>
-      </c>
-      <c r="E25" s="19" t="s">
-        <v>379</v>
       </c>
       <c r="F25" s="7"/>
       <c r="G25" s="8"/>
       <c r="H25" s="8"/>
       <c r="I25" s="24" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="N25" s="10"/>
     </row>
@@ -8629,22 +8637,22 @@
         <v>79</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D26" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="E26" s="19" t="s">
         <v>380</v>
-      </c>
-      <c r="E26" s="19" t="s">
-        <v>381</v>
       </c>
       <c r="F26" s="7"/>
       <c r="G26" s="8"/>
       <c r="H26" s="8"/>
       <c r="I26" s="24" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="N26" s="10"/>
     </row>
@@ -9167,17 +9175,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
   </sheetData>

--- a/test-data/sscData.xlsx
+++ b/test-data/sscData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Chorus Portal Automation_Work\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2D5A1E3-37AC-46AA-B51B-1846DEFE939E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{289BDC5B-8AC8-4BD7-A6E8-E526BAAAB1E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="QA" sheetId="1" r:id="rId1"/>
@@ -1587,14 +1587,14 @@
     <t>Ai4P@ssword5</t>
   </si>
   <si>
-    <t>Insurance</t>
+    <t>PACLIFE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1655,13 +1655,6 @@
       <name val="Courier New"/>
       <family val="3"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1690,7 +1683,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
@@ -1752,7 +1745,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -5070,7 +5062,7 @@
       <c r="K2" s="23">
         <v>1</v>
       </c>
-      <c r="L2" s="25" t="s">
+      <c r="L2" s="6" t="s">
         <v>428</v>
       </c>
       <c r="M2" s="6" t="s">

--- a/test-data/sscData.xlsx
+++ b/test-data/sscData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Chorus Portal Automation_Work\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82F2C1FC-EAF7-47A7-8A1A-F1BB81E0335B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFDB3C18-3D11-4666-98E6-494450949758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3995" uniqueCount="721">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3933" uniqueCount="721">
   <si>
     <t>username</t>
   </si>
@@ -17913,9 +17913,6 @@
       <c r="A3" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>424</v>
-      </c>
       <c r="C3" s="6" t="s">
         <v>177</v>
       </c>
@@ -17954,9 +17951,6 @@
       <c r="A4" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>424</v>
-      </c>
       <c r="C4" s="6" t="s">
         <v>177</v>
       </c>
@@ -17995,9 +17989,6 @@
       <c r="A5" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>424</v>
-      </c>
       <c r="C5" s="6" t="s">
         <v>177</v>
       </c>
@@ -18036,9 +18027,6 @@
       <c r="A6" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>424</v>
-      </c>
       <c r="C6" s="6" t="s">
         <v>177</v>
       </c>
@@ -18077,9 +18065,6 @@
       <c r="A7" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>424</v>
-      </c>
       <c r="C7" s="6" t="s">
         <v>177</v>
       </c>
@@ -18118,9 +18103,6 @@
       <c r="A8" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>424</v>
-      </c>
       <c r="C8" s="6" t="s">
         <v>177</v>
       </c>
@@ -18159,9 +18141,6 @@
       <c r="A9" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>424</v>
-      </c>
       <c r="C9" s="6" t="s">
         <v>177</v>
       </c>
@@ -18200,9 +18179,6 @@
       <c r="A10" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>424</v>
-      </c>
       <c r="C10" s="6" t="s">
         <v>177</v>
       </c>
@@ -18241,9 +18217,6 @@
       <c r="A11" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>424</v>
-      </c>
       <c r="C11" s="6" t="s">
         <v>177</v>
       </c>
@@ -18282,9 +18255,6 @@
       <c r="A12" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>424</v>
-      </c>
       <c r="C12" s="6" t="s">
         <v>177</v>
       </c>
@@ -18323,9 +18293,6 @@
       <c r="A13" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>424</v>
-      </c>
       <c r="C13" s="6" t="s">
         <v>177</v>
       </c>
@@ -18364,9 +18331,6 @@
       <c r="A14" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>424</v>
-      </c>
       <c r="C14" s="6" t="s">
         <v>177</v>
       </c>
@@ -18405,9 +18369,6 @@
       <c r="A15" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>424</v>
-      </c>
       <c r="C15" s="6" t="s">
         <v>177</v>
       </c>
@@ -18446,9 +18407,6 @@
       <c r="A16" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>424</v>
-      </c>
       <c r="C16" s="6" t="s">
         <v>177</v>
       </c>
@@ -18487,9 +18445,6 @@
       <c r="A17" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>424</v>
-      </c>
       <c r="C17" s="6" t="s">
         <v>177</v>
       </c>
@@ -18528,9 +18483,6 @@
       <c r="A18" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>424</v>
-      </c>
       <c r="C18" s="6" t="s">
         <v>177</v>
       </c>
@@ -18569,9 +18521,6 @@
       <c r="A19" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>424</v>
-      </c>
       <c r="C19" s="6" t="s">
         <v>177</v>
       </c>
@@ -18610,9 +18559,6 @@
       <c r="A20" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>424</v>
-      </c>
       <c r="C20" s="6" t="s">
         <v>177</v>
       </c>
@@ -18651,9 +18597,6 @@
       <c r="A21" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>424</v>
-      </c>
       <c r="C21" s="6" t="s">
         <v>177</v>
       </c>
@@ -18692,9 +18635,6 @@
       <c r="A22" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>424</v>
-      </c>
       <c r="C22" s="6" t="s">
         <v>177</v>
       </c>
@@ -18733,9 +18673,6 @@
       <c r="A23" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>424</v>
-      </c>
       <c r="C23" s="6" t="s">
         <v>177</v>
       </c>
@@ -18774,9 +18711,6 @@
       <c r="A24" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>424</v>
-      </c>
       <c r="C24" s="6" t="s">
         <v>177</v>
       </c>
@@ -18814,9 +18748,6 @@
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
         <v>113</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>424</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>177</v>
@@ -18848,9 +18779,6 @@
       <c r="A26" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>424</v>
-      </c>
       <c r="C26" s="6" t="s">
         <v>177</v>
       </c>
@@ -18881,9 +18809,6 @@
       <c r="A27" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>424</v>
-      </c>
       <c r="C27" s="6" t="s">
         <v>177</v>
       </c>
@@ -18914,9 +18839,6 @@
       <c r="A28" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>424</v>
-      </c>
       <c r="C28" s="6" t="s">
         <v>177</v>
       </c>
@@ -18955,9 +18877,6 @@
       <c r="A29" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>424</v>
-      </c>
       <c r="C29" s="6" t="s">
         <v>177</v>
       </c>
@@ -18996,9 +18915,6 @@
       <c r="A30" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="B30" s="6" t="s">
-        <v>424</v>
-      </c>
       <c r="C30" s="6" t="s">
         <v>177</v>
       </c>
@@ -19036,9 +18952,6 @@
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
         <v>119</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>424</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>177</v>
@@ -19070,9 +18983,6 @@
       <c r="A32" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="B32" s="6" t="s">
-        <v>424</v>
-      </c>
       <c r="C32" s="6" t="s">
         <v>177</v>
       </c>
@@ -19111,9 +19021,6 @@
       <c r="A33" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="B33" s="6" t="s">
-        <v>424</v>
-      </c>
       <c r="C33" s="6" t="s">
         <v>177</v>
       </c>
@@ -19151,9 +19058,6 @@
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
         <v>122</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>424</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>177</v>
@@ -19185,9 +19089,6 @@
       <c r="A35" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="B35" s="6" t="s">
-        <v>424</v>
-      </c>
       <c r="C35" s="6" t="s">
         <v>177</v>
       </c>
@@ -19225,9 +19126,6 @@
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
         <v>124</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>424</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>177</v>
@@ -19259,9 +19157,6 @@
       <c r="A37" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="B37" s="6" t="s">
-        <v>424</v>
-      </c>
       <c r="C37" s="6" t="s">
         <v>177</v>
       </c>
@@ -19300,9 +19195,6 @@
       <c r="A38" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="B38" s="6" t="s">
-        <v>424</v>
-      </c>
       <c r="C38" s="6" t="s">
         <v>177</v>
       </c>
@@ -19343,9 +19235,6 @@
       <c r="A39" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="B39" s="6" t="s">
-        <v>424</v>
-      </c>
       <c r="C39" s="6" t="s">
         <v>177</v>
       </c>
@@ -19386,9 +19275,6 @@
       <c r="A40" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="B40" s="6" t="s">
-        <v>424</v>
-      </c>
       <c r="C40" s="6" t="s">
         <v>177</v>
       </c>
@@ -19429,9 +19315,6 @@
       <c r="A41" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="B41" s="6" t="s">
-        <v>424</v>
-      </c>
       <c r="C41" s="6" t="s">
         <v>177</v>
       </c>
@@ -19472,9 +19355,6 @@
       <c r="A42" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="B42" s="6" t="s">
-        <v>424</v>
-      </c>
       <c r="C42" s="6" t="s">
         <v>177</v>
       </c>
@@ -19515,9 +19395,6 @@
       <c r="A43" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="B43" s="6" t="s">
-        <v>424</v>
-      </c>
       <c r="C43" s="6" t="s">
         <v>178</v>
       </c>
@@ -19557,9 +19434,6 @@
     <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
         <v>179</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>424</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>180</v>
@@ -19593,9 +19467,6 @@
       <c r="A45" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="B45" s="6" t="s">
-        <v>424</v>
-      </c>
       <c r="C45" s="6" t="s">
         <v>177</v>
       </c>
@@ -19628,9 +19499,6 @@
       <c r="A46" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="B46" s="6" t="s">
-        <v>424</v>
-      </c>
       <c r="C46" s="6" t="s">
         <v>177</v>
       </c>
@@ -19663,9 +19531,6 @@
       <c r="A47" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="B47" s="6" t="s">
-        <v>424</v>
-      </c>
       <c r="C47" s="6" t="s">
         <v>177</v>
       </c>
@@ -19698,9 +19563,6 @@
       <c r="A48" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="B48" s="6" t="s">
-        <v>424</v>
-      </c>
       <c r="C48" s="6" t="s">
         <v>177</v>
       </c>
@@ -19733,9 +19595,6 @@
       <c r="A49" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="B49" s="6" t="s">
-        <v>424</v>
-      </c>
       <c r="C49" s="6" t="s">
         <v>177</v>
       </c>
@@ -19768,9 +19627,6 @@
       <c r="A50" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="B50" s="6" t="s">
-        <v>424</v>
-      </c>
       <c r="C50" s="6" t="s">
         <v>177</v>
       </c>
@@ -19811,9 +19667,6 @@
       <c r="A51" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="B51" s="6" t="s">
-        <v>424</v>
-      </c>
       <c r="C51" s="6" t="s">
         <v>177</v>
       </c>
@@ -19854,9 +19707,6 @@
       <c r="A52" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="B52" s="6" t="s">
-        <v>424</v>
-      </c>
       <c r="C52" s="6" t="s">
         <v>177</v>
       </c>
@@ -19896,9 +19746,6 @@
     <row r="53" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A53" s="6" t="s">
         <v>202</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>424</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>177</v>
@@ -19932,9 +19779,6 @@
       <c r="A54" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="B54" s="6" t="s">
-        <v>424</v>
-      </c>
       <c r="C54" s="6" t="s">
         <v>177</v>
       </c>
@@ -19975,9 +19819,6 @@
       <c r="A55" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="B55" s="6" t="s">
-        <v>424</v>
-      </c>
       <c r="C55" s="6" t="s">
         <v>177</v>
       </c>
@@ -20017,9 +19858,6 @@
     <row r="56" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A56" s="6" t="s">
         <v>205</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>424</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>177</v>
@@ -20053,9 +19891,6 @@
       <c r="A57" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="B57" s="6" t="s">
-        <v>424</v>
-      </c>
       <c r="C57" s="6" t="s">
         <v>177</v>
       </c>
@@ -20096,9 +19931,6 @@
       <c r="A58" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="B58" s="6" t="s">
-        <v>424</v>
-      </c>
       <c r="C58" s="6" t="s">
         <v>177</v>
       </c>
@@ -20139,9 +19971,6 @@
       <c r="A59" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="B59" s="6" t="s">
-        <v>424</v>
-      </c>
       <c r="C59" s="6" t="s">
         <v>177</v>
       </c>
@@ -20186,9 +20015,6 @@
       <c r="A60" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="B60" s="6" t="s">
-        <v>424</v>
-      </c>
       <c r="C60" s="6" t="s">
         <v>177</v>
       </c>
@@ -20230,9 +20056,6 @@
       <c r="A61" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="B61" s="6" t="s">
-        <v>424</v>
-      </c>
       <c r="C61" s="6" t="s">
         <v>177</v>
       </c>
@@ -20268,9 +20091,6 @@
     <row r="62" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A62" s="6" t="s">
         <v>211</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>424</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>177</v>
@@ -20300,9 +20120,6 @@
       <c r="A63" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="B63" s="6" t="s">
-        <v>424</v>
-      </c>
       <c r="C63" s="6" t="s">
         <v>324</v>
       </c>
@@ -20341,9 +20158,6 @@
     <row r="64" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A64" s="6" t="s">
         <v>285</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>424</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>177</v>

--- a/test-data/sscData.xlsx
+++ b/test-data/sscData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Chorus Portal Automation_Work\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFDB3C18-3D11-4666-98E6-494450949758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CA2F5A3-511D-420C-BB94-D389CE3A1A21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="QA" sheetId="1" r:id="rId1"/>
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3933" uniqueCount="721">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4065" uniqueCount="751">
   <si>
     <t>username</t>
   </si>
@@ -2510,6 +2510,96 @@
   </si>
   <si>
     <t>Ai4P@ssword6</t>
+  </si>
+  <si>
+    <t>startLoc</t>
+  </si>
+  <si>
+    <t>destLoc</t>
+  </si>
+  <si>
+    <t>Distance</t>
+  </si>
+  <si>
+    <t>Birmingham</t>
+  </si>
+  <si>
+    <t>Coventry</t>
+  </si>
+  <si>
+    <t>London</t>
+  </si>
+  <si>
+    <t>Bristol</t>
+  </si>
+  <si>
+    <t>stDate</t>
+  </si>
+  <si>
+    <t>endDate</t>
+  </si>
+  <si>
+    <t>18-02-2026</t>
+  </si>
+  <si>
+    <t>19-02-2026</t>
+  </si>
+  <si>
+    <t>20-02-2026</t>
+  </si>
+  <si>
+    <t>trPurpose</t>
+  </si>
+  <si>
+    <t>Business Meeting</t>
+  </si>
+  <si>
+    <t>Leisure</t>
+  </si>
+  <si>
+    <t>Seminar</t>
+  </si>
+  <si>
+    <t>stAirport</t>
+  </si>
+  <si>
+    <t>endAirport</t>
+  </si>
+  <si>
+    <t>Birmingham Airport - BHX</t>
+  </si>
+  <si>
+    <t>Cambridge Airpor - CBG</t>
+  </si>
+  <si>
+    <t>Edinburgh</t>
+  </si>
+  <si>
+    <t>Glasgow</t>
+  </si>
+  <si>
+    <t>Leeds</t>
+  </si>
+  <si>
+    <t>Liverpool</t>
+  </si>
+  <si>
+    <t>Manchester</t>
+  </si>
+  <si>
+    <t>Portsmouth</t>
+  </si>
+  <si>
+    <t>Sheffield</t>
+  </si>
+  <si>
+    <t>Southampton</t>
+  </si>
+  <si>
+    <t>Worthing</t>
+  </si>
+  <si>
+    <t>Leicester</t>
   </si>
 </sst>
 </file>
@@ -2611,7 +2701,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
@@ -2677,6 +2767,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2991,37 +3083,40 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S9"/>
+  <dimension ref="A1:AA30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.109375" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="4.109375" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.109375" style="6" customWidth="1"/>
-    <col min="5" max="5" width="12.5546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.21875" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.88671875" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.21875" style="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.21875" style="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.44140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.21875" style="6" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.21875" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.44140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="23.109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.109375" style="6" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5546875" style="6" customWidth="1"/>
+    <col min="6" max="6" width="11" style="6" customWidth="1"/>
+    <col min="7" max="7" width="10.21875" style="6" customWidth="1"/>
+    <col min="8" max="8" width="20.88671875" style="6" customWidth="1"/>
+    <col min="9" max="9" width="11.21875" style="6" customWidth="1"/>
+    <col min="10" max="10" width="8.21875" style="6" customWidth="1"/>
+    <col min="11" max="11" width="12.109375" style="6" customWidth="1"/>
+    <col min="12" max="12" width="11.44140625" style="6" customWidth="1"/>
+    <col min="13" max="13" width="11.21875" style="6" customWidth="1"/>
+    <col min="14" max="14" width="8.21875" style="6" customWidth="1"/>
+    <col min="15" max="15" width="12.109375" style="6" customWidth="1"/>
+    <col min="16" max="16" width="13.44140625" style="6" customWidth="1"/>
+    <col min="17" max="17" width="23.109375" style="6" customWidth="1"/>
+    <col min="18" max="18" width="15.109375" style="6" customWidth="1"/>
+    <col min="19" max="19" width="14.5546875" style="6" customWidth="1"/>
     <col min="20" max="20" width="21.77734375" style="6" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="15.44140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="18.77734375" style="6" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="20.21875" style="6" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="15.44140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="8.88671875" style="6"/>
+    <col min="22" max="22" width="18.77734375" style="23" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="20.21875" style="28" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.44140625" style="28" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="15.88671875" style="6" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="23" style="6" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="21.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="8.88671875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>11</v>
       </c>
@@ -3079,8 +3174,32 @@
       <c r="S1" s="4" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T1" s="4" t="s">
+        <v>721</v>
+      </c>
+      <c r="U1" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="V1" s="22" t="s">
+        <v>723</v>
+      </c>
+      <c r="W1" s="27" t="s">
+        <v>728</v>
+      </c>
+      <c r="X1" s="27" t="s">
+        <v>729</v>
+      </c>
+      <c r="Y1" s="4" t="s">
+        <v>733</v>
+      </c>
+      <c r="Z1" s="4" t="s">
+        <v>737</v>
+      </c>
+      <c r="AA1" s="4" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>12</v>
       </c>
@@ -3106,7 +3225,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>13</v>
       </c>
@@ -3132,7 +3251,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>16</v>
       </c>
@@ -3156,7 +3275,7 @@
       </c>
       <c r="H4" s="8"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>18</v>
       </c>
@@ -3204,7 +3323,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>31</v>
       </c>
@@ -3227,7 +3346,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>33</v>
       </c>
@@ -3256,7 +3375,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>46</v>
       </c>
@@ -3273,7 +3392,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9" s="15" t="s">
         <v>58</v>
       </c>
@@ -3285,6 +3404,291 @@
       </c>
       <c r="D9" s="13" t="s">
         <v>720</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A10" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>720</v>
+      </c>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="8"/>
+      <c r="T10" s="6" t="s">
+        <v>726</v>
+      </c>
+      <c r="U10" s="6" t="s">
+        <v>727</v>
+      </c>
+      <c r="V10" s="23">
+        <v>195</v>
+      </c>
+      <c r="W10" s="28" t="s">
+        <v>730</v>
+      </c>
+      <c r="X10" s="28" t="s">
+        <v>731</v>
+      </c>
+      <c r="Y10" s="6" t="s">
+        <v>736</v>
+      </c>
+      <c r="Z10" s="6" t="s">
+        <v>739</v>
+      </c>
+      <c r="AA10" s="6" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A11" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>720</v>
+      </c>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="8"/>
+      <c r="T11" s="6" t="s">
+        <v>749</v>
+      </c>
+      <c r="U11" s="6" t="s">
+        <v>724</v>
+      </c>
+      <c r="V11" s="23">
+        <v>217</v>
+      </c>
+      <c r="W11" s="28" t="s">
+        <v>730</v>
+      </c>
+      <c r="X11" s="28" t="s">
+        <v>731</v>
+      </c>
+      <c r="Y11" s="6" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A12" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>720</v>
+      </c>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="8"/>
+      <c r="T12" s="6" t="s">
+        <v>724</v>
+      </c>
+      <c r="U12" s="6" t="s">
+        <v>727</v>
+      </c>
+      <c r="V12" s="23">
+        <v>124</v>
+      </c>
+      <c r="W12" s="28" t="s">
+        <v>731</v>
+      </c>
+      <c r="X12" s="28" t="s">
+        <v>732</v>
+      </c>
+      <c r="Y12" s="6" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="T16" s="4" t="s">
+        <v>721</v>
+      </c>
+      <c r="U16" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="V16" s="22" t="s">
+        <v>723</v>
+      </c>
+      <c r="W16" s="4" t="s">
+        <v>737</v>
+      </c>
+      <c r="X16" s="4" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="17" spans="20:22" x14ac:dyDescent="0.3">
+      <c r="T17" s="6" t="s">
+        <v>724</v>
+      </c>
+      <c r="U17" s="6" t="s">
+        <v>727</v>
+      </c>
+      <c r="V17" s="23">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="18" spans="20:22" x14ac:dyDescent="0.3">
+      <c r="T18" s="6" t="s">
+        <v>727</v>
+      </c>
+      <c r="U18" s="6" t="s">
+        <v>725</v>
+      </c>
+      <c r="V18" s="23">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="19" spans="20:22" x14ac:dyDescent="0.3">
+      <c r="T19" s="6" t="s">
+        <v>725</v>
+      </c>
+      <c r="U19" s="6" t="s">
+        <v>741</v>
+      </c>
+      <c r="V19" s="23">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="20" spans="20:22" x14ac:dyDescent="0.3">
+      <c r="T20" s="6" t="s">
+        <v>741</v>
+      </c>
+      <c r="U20" s="6" t="s">
+        <v>742</v>
+      </c>
+      <c r="V20" s="23">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="21" spans="20:22" x14ac:dyDescent="0.3">
+      <c r="T21" s="6" t="s">
+        <v>742</v>
+      </c>
+      <c r="U21" s="6" t="s">
+        <v>743</v>
+      </c>
+      <c r="V21" s="23">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="22" spans="20:22" x14ac:dyDescent="0.3">
+      <c r="T22" s="6" t="s">
+        <v>743</v>
+      </c>
+      <c r="U22" t="s">
+        <v>750</v>
+      </c>
+      <c r="V22" s="23">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="23" spans="20:22" x14ac:dyDescent="0.3">
+      <c r="T23" t="s">
+        <v>750</v>
+      </c>
+      <c r="U23" s="6" t="s">
+        <v>744</v>
+      </c>
+      <c r="V23" s="23">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="24" spans="20:22" x14ac:dyDescent="0.3">
+      <c r="T24" s="6" t="s">
+        <v>744</v>
+      </c>
+      <c r="U24" s="6" t="s">
+        <v>726</v>
+      </c>
+      <c r="V24" s="23">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="25" spans="20:22" x14ac:dyDescent="0.3">
+      <c r="T25" s="6" t="s">
+        <v>726</v>
+      </c>
+      <c r="U25" s="6" t="s">
+        <v>745</v>
+      </c>
+      <c r="V25" s="23">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="26" spans="20:22" x14ac:dyDescent="0.3">
+      <c r="T26" s="6" t="s">
+        <v>745</v>
+      </c>
+      <c r="U26" s="6" t="s">
+        <v>746</v>
+      </c>
+      <c r="V26" s="23">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="27" spans="20:22" x14ac:dyDescent="0.3">
+      <c r="T27" s="6" t="s">
+        <v>746</v>
+      </c>
+      <c r="U27" s="6" t="s">
+        <v>747</v>
+      </c>
+      <c r="V27" s="23">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="28" spans="20:22" x14ac:dyDescent="0.3">
+      <c r="T28" s="6" t="s">
+        <v>747</v>
+      </c>
+      <c r="U28" s="6" t="s">
+        <v>748</v>
+      </c>
+      <c r="V28" s="23">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="29" spans="20:22" x14ac:dyDescent="0.3">
+      <c r="T29" s="6" t="s">
+        <v>748</v>
+      </c>
+      <c r="U29" s="6" t="s">
+        <v>749</v>
+      </c>
+      <c r="V29" s="23">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="30" spans="20:22" x14ac:dyDescent="0.3">
+      <c r="T30" s="6" t="s">
+        <v>749</v>
+      </c>
+      <c r="U30" s="6" t="s">
+        <v>724</v>
+      </c>
+      <c r="V30" s="23">
+        <v>217</v>
       </c>
     </row>
   </sheetData>
@@ -3293,9 +3697,12 @@
     <hyperlink ref="H3" r:id="rId2" xr:uid="{6B0F5573-1B6D-40BD-A1CD-4FF2D6A12B60}"/>
     <hyperlink ref="D2" r:id="rId3" display="Ai4P@ssword3" xr:uid="{BFC9E07A-6B6B-4917-9373-71F733F22D5F}"/>
     <hyperlink ref="D9" r:id="rId4" display="Ai4P@ssword4" xr:uid="{C693285A-AACF-4030-BAA6-4C6360692518}"/>
+    <hyperlink ref="D10" r:id="rId5" display="Ai4P@ssword3" xr:uid="{B1AC8471-FE38-491F-AAB3-B38C4048CD41}"/>
+    <hyperlink ref="D11" r:id="rId6" display="Ai4P@ssword3" xr:uid="{ACA9CCDE-DEF1-46AD-B314-6DAEDD9FF34D}"/>
+    <hyperlink ref="D12" r:id="rId7" display="Ai4P@ssword3" xr:uid="{935C9AFC-698F-410C-A364-D9F348F9314C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId8"/>
 </worksheet>
 </file>
 
@@ -17800,7 +18207,8 @@
     <col min="4" max="4" width="7.21875" style="6" customWidth="1"/>
     <col min="5" max="5" width="102.44140625" style="20" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.5546875" style="6" customWidth="1"/>
-    <col min="7" max="8" width="13.88671875" style="6" customWidth="1"/>
+    <col min="7" max="7" width="13.88671875" style="6" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="13.88671875" style="6" customWidth="1"/>
     <col min="9" max="10" width="14.109375" style="20" customWidth="1"/>
     <col min="11" max="11" width="11.77734375" style="23" customWidth="1"/>
     <col min="12" max="12" width="25.5546875" style="6" customWidth="1"/>
@@ -17913,6 +18321,9 @@
       <c r="A3" s="6" t="s">
         <v>57</v>
       </c>
+      <c r="B3" s="6" t="s">
+        <v>424</v>
+      </c>
       <c r="C3" s="6" t="s">
         <v>177</v>
       </c>
@@ -17951,6 +18362,9 @@
       <c r="A4" s="6" t="s">
         <v>64</v>
       </c>
+      <c r="B4" s="6" t="s">
+        <v>424</v>
+      </c>
       <c r="C4" s="6" t="s">
         <v>177</v>
       </c>
@@ -17989,6 +18403,9 @@
       <c r="A5" s="6" t="s">
         <v>66</v>
       </c>
+      <c r="B5" s="6" t="s">
+        <v>424</v>
+      </c>
       <c r="C5" s="6" t="s">
         <v>177</v>
       </c>
@@ -18027,6 +18444,9 @@
       <c r="A6" s="6" t="s">
         <v>67</v>
       </c>
+      <c r="B6" s="6" t="s">
+        <v>424</v>
+      </c>
       <c r="C6" s="6" t="s">
         <v>177</v>
       </c>
@@ -18065,6 +18485,9 @@
       <c r="A7" s="6" t="s">
         <v>68</v>
       </c>
+      <c r="B7" s="6" t="s">
+        <v>424</v>
+      </c>
       <c r="C7" s="6" t="s">
         <v>177</v>
       </c>
@@ -18103,6 +18526,9 @@
       <c r="A8" s="6" t="s">
         <v>69</v>
       </c>
+      <c r="B8" s="6" t="s">
+        <v>424</v>
+      </c>
       <c r="C8" s="6" t="s">
         <v>177</v>
       </c>
@@ -18141,6 +18567,9 @@
       <c r="A9" s="6" t="s">
         <v>70</v>
       </c>
+      <c r="B9" s="6" t="s">
+        <v>424</v>
+      </c>
       <c r="C9" s="6" t="s">
         <v>177</v>
       </c>
@@ -18179,6 +18608,9 @@
       <c r="A10" s="6" t="s">
         <v>71</v>
       </c>
+      <c r="B10" s="6" t="s">
+        <v>424</v>
+      </c>
       <c r="C10" s="6" t="s">
         <v>177</v>
       </c>
@@ -18217,6 +18649,9 @@
       <c r="A11" s="6" t="s">
         <v>72</v>
       </c>
+      <c r="B11" s="6" t="s">
+        <v>424</v>
+      </c>
       <c r="C11" s="6" t="s">
         <v>177</v>
       </c>
@@ -18255,6 +18690,9 @@
       <c r="A12" s="6" t="s">
         <v>73</v>
       </c>
+      <c r="B12" s="6" t="s">
+        <v>424</v>
+      </c>
       <c r="C12" s="6" t="s">
         <v>177</v>
       </c>
@@ -18293,6 +18731,9 @@
       <c r="A13" s="6" t="s">
         <v>74</v>
       </c>
+      <c r="B13" s="6" t="s">
+        <v>424</v>
+      </c>
       <c r="C13" s="6" t="s">
         <v>177</v>
       </c>
@@ -18331,6 +18772,9 @@
       <c r="A14" s="6" t="s">
         <v>75</v>
       </c>
+      <c r="B14" s="6" t="s">
+        <v>424</v>
+      </c>
       <c r="C14" s="6" t="s">
         <v>177</v>
       </c>
@@ -18369,6 +18813,9 @@
       <c r="A15" s="6" t="s">
         <v>76</v>
       </c>
+      <c r="B15" s="6" t="s">
+        <v>424</v>
+      </c>
       <c r="C15" s="6" t="s">
         <v>177</v>
       </c>
@@ -18407,6 +18854,9 @@
       <c r="A16" s="6" t="s">
         <v>77</v>
       </c>
+      <c r="B16" s="6" t="s">
+        <v>424</v>
+      </c>
       <c r="C16" s="6" t="s">
         <v>177</v>
       </c>
@@ -18445,6 +18895,9 @@
       <c r="A17" s="6" t="s">
         <v>78</v>
       </c>
+      <c r="B17" s="6" t="s">
+        <v>424</v>
+      </c>
       <c r="C17" s="6" t="s">
         <v>177</v>
       </c>
@@ -18483,6 +18936,9 @@
       <c r="A18" s="6" t="s">
         <v>79</v>
       </c>
+      <c r="B18" s="6" t="s">
+        <v>424</v>
+      </c>
       <c r="C18" s="6" t="s">
         <v>177</v>
       </c>
@@ -18521,6 +18977,9 @@
       <c r="A19" s="6" t="s">
         <v>80</v>
       </c>
+      <c r="B19" s="6" t="s">
+        <v>424</v>
+      </c>
       <c r="C19" s="6" t="s">
         <v>177</v>
       </c>
@@ -18559,6 +19018,9 @@
       <c r="A20" s="6" t="s">
         <v>81</v>
       </c>
+      <c r="B20" s="6" t="s">
+        <v>424</v>
+      </c>
       <c r="C20" s="6" t="s">
         <v>177</v>
       </c>
@@ -18597,6 +19059,9 @@
       <c r="A21" s="6" t="s">
         <v>82</v>
       </c>
+      <c r="B21" s="6" t="s">
+        <v>424</v>
+      </c>
       <c r="C21" s="6" t="s">
         <v>177</v>
       </c>
@@ -18635,6 +19100,9 @@
       <c r="A22" s="6" t="s">
         <v>83</v>
       </c>
+      <c r="B22" s="6" t="s">
+        <v>424</v>
+      </c>
       <c r="C22" s="6" t="s">
         <v>177</v>
       </c>
@@ -18673,6 +19141,9 @@
       <c r="A23" s="6" t="s">
         <v>84</v>
       </c>
+      <c r="B23" s="6" t="s">
+        <v>424</v>
+      </c>
       <c r="C23" s="6" t="s">
         <v>177</v>
       </c>
@@ -18711,6 +19182,9 @@
       <c r="A24" s="6" t="s">
         <v>112</v>
       </c>
+      <c r="B24" s="6" t="s">
+        <v>424</v>
+      </c>
       <c r="C24" s="6" t="s">
         <v>177</v>
       </c>
@@ -18748,6 +19222,9 @@
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
         <v>113</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>424</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>177</v>
@@ -18779,6 +19256,9 @@
       <c r="A26" s="6" t="s">
         <v>114</v>
       </c>
+      <c r="B26" s="6" t="s">
+        <v>424</v>
+      </c>
       <c r="C26" s="6" t="s">
         <v>177</v>
       </c>
@@ -18809,6 +19289,9 @@
       <c r="A27" s="6" t="s">
         <v>115</v>
       </c>
+      <c r="B27" s="6" t="s">
+        <v>424</v>
+      </c>
       <c r="C27" s="6" t="s">
         <v>177</v>
       </c>
@@ -18839,6 +19322,9 @@
       <c r="A28" s="6" t="s">
         <v>116</v>
       </c>
+      <c r="B28" s="6" t="s">
+        <v>424</v>
+      </c>
       <c r="C28" s="6" t="s">
         <v>177</v>
       </c>
@@ -18877,6 +19363,9 @@
       <c r="A29" s="6" t="s">
         <v>117</v>
       </c>
+      <c r="B29" s="6" t="s">
+        <v>424</v>
+      </c>
       <c r="C29" s="6" t="s">
         <v>177</v>
       </c>
@@ -18915,6 +19404,9 @@
       <c r="A30" s="6" t="s">
         <v>118</v>
       </c>
+      <c r="B30" s="6" t="s">
+        <v>424</v>
+      </c>
       <c r="C30" s="6" t="s">
         <v>177</v>
       </c>
@@ -18952,6 +19444,9 @@
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
         <v>119</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>424</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>177</v>
@@ -18983,6 +19478,9 @@
       <c r="A32" s="6" t="s">
         <v>120</v>
       </c>
+      <c r="B32" s="6" t="s">
+        <v>424</v>
+      </c>
       <c r="C32" s="6" t="s">
         <v>177</v>
       </c>
@@ -19021,6 +19519,9 @@
       <c r="A33" s="6" t="s">
         <v>121</v>
       </c>
+      <c r="B33" s="6" t="s">
+        <v>424</v>
+      </c>
       <c r="C33" s="6" t="s">
         <v>177</v>
       </c>
@@ -19058,6 +19559,9 @@
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
         <v>122</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>424</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>177</v>
@@ -19089,6 +19593,9 @@
       <c r="A35" s="6" t="s">
         <v>123</v>
       </c>
+      <c r="B35" s="6" t="s">
+        <v>424</v>
+      </c>
       <c r="C35" s="6" t="s">
         <v>177</v>
       </c>
@@ -19126,6 +19633,9 @@
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
         <v>124</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>424</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>177</v>
@@ -19157,6 +19667,9 @@
       <c r="A37" s="6" t="s">
         <v>125</v>
       </c>
+      <c r="B37" s="6" t="s">
+        <v>424</v>
+      </c>
       <c r="C37" s="6" t="s">
         <v>177</v>
       </c>
@@ -19195,6 +19708,9 @@
       <c r="A38" s="6" t="s">
         <v>126</v>
       </c>
+      <c r="B38" s="6" t="s">
+        <v>424</v>
+      </c>
       <c r="C38" s="6" t="s">
         <v>177</v>
       </c>
@@ -19235,6 +19751,9 @@
       <c r="A39" s="6" t="s">
         <v>127</v>
       </c>
+      <c r="B39" s="6" t="s">
+        <v>424</v>
+      </c>
       <c r="C39" s="6" t="s">
         <v>177</v>
       </c>
@@ -19275,6 +19794,9 @@
       <c r="A40" s="6" t="s">
         <v>128</v>
       </c>
+      <c r="B40" s="6" t="s">
+        <v>424</v>
+      </c>
       <c r="C40" s="6" t="s">
         <v>177</v>
       </c>
@@ -19315,6 +19837,9 @@
       <c r="A41" s="6" t="s">
         <v>129</v>
       </c>
+      <c r="B41" s="6" t="s">
+        <v>424</v>
+      </c>
       <c r="C41" s="6" t="s">
         <v>177</v>
       </c>
@@ -19355,6 +19880,9 @@
       <c r="A42" s="6" t="s">
         <v>165</v>
       </c>
+      <c r="B42" s="6" t="s">
+        <v>424</v>
+      </c>
       <c r="C42" s="6" t="s">
         <v>177</v>
       </c>
@@ -19395,6 +19923,9 @@
       <c r="A43" s="6" t="s">
         <v>166</v>
       </c>
+      <c r="B43" s="6" t="s">
+        <v>424</v>
+      </c>
       <c r="C43" s="6" t="s">
         <v>178</v>
       </c>
@@ -19434,6 +19965,9 @@
     <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
         <v>179</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>424</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>180</v>
@@ -19467,6 +20001,9 @@
       <c r="A45" s="6" t="s">
         <v>181</v>
       </c>
+      <c r="B45" s="6" t="s">
+        <v>424</v>
+      </c>
       <c r="C45" s="6" t="s">
         <v>177</v>
       </c>
@@ -19499,6 +20036,9 @@
       <c r="A46" s="6" t="s">
         <v>193</v>
       </c>
+      <c r="B46" s="6" t="s">
+        <v>424</v>
+      </c>
       <c r="C46" s="6" t="s">
         <v>177</v>
       </c>
@@ -19531,6 +20071,9 @@
       <c r="A47" s="6" t="s">
         <v>196</v>
       </c>
+      <c r="B47" s="6" t="s">
+        <v>424</v>
+      </c>
       <c r="C47" s="6" t="s">
         <v>177</v>
       </c>
@@ -19563,6 +20106,9 @@
       <c r="A48" s="6" t="s">
         <v>197</v>
       </c>
+      <c r="B48" s="6" t="s">
+        <v>424</v>
+      </c>
       <c r="C48" s="6" t="s">
         <v>177</v>
       </c>
@@ -19595,6 +20141,9 @@
       <c r="A49" s="6" t="s">
         <v>198</v>
       </c>
+      <c r="B49" s="6" t="s">
+        <v>424</v>
+      </c>
       <c r="C49" s="6" t="s">
         <v>177</v>
       </c>
@@ -19627,6 +20176,9 @@
       <c r="A50" s="6" t="s">
         <v>199</v>
       </c>
+      <c r="B50" s="6" t="s">
+        <v>424</v>
+      </c>
       <c r="C50" s="6" t="s">
         <v>177</v>
       </c>
@@ -19667,6 +20219,9 @@
       <c r="A51" s="6" t="s">
         <v>200</v>
       </c>
+      <c r="B51" s="6" t="s">
+        <v>424</v>
+      </c>
       <c r="C51" s="6" t="s">
         <v>177</v>
       </c>
@@ -19707,6 +20262,9 @@
       <c r="A52" s="6" t="s">
         <v>201</v>
       </c>
+      <c r="B52" s="6" t="s">
+        <v>424</v>
+      </c>
       <c r="C52" s="6" t="s">
         <v>177</v>
       </c>
@@ -19746,6 +20304,9 @@
     <row r="53" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A53" s="6" t="s">
         <v>202</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>424</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>177</v>
@@ -19779,6 +20340,9 @@
       <c r="A54" s="6" t="s">
         <v>203</v>
       </c>
+      <c r="B54" s="6" t="s">
+        <v>424</v>
+      </c>
       <c r="C54" s="6" t="s">
         <v>177</v>
       </c>
@@ -19819,6 +20383,9 @@
       <c r="A55" s="6" t="s">
         <v>204</v>
       </c>
+      <c r="B55" s="6" t="s">
+        <v>424</v>
+      </c>
       <c r="C55" s="6" t="s">
         <v>177</v>
       </c>
@@ -19858,6 +20425,9 @@
     <row r="56" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A56" s="6" t="s">
         <v>205</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>424</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>177</v>
@@ -19891,6 +20461,9 @@
       <c r="A57" s="6" t="s">
         <v>206</v>
       </c>
+      <c r="B57" s="6" t="s">
+        <v>424</v>
+      </c>
       <c r="C57" s="6" t="s">
         <v>177</v>
       </c>
@@ -19931,6 +20504,9 @@
       <c r="A58" s="6" t="s">
         <v>207</v>
       </c>
+      <c r="B58" s="6" t="s">
+        <v>424</v>
+      </c>
       <c r="C58" s="6" t="s">
         <v>177</v>
       </c>
@@ -19971,6 +20547,9 @@
       <c r="A59" s="6" t="s">
         <v>208</v>
       </c>
+      <c r="B59" s="6" t="s">
+        <v>424</v>
+      </c>
       <c r="C59" s="6" t="s">
         <v>177</v>
       </c>
@@ -20015,6 +20594,9 @@
       <c r="A60" s="6" t="s">
         <v>209</v>
       </c>
+      <c r="B60" s="6" t="s">
+        <v>424</v>
+      </c>
       <c r="C60" s="6" t="s">
         <v>177</v>
       </c>
@@ -20056,6 +20638,9 @@
       <c r="A61" s="6" t="s">
         <v>210</v>
       </c>
+      <c r="B61" s="6" t="s">
+        <v>424</v>
+      </c>
       <c r="C61" s="6" t="s">
         <v>177</v>
       </c>
@@ -20091,6 +20676,9 @@
     <row r="62" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A62" s="6" t="s">
         <v>211</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>424</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>177</v>
@@ -20120,6 +20708,9 @@
       <c r="A63" s="6" t="s">
         <v>274</v>
       </c>
+      <c r="B63" s="6" t="s">
+        <v>424</v>
+      </c>
       <c r="C63" s="6" t="s">
         <v>324</v>
       </c>
@@ -20158,6 +20749,9 @@
     <row r="64" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A64" s="6" t="s">
         <v>285</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>424</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>177</v>

--- a/test-data/sscData.xlsx
+++ b/test-data/sscData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Chorus Portal Automation_Work\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CA2F5A3-511D-420C-BB94-D389CE3A1A21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D90AE950-3A88-4C78-B3AB-111650657890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="QA" sheetId="1" r:id="rId1"/>
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4065" uniqueCount="751">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4065" uniqueCount="753">
   <si>
     <t>username</t>
   </si>
@@ -2539,15 +2539,6 @@
     <t>endDate</t>
   </si>
   <si>
-    <t>18-02-2026</t>
-  </si>
-  <si>
-    <t>19-02-2026</t>
-  </si>
-  <si>
-    <t>20-02-2026</t>
-  </si>
-  <si>
     <t>trPurpose</t>
   </si>
   <si>
@@ -2569,9 +2560,6 @@
     <t>Birmingham Airport - BHX</t>
   </si>
   <si>
-    <t>Cambridge Airpor - CBG</t>
-  </si>
-  <si>
     <t>Edinburgh</t>
   </si>
   <si>
@@ -2600,6 +2588,24 @@
   </si>
   <si>
     <t>Leicester</t>
+  </si>
+  <si>
+    <t>23-02-2026</t>
+  </si>
+  <si>
+    <t>25-02-2026</t>
+  </si>
+  <si>
+    <t>24-02-2026</t>
+  </si>
+  <si>
+    <t>26-02-2026</t>
+  </si>
+  <si>
+    <t>27-02-2026</t>
+  </si>
+  <si>
+    <t>Cambridge Airport - CBG</t>
   </si>
 </sst>
 </file>
@@ -3111,8 +3117,8 @@
     <col min="23" max="23" width="20.21875" style="28" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="15.44140625" style="28" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="15.88671875" style="6" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="23" style="6" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="21.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="24" style="6" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="22.6640625" style="6" bestFit="1" customWidth="1"/>
     <col min="28" max="16384" width="8.88671875" style="6"/>
   </cols>
   <sheetData>
@@ -3190,13 +3196,13 @@
         <v>729</v>
       </c>
       <c r="Y1" s="4" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="Z1" s="4" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="AA1" s="4" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.3">
@@ -3424,28 +3430,28 @@
       <c r="G10" s="7"/>
       <c r="H10" s="8"/>
       <c r="T10" s="6" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="U10" s="6" t="s">
         <v>727</v>
       </c>
       <c r="V10" s="23">
-        <v>195</v>
+        <v>124</v>
       </c>
       <c r="W10" s="28" t="s">
-        <v>730</v>
+        <v>747</v>
       </c>
       <c r="X10" s="28" t="s">
-        <v>731</v>
+        <v>748</v>
       </c>
       <c r="Y10" s="6" t="s">
+        <v>733</v>
+      </c>
+      <c r="Z10" s="6" t="s">
         <v>736</v>
       </c>
-      <c r="Z10" s="6" t="s">
-        <v>739</v>
-      </c>
       <c r="AA10" s="6" t="s">
-        <v>740</v>
+        <v>752</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.3">
@@ -3466,22 +3472,22 @@
       <c r="G11" s="7"/>
       <c r="H11" s="8"/>
       <c r="T11" s="6" t="s">
+        <v>741</v>
+      </c>
+      <c r="U11" s="6" t="s">
+        <v>742</v>
+      </c>
+      <c r="V11" s="23">
+        <v>308</v>
+      </c>
+      <c r="W11" s="28" t="s">
         <v>749</v>
       </c>
-      <c r="U11" s="6" t="s">
-        <v>724</v>
-      </c>
-      <c r="V11" s="23">
-        <v>217</v>
-      </c>
-      <c r="W11" s="28" t="s">
-        <v>730</v>
-      </c>
       <c r="X11" s="28" t="s">
+        <v>750</v>
+      </c>
+      <c r="Y11" s="6" t="s">
         <v>731</v>
-      </c>
-      <c r="Y11" s="6" t="s">
-        <v>734</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.3">
@@ -3502,22 +3508,22 @@
       <c r="G12" s="7"/>
       <c r="H12" s="8"/>
       <c r="T12" s="6" t="s">
-        <v>724</v>
+        <v>742</v>
       </c>
       <c r="U12" s="6" t="s">
-        <v>727</v>
+        <v>743</v>
       </c>
       <c r="V12" s="23">
-        <v>124</v>
+        <v>347</v>
       </c>
       <c r="W12" s="28" t="s">
-        <v>731</v>
+        <v>748</v>
       </c>
       <c r="X12" s="28" t="s">
+        <v>751</v>
+      </c>
+      <c r="Y12" s="6" t="s">
         <v>732</v>
-      </c>
-      <c r="Y12" s="6" t="s">
-        <v>735</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.3">
@@ -3531,10 +3537,10 @@
         <v>723</v>
       </c>
       <c r="W16" s="4" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="X16" s="4" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
     </row>
     <row r="17" spans="20:22" x14ac:dyDescent="0.3">
@@ -3564,7 +3570,7 @@
         <v>725</v>
       </c>
       <c r="U19" s="6" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="V19" s="23">
         <v>410</v>
@@ -3572,10 +3578,10 @@
     </row>
     <row r="20" spans="20:22" x14ac:dyDescent="0.3">
       <c r="T20" s="6" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="U20" s="6" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="V20" s="23">
         <v>75</v>
@@ -3583,10 +3589,10 @@
     </row>
     <row r="21" spans="20:22" x14ac:dyDescent="0.3">
       <c r="T21" s="6" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="U21" s="6" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="V21" s="23">
         <v>290</v>
@@ -3594,10 +3600,10 @@
     </row>
     <row r="22" spans="20:22" x14ac:dyDescent="0.3">
       <c r="T22" s="6" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="U22" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="V22" s="23">
         <v>132</v>
@@ -3605,10 +3611,10 @@
     </row>
     <row r="23" spans="20:22" x14ac:dyDescent="0.3">
       <c r="T23" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="U23" s="6" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="V23" s="23">
         <v>150</v>
@@ -3616,7 +3622,7 @@
     </row>
     <row r="24" spans="20:22" x14ac:dyDescent="0.3">
       <c r="T24" s="6" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="U24" s="6" t="s">
         <v>726</v>
@@ -3630,7 +3636,7 @@
         <v>726</v>
       </c>
       <c r="U25" s="6" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="V25" s="23">
         <v>262</v>
@@ -3638,10 +3644,10 @@
     </row>
     <row r="26" spans="20:22" x14ac:dyDescent="0.3">
       <c r="T26" s="6" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="U26" s="6" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="V26" s="23">
         <v>308</v>
@@ -3649,10 +3655,10 @@
     </row>
     <row r="27" spans="20:22" x14ac:dyDescent="0.3">
       <c r="T27" s="6" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="U27" s="6" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="V27" s="23">
         <v>347</v>
@@ -3660,10 +3666,10 @@
     </row>
     <row r="28" spans="20:22" x14ac:dyDescent="0.3">
       <c r="T28" s="6" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="U28" s="6" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="V28" s="23">
         <v>310</v>
@@ -3671,10 +3677,10 @@
     </row>
     <row r="29" spans="20:22" x14ac:dyDescent="0.3">
       <c r="T29" s="6" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="U29" s="6" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="V29" s="23">
         <v>90</v>
@@ -3682,7 +3688,7 @@
     </row>
     <row r="30" spans="20:22" x14ac:dyDescent="0.3">
       <c r="T30" s="6" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="U30" s="6" t="s">
         <v>724</v>

--- a/test-data/sscData.xlsx
+++ b/test-data/sscData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Chorus Portal Automation_Work\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D90AE950-3A88-4C78-B3AB-111650657890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5065E3B6-87DF-4259-8EDE-5968D97EE12E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
